--- a/output/2024-04-04.xlsx
+++ b/output/2024-04-04.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.66</v>
+        <v>3.05</v>
       </c>
       <c r="F14" t="n">
-        <v>9.289999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="G14" t="n">
-        <v>317.5</v>
+        <v>299.7</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>289.11</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-44.97</v>
+        <v>110.74</v>
       </c>
       <c r="L14" t="n">
-        <v>292.58</v>
+        <v>134.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:38:11</t>
+          <t>06:38:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="F15" t="n">
-        <v>9.630000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="G15" t="n">
-        <v>306.6</v>
+        <v>309.6</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>331.18</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>46.49</v>
+        <v>126.08</v>
       </c>
       <c r="L15" t="n">
-        <v>334.43</v>
+        <v>157.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:40:33</t>
+          <t>06:40:29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.44</v>
+        <v>4.14</v>
       </c>
       <c r="F16" t="n">
-        <v>9.35</v>
+        <v>9.52</v>
       </c>
       <c r="G16" t="n">
-        <v>307.3</v>
+        <v>305.8</v>
       </c>
       <c r="H16" t="n">
-        <v>96.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-99.18000000000001</v>
+        <v>63.27</v>
       </c>
       <c r="K16" t="n">
-        <v>-120.92</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>156.4</v>
+        <v>115.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:43:39</t>
+          <t>06:45:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="F17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="G17" t="n">
-        <v>305.2</v>
+        <v>292.6</v>
       </c>
       <c r="H17" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>96.91</v>
+        <v>137.89</v>
       </c>
       <c r="K17" t="n">
-        <v>111.33</v>
+        <v>-243.84</v>
       </c>
       <c r="L17" t="n">
-        <v>147.6</v>
+        <v>280.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:44:45</t>
+          <t>06:46:59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.06</v>
+        <v>3.29</v>
       </c>
       <c r="F18" t="n">
-        <v>9.25</v>
+        <v>9.35</v>
       </c>
       <c r="G18" t="n">
-        <v>293.9</v>
+        <v>290.9</v>
       </c>
       <c r="H18" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>-224.13</v>
+        <v>-112.38</v>
       </c>
       <c r="K18" t="n">
-        <v>56.53</v>
+        <v>40.65</v>
       </c>
       <c r="L18" t="n">
-        <v>231.15</v>
+        <v>119.51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:46:43</t>
+          <t>06:49:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="F19" t="n">
-        <v>10.35</v>
+        <v>9.92</v>
       </c>
       <c r="G19" t="n">
-        <v>296.8</v>
+        <v>298.5</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-283.19</v>
+        <v>-237.05</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.89</v>
+        <v>111.73</v>
       </c>
       <c r="L19" t="n">
-        <v>283.23</v>
+        <v>262.06</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:50:44</t>
+          <t>06:55:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="F20" t="n">
-        <v>9.789999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="G20" t="n">
-        <v>304.2</v>
+        <v>302.1</v>
       </c>
       <c r="H20" t="n">
         <v>100</v>
@@ -892,19 +892,19 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>29.18</v>
+        <v>157.89</v>
       </c>
       <c r="K20" t="n">
-        <v>-448.52</v>
+        <v>-84.79000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>449.47</v>
+        <v>179.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:52:26</t>
+          <t>06:56:09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.66</v>
+        <v>3.81</v>
       </c>
       <c r="F21" t="n">
-        <v>9.43</v>
+        <v>9.07</v>
       </c>
       <c r="G21" t="n">
-        <v>295.5</v>
+        <v>290.2</v>
       </c>
       <c r="H21" t="n">
-        <v>96.7</v>
+        <v>97.5</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-64.55</v>
+        <v>143.86</v>
       </c>
       <c r="K21" t="n">
-        <v>-96.95999999999999</v>
+        <v>412.73</v>
       </c>
       <c r="L21" t="n">
-        <v>116.48</v>
+        <v>437.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:54:04</t>
+          <t>06:57:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.86</v>
+        <v>4.17</v>
       </c>
       <c r="F22" t="n">
-        <v>9.890000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="G22" t="n">
-        <v>306.1</v>
+        <v>311.2</v>
       </c>
       <c r="H22" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>24.61</v>
+        <v>-505.82</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.41</v>
+        <v>81.11</v>
       </c>
       <c r="L22" t="n">
-        <v>25.7</v>
+        <v>512.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:58:11</t>
+          <t>07:02:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.71</v>
+        <v>3.44</v>
       </c>
       <c r="F23" t="n">
-        <v>9.529999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="G23" t="n">
-        <v>293.7</v>
+        <v>308</v>
       </c>
       <c r="H23" t="n">
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>29.58</v>
+        <v>-639.83</v>
       </c>
       <c r="K23" t="n">
-        <v>188.94</v>
+        <v>-53.38</v>
       </c>
       <c r="L23" t="n">
-        <v>191.24</v>
+        <v>642.05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:59:28</t>
+          <t>07:04:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,13 +1045,13 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.41</v>
+        <v>3.6</v>
       </c>
       <c r="F24" t="n">
-        <v>8.99</v>
+        <v>9.07</v>
       </c>
       <c r="G24" t="n">
-        <v>291.2</v>
+        <v>296.2</v>
       </c>
       <c r="H24" t="n">
         <v>100</v>
@@ -1060,19 +1060,19 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-28.92</v>
+        <v>285.81</v>
       </c>
       <c r="K24" t="n">
-        <v>-45.75</v>
+        <v>198.62</v>
       </c>
       <c r="L24" t="n">
-        <v>54.12</v>
+        <v>348.05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:00:49</t>
+          <t>07:05:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="F25" t="n">
-        <v>9.880000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="G25" t="n">
-        <v>288.7</v>
+        <v>301</v>
       </c>
       <c r="H25" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-257.1</v>
+        <v>-294.14</v>
       </c>
       <c r="K25" t="n">
-        <v>-43.85</v>
+        <v>190.12</v>
       </c>
       <c r="L25" t="n">
-        <v>260.81</v>
+        <v>350.23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:04:02</t>
+          <t>07:10:39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="F26" t="n">
-        <v>8.550000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="G26" t="n">
-        <v>305.2</v>
+        <v>275.4</v>
       </c>
       <c r="H26" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>71.94</v>
+        <v>-209.15</v>
       </c>
       <c r="K26" t="n">
-        <v>431.26</v>
+        <v>-591.59</v>
       </c>
       <c r="L26" t="n">
-        <v>437.22</v>
+        <v>627.47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:05:44</t>
+          <t>07:13:12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.95</v>
+        <v>3.48</v>
       </c>
       <c r="F27" t="n">
-        <v>9.69</v>
+        <v>9.02</v>
       </c>
       <c r="G27" t="n">
-        <v>298.2</v>
+        <v>299.4</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-712.46</v>
+        <v>-492.48</v>
       </c>
       <c r="K27" t="n">
-        <v>-181.8</v>
+        <v>401.22</v>
       </c>
       <c r="L27" t="n">
-        <v>735.29</v>
+        <v>635.23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:07:22</t>
+          <t>07:15:13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.91</v>
+        <v>4.05</v>
       </c>
       <c r="F28" t="n">
-        <v>9.550000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="G28" t="n">
-        <v>307.1</v>
+        <v>292.9</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-244.56</v>
+        <v>606.28</v>
       </c>
       <c r="K28" t="n">
-        <v>-752.3200000000001</v>
+        <v>18.9</v>
       </c>
       <c r="L28" t="n">
-        <v>791.08</v>
+        <v>606.5700000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:16:45</t>
+          <t>07:26:29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="F29" t="n">
-        <v>9.65</v>
+        <v>9.01</v>
       </c>
       <c r="G29" t="n">
-        <v>303.5</v>
+        <v>300.6</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-195.81</v>
+        <v>-55.52</v>
       </c>
       <c r="K29" t="n">
-        <v>66.19</v>
+        <v>-247.14</v>
       </c>
       <c r="L29" t="n">
-        <v>206.69</v>
+        <v>253.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:17:27</t>
+          <t>07:28:46</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.18</v>
+        <v>3.65</v>
       </c>
       <c r="F30" t="n">
-        <v>9.869999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="G30" t="n">
-        <v>309.1</v>
+        <v>315.8</v>
       </c>
       <c r="H30" t="n">
-        <v>98.3</v>
+        <v>96.5</v>
       </c>
       <c r="I30" t="n">
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-41.11</v>
+        <v>-255.12</v>
       </c>
       <c r="K30" t="n">
-        <v>-61.24</v>
+        <v>-90.19</v>
       </c>
       <c r="L30" t="n">
-        <v>73.76000000000001</v>
+        <v>270.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:18:55</t>
+          <t>07:30:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.57</v>
+        <v>3.96</v>
       </c>
       <c r="F31" t="n">
-        <v>10.27</v>
+        <v>9.27</v>
       </c>
       <c r="G31" t="n">
-        <v>295.9</v>
+        <v>297.5</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>103.68</v>
+        <v>-123.46</v>
       </c>
       <c r="K31" t="n">
-        <v>34.17</v>
+        <v>-47.68</v>
       </c>
       <c r="L31" t="n">
-        <v>109.17</v>
+        <v>132.35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:23:59</t>
+          <t>07:35:19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.28</v>
+        <v>3.84</v>
       </c>
       <c r="F32" t="n">
-        <v>9.380000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>302.7</v>
+        <v>301.7</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>95.03</v>
+        <v>148.38</v>
       </c>
       <c r="K32" t="n">
-        <v>223.68</v>
+        <v>-41.39</v>
       </c>
       <c r="L32" t="n">
-        <v>243.03</v>
+        <v>154.04</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:25:49</t>
+          <t>07:38:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.22</v>
+        <v>4.52</v>
       </c>
       <c r="F33" t="n">
-        <v>10.09</v>
+        <v>9.59</v>
       </c>
       <c r="G33" t="n">
-        <v>282</v>
+        <v>284.7</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-241.57</v>
+        <v>113.76</v>
       </c>
       <c r="K33" t="n">
-        <v>34.7</v>
+        <v>48.33</v>
       </c>
       <c r="L33" t="n">
-        <v>244.05</v>
+        <v>123.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:26:39</t>
+          <t>07:39:19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.86</v>
+        <v>3.76</v>
       </c>
       <c r="F34" t="n">
-        <v>9.83</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>321.9</v>
+        <v>293.5</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-25.65</v>
+        <v>-150.43</v>
       </c>
       <c r="K34" t="n">
-        <v>-340.14</v>
+        <v>-146.38</v>
       </c>
       <c r="L34" t="n">
-        <v>341.1</v>
+        <v>209.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:30:41</t>
+          <t>07:43:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.83</v>
+        <v>3.54</v>
       </c>
       <c r="F35" t="n">
-        <v>10.1</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>294.3</v>
+        <v>307.5</v>
       </c>
       <c r="H35" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.85</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>56.84</v>
+        <v>-13.81</v>
       </c>
       <c r="L35" t="n">
-        <v>56.87</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:33:15</t>
+          <t>07:45:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="F36" t="n">
-        <v>9.98</v>
+        <v>9.67</v>
       </c>
       <c r="G36" t="n">
-        <v>302.4</v>
+        <v>294.5</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-59.8</v>
+        <v>-347.65</v>
       </c>
       <c r="K36" t="n">
-        <v>93.45999999999999</v>
+        <v>271.02</v>
       </c>
       <c r="L36" t="n">
-        <v>110.95</v>
+        <v>440.81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:33:57</t>
+          <t>07:47:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.68</v>
+        <v>3.94</v>
       </c>
       <c r="F37" t="n">
-        <v>9.82</v>
+        <v>10.21</v>
       </c>
       <c r="G37" t="n">
-        <v>292.7</v>
+        <v>289.7</v>
       </c>
       <c r="H37" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>411.67</v>
+        <v>-27.47</v>
       </c>
       <c r="K37" t="n">
-        <v>-93.69</v>
+        <v>439.2</v>
       </c>
       <c r="L37" t="n">
-        <v>422.2</v>
+        <v>440.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:38:43</t>
+          <t>07:51:45</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.19</v>
+        <v>4.03</v>
       </c>
       <c r="F38" t="n">
-        <v>9.470000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="G38" t="n">
-        <v>300.1</v>
+        <v>304.5</v>
       </c>
       <c r="H38" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-156.61</v>
+        <v>-329.85</v>
       </c>
       <c r="K38" t="n">
-        <v>198.64</v>
+        <v>77.42</v>
       </c>
       <c r="L38" t="n">
-        <v>252.95</v>
+        <v>338.82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:40:40</t>
+          <t>07:53:34</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,13 +1675,13 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.75</v>
+        <v>3.97</v>
       </c>
       <c r="F39" t="n">
-        <v>8.720000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="G39" t="n">
-        <v>299.4</v>
+        <v>279</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
@@ -1690,19 +1690,19 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-326.9</v>
+        <v>435.33</v>
       </c>
       <c r="K39" t="n">
-        <v>-383.78</v>
+        <v>-176.06</v>
       </c>
       <c r="L39" t="n">
-        <v>504.14</v>
+        <v>469.59</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:42:42</t>
+          <t>07:54:13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.81</v>
+        <v>4.74</v>
       </c>
       <c r="F40" t="n">
-        <v>9.32</v>
+        <v>9.9</v>
       </c>
       <c r="G40" t="n">
-        <v>304.5</v>
+        <v>296.1</v>
       </c>
       <c r="H40" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I40" t="n">
         <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>-280.21</v>
+        <v>59.08</v>
       </c>
       <c r="K40" t="n">
-        <v>-550.87</v>
+        <v>429.76</v>
       </c>
       <c r="L40" t="n">
-        <v>618.05</v>
+        <v>433.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:47:25</t>
+          <t>07:58:54</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.05</v>
+        <v>4.22</v>
       </c>
       <c r="F41" t="n">
-        <v>10.13</v>
+        <v>9.76</v>
       </c>
       <c r="G41" t="n">
-        <v>292.6</v>
+        <v>291.8</v>
       </c>
       <c r="H41" t="n">
-        <v>97.90000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>500.59</v>
+        <v>-45.87</v>
       </c>
       <c r="K41" t="n">
-        <v>-268.84</v>
+        <v>-529.2</v>
       </c>
       <c r="L41" t="n">
-        <v>568.21</v>
+        <v>531.1799999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:49:14</t>
+          <t>08:00:13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.78</v>
+        <v>4.25</v>
       </c>
       <c r="F42" t="n">
-        <v>9.390000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="G42" t="n">
-        <v>284.9</v>
+        <v>322.7</v>
       </c>
       <c r="H42" t="n">
-        <v>90.7</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>428.59</v>
+        <v>-297.25</v>
       </c>
       <c r="K42" t="n">
-        <v>817.15</v>
+        <v>-788.53</v>
       </c>
       <c r="L42" t="n">
-        <v>922.72</v>
+        <v>842.6900000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:49:50</t>
+          <t>08:02:18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="F43" t="n">
-        <v>9.09</v>
+        <v>9.65</v>
       </c>
       <c r="G43" t="n">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="H43" t="n">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-386.42</v>
+        <v>-154.59</v>
       </c>
       <c r="K43" t="n">
-        <v>89.39</v>
+        <v>493.51</v>
       </c>
       <c r="L43" t="n">
-        <v>396.62</v>
+        <v>517.15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:00:33</t>
+          <t>08:13:13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.32</v>
+        <v>4.06</v>
       </c>
       <c r="F44" t="n">
-        <v>9.109999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="G44" t="n">
-        <v>304.4</v>
+        <v>297.1</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-45.45</v>
+        <v>-61.46</v>
       </c>
       <c r="K44" t="n">
-        <v>-44.11</v>
+        <v>14.96</v>
       </c>
       <c r="L44" t="n">
-        <v>63.34</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:01:45</t>
+          <t>08:14:19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.26</v>
+        <v>3.69</v>
       </c>
       <c r="F45" t="n">
-        <v>9.17</v>
+        <v>9.66</v>
       </c>
       <c r="G45" t="n">
-        <v>304.1</v>
+        <v>292.5</v>
       </c>
       <c r="H45" t="n">
-        <v>98.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-72.14</v>
+        <v>-183.14</v>
       </c>
       <c r="K45" t="n">
-        <v>-214.7</v>
+        <v>26.24</v>
       </c>
       <c r="L45" t="n">
-        <v>226.5</v>
+        <v>185.01</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:03:05</t>
+          <t>08:17:06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="F46" t="n">
-        <v>9.02</v>
+        <v>9.25</v>
       </c>
       <c r="G46" t="n">
-        <v>298.6</v>
+        <v>296.1</v>
       </c>
       <c r="H46" t="n">
-        <v>94.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>150.97</v>
+        <v>33.14</v>
       </c>
       <c r="K46" t="n">
-        <v>75.44</v>
+        <v>128.57</v>
       </c>
       <c r="L46" t="n">
-        <v>168.77</v>
+        <v>132.77</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:06:56</t>
+          <t>08:22:23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="F47" t="n">
-        <v>9.140000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="G47" t="n">
-        <v>304.5</v>
+        <v>306.8</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>113.14</v>
+        <v>298.58</v>
       </c>
       <c r="K47" t="n">
-        <v>-46.06</v>
+        <v>57.08</v>
       </c>
       <c r="L47" t="n">
-        <v>122.16</v>
+        <v>303.98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:08:53</t>
+          <t>08:23:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.61</v>
+        <v>3.6</v>
       </c>
       <c r="F48" t="n">
-        <v>9.460000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>299.5</v>
+        <v>297.6</v>
       </c>
       <c r="H48" t="n">
         <v>100</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>267.34</v>
+        <v>-175.59</v>
       </c>
       <c r="K48" t="n">
-        <v>8</v>
+        <v>-125.67</v>
       </c>
       <c r="L48" t="n">
-        <v>267.46</v>
+        <v>215.93</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:10:35</t>
+          <t>08:25:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.31</v>
+        <v>4.19</v>
       </c>
       <c r="F49" t="n">
-        <v>10.38</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>308.5</v>
+        <v>301.4</v>
       </c>
       <c r="H49" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>195.01</v>
+        <v>6.98</v>
       </c>
       <c r="K49" t="n">
-        <v>91.77</v>
+        <v>50.21</v>
       </c>
       <c r="L49" t="n">
-        <v>215.53</v>
+        <v>50.69</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:14:48</t>
+          <t>08:31:45</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,13 +2137,13 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.16</v>
+        <v>4.21</v>
       </c>
       <c r="F50" t="n">
-        <v>9.869999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="G50" t="n">
-        <v>309.5</v>
+        <v>300.2</v>
       </c>
       <c r="H50" t="n">
         <v>100</v>
@@ -2152,19 +2152,19 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-73.5</v>
+        <v>-48.52</v>
       </c>
       <c r="K50" t="n">
-        <v>-139.6</v>
+        <v>101.22</v>
       </c>
       <c r="L50" t="n">
-        <v>157.76</v>
+        <v>112.25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:16:05</t>
+          <t>08:33:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.6</v>
+        <v>4.83</v>
       </c>
       <c r="F51" t="n">
-        <v>9.5</v>
+        <v>10.44</v>
       </c>
       <c r="G51" t="n">
-        <v>295.1</v>
+        <v>300.6</v>
       </c>
       <c r="H51" t="n">
         <v>100</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-49.37</v>
+        <v>72.64</v>
       </c>
       <c r="K51" t="n">
-        <v>439.65</v>
+        <v>-241.84</v>
       </c>
       <c r="L51" t="n">
-        <v>442.41</v>
+        <v>252.51</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:18:24</t>
+          <t>08:36:17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.03</v>
+        <v>4.06</v>
       </c>
       <c r="F52" t="n">
-        <v>9.470000000000001</v>
+        <v>10</v>
       </c>
       <c r="G52" t="n">
-        <v>305.3</v>
+        <v>302.4</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>269.03</v>
+        <v>-106.94</v>
       </c>
       <c r="K52" t="n">
-        <v>116</v>
+        <v>707.91</v>
       </c>
       <c r="L52" t="n">
-        <v>292.97</v>
+        <v>715.9400000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:23:58</t>
+          <t>08:40:57</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.19</v>
+        <v>4.3</v>
       </c>
       <c r="F53" t="n">
-        <v>8.85</v>
+        <v>9.35</v>
       </c>
       <c r="G53" t="n">
-        <v>292.9</v>
+        <v>307.3</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>142.86</v>
+        <v>-79.38</v>
       </c>
       <c r="K53" t="n">
-        <v>-96.73</v>
+        <v>346.16</v>
       </c>
       <c r="L53" t="n">
-        <v>172.53</v>
+        <v>355.15</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:25:14</t>
+          <t>08:42:06</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.36</v>
+        <v>3.93</v>
       </c>
       <c r="F54" t="n">
-        <v>10.31</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>297.3</v>
+        <v>304.6</v>
       </c>
       <c r="H54" t="n">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-29.05</v>
+        <v>215.58</v>
       </c>
       <c r="K54" t="n">
-        <v>-172.8</v>
+        <v>-255.54</v>
       </c>
       <c r="L54" t="n">
-        <v>175.22</v>
+        <v>334.33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:26:48</t>
+          <t>08:43:07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.49</v>
+        <v>4.03</v>
       </c>
       <c r="F55" t="n">
-        <v>10.07</v>
+        <v>9.75</v>
       </c>
       <c r="G55" t="n">
-        <v>306.5</v>
+        <v>310.2</v>
       </c>
       <c r="H55" t="n">
-        <v>91.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>445.28</v>
+        <v>361.1</v>
       </c>
       <c r="K55" t="n">
-        <v>558.96</v>
+        <v>926.59</v>
       </c>
       <c r="L55" t="n">
-        <v>714.64</v>
+        <v>994.47</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:31:22</t>
+          <t>08:47:47</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.49</v>
+        <v>3.69</v>
       </c>
       <c r="F56" t="n">
-        <v>8.779999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="G56" t="n">
-        <v>303.3</v>
+        <v>293</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>638.72</v>
+        <v>-572.25</v>
       </c>
       <c r="K56" t="n">
-        <v>87.68000000000001</v>
+        <v>167.9</v>
       </c>
       <c r="L56" t="n">
-        <v>644.71</v>
+        <v>596.37</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:32:29</t>
+          <t>08:50:13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.13</v>
+        <v>4.23</v>
       </c>
       <c r="F57" t="n">
-        <v>10.05</v>
+        <v>10.35</v>
       </c>
       <c r="G57" t="n">
-        <v>309.9</v>
+        <v>296.8</v>
       </c>
       <c r="H57" t="n">
-        <v>96.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>154.39</v>
+        <v>-928.65</v>
       </c>
       <c r="K57" t="n">
-        <v>183.84</v>
+        <v>-411.87</v>
       </c>
       <c r="L57" t="n">
-        <v>240.07</v>
+        <v>1015.89</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:34:05</t>
+          <t>08:52:22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.46</v>
+        <v>3.7</v>
       </c>
       <c r="F58" t="n">
-        <v>9.75</v>
+        <v>10.3</v>
       </c>
       <c r="G58" t="n">
-        <v>302.3</v>
+        <v>296.1</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>328.33</v>
+        <v>271.49</v>
       </c>
       <c r="K58" t="n">
-        <v>-635.75</v>
+        <v>-410.69</v>
       </c>
       <c r="L58" t="n">
-        <v>715.53</v>
+        <v>492.32</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:45:39</t>
+          <t>09:03:46</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="F59" t="n">
-        <v>9.279999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="G59" t="n">
-        <v>308.1</v>
+        <v>298.4</v>
       </c>
       <c r="H59" t="n">
-        <v>92.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>148</v>
+        <v>-136.38</v>
       </c>
       <c r="K59" t="n">
-        <v>-111.79</v>
+        <v>-85.43000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>185.48</v>
+        <v>160.93</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:47:00</t>
+          <t>09:05:09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.9</v>
+        <v>4.22</v>
       </c>
       <c r="F60" t="n">
-        <v>8.83</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>289.2</v>
+        <v>308.4</v>
       </c>
       <c r="H60" t="n">
         <v>100</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-236.45</v>
+        <v>77.67</v>
       </c>
       <c r="K60" t="n">
-        <v>-87.38</v>
+        <v>118.45</v>
       </c>
       <c r="L60" t="n">
-        <v>252.07</v>
+        <v>141.64</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:47:59</t>
+          <t>09:06:41</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="F61" t="n">
-        <v>9.23</v>
+        <v>9.15</v>
       </c>
       <c r="G61" t="n">
-        <v>294.3</v>
+        <v>314</v>
       </c>
       <c r="H61" t="n">
         <v>100</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.2</v>
+        <v>-5.1</v>
       </c>
       <c r="K61" t="n">
-        <v>155.72</v>
+        <v>-36.35</v>
       </c>
       <c r="L61" t="n">
-        <v>156.66</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:51:59</t>
+          <t>09:11:21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.67</v>
+        <v>4.1</v>
       </c>
       <c r="F62" t="n">
-        <v>9.109999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>300.5</v>
+        <v>293.7</v>
       </c>
       <c r="H62" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>212.7</v>
+        <v>-208.01</v>
       </c>
       <c r="K62" t="n">
-        <v>-47.79</v>
+        <v>46.21</v>
       </c>
       <c r="L62" t="n">
-        <v>218.01</v>
+        <v>213.08</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:54:01</t>
+          <t>09:12:57</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.17</v>
+        <v>4.35</v>
       </c>
       <c r="F63" t="n">
-        <v>9.109999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="G63" t="n">
-        <v>299.1</v>
+        <v>303.7</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>277.55</v>
+        <v>315.44</v>
       </c>
       <c r="K63" t="n">
-        <v>-84.41</v>
+        <v>-183.28</v>
       </c>
       <c r="L63" t="n">
-        <v>290.11</v>
+        <v>364.82</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:56:35</t>
+          <t>09:14:15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.33</v>
+        <v>3.99</v>
       </c>
       <c r="F64" t="n">
-        <v>10.01</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>284.6</v>
+        <v>292.6</v>
       </c>
       <c r="H64" t="n">
-        <v>95.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>45.72</v>
+        <v>-145.37</v>
       </c>
       <c r="K64" t="n">
-        <v>-169.12</v>
+        <v>-234.75</v>
       </c>
       <c r="L64" t="n">
-        <v>175.19</v>
+        <v>276.12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:01:45</t>
+          <t>09:18:42</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.21</v>
+        <v>4.61</v>
       </c>
       <c r="F65" t="n">
-        <v>8.93</v>
+        <v>9.48</v>
       </c>
       <c r="G65" t="n">
-        <v>297</v>
+        <v>293.8</v>
       </c>
       <c r="H65" t="n">
-        <v>97.2</v>
+        <v>93.7</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-67.28</v>
+        <v>-332.76</v>
       </c>
       <c r="K65" t="n">
-        <v>-9.609999999999999</v>
+        <v>-11.3</v>
       </c>
       <c r="L65" t="n">
-        <v>67.97</v>
+        <v>332.95</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:04:03</t>
+          <t>09:19:47</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,13 +2809,13 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.07</v>
+        <v>4.53</v>
       </c>
       <c r="F66" t="n">
-        <v>9.69</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>296.1</v>
+        <v>290.3</v>
       </c>
       <c r="H66" t="n">
         <v>100</v>
@@ -2824,19 +2824,19 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>130.12</v>
+        <v>301.1</v>
       </c>
       <c r="K66" t="n">
-        <v>-420.6</v>
+        <v>181.15</v>
       </c>
       <c r="L66" t="n">
-        <v>440.26</v>
+        <v>351.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:05:14</t>
+          <t>09:22:06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.41</v>
+        <v>3.61</v>
       </c>
       <c r="F67" t="n">
-        <v>8.91</v>
+        <v>9.82</v>
       </c>
       <c r="G67" t="n">
-        <v>294.3</v>
+        <v>303.6</v>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>303.61</v>
+        <v>-70.45</v>
       </c>
       <c r="K67" t="n">
-        <v>-487.54</v>
+        <v>-439.16</v>
       </c>
       <c r="L67" t="n">
-        <v>574.35</v>
+        <v>444.78</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:09:22</t>
+          <t>09:26:16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.9</v>
+        <v>4.55</v>
       </c>
       <c r="F68" t="n">
-        <v>10.06</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>296.9</v>
+        <v>307.1</v>
       </c>
       <c r="H68" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>133.36</v>
+        <v>-541.53</v>
       </c>
       <c r="K68" t="n">
-        <v>-274.29</v>
+        <v>762.21</v>
       </c>
       <c r="L68" t="n">
-        <v>304.99</v>
+        <v>934.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:10:23</t>
+          <t>09:28:11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.55</v>
+        <v>4.18</v>
       </c>
       <c r="F69" t="n">
-        <v>9.43</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>301.5</v>
+        <v>308.6</v>
       </c>
       <c r="H69" t="n">
         <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>-89.29000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>-11.49</v>
+        <v>298.5</v>
       </c>
       <c r="L69" t="n">
-        <v>90.03</v>
+        <v>312.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:11:13</t>
+          <t>09:30:02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.51</v>
+        <v>5.05</v>
       </c>
       <c r="F70" t="n">
-        <v>9.529999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>298.7</v>
+        <v>303.4</v>
       </c>
       <c r="H70" t="n">
-        <v>95.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-371.17</v>
+        <v>-245.99</v>
       </c>
       <c r="K70" t="n">
-        <v>78.79000000000001</v>
+        <v>535.52</v>
       </c>
       <c r="L70" t="n">
-        <v>379.44</v>
+        <v>589.3099999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:14:49</t>
+          <t>09:34:30</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="F71" t="n">
-        <v>9.140000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>296.8</v>
+        <v>297.4</v>
       </c>
       <c r="H71" t="n">
-        <v>97.7</v>
+        <v>98</v>
       </c>
       <c r="I71" t="n">
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-431.95</v>
+        <v>-1407.52</v>
       </c>
       <c r="K71" t="n">
-        <v>-544.27</v>
+        <v>-156.3</v>
       </c>
       <c r="L71" t="n">
-        <v>694.85</v>
+        <v>1416.17</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:15:43</t>
+          <t>09:36:11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.83</v>
+        <v>4.49</v>
       </c>
       <c r="F72" t="n">
-        <v>9.119999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="G72" t="n">
-        <v>296.6</v>
+        <v>299.9</v>
       </c>
       <c r="H72" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I72" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-295.32</v>
+        <v>334.59</v>
       </c>
       <c r="K72" t="n">
-        <v>289.29</v>
+        <v>205.27</v>
       </c>
       <c r="L72" t="n">
-        <v>413.41</v>
+        <v>392.54</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:16:55</t>
+          <t>09:37:55</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.06</v>
+        <v>4.8</v>
       </c>
       <c r="F73" t="n">
-        <v>9.31</v>
+        <v>9.66</v>
       </c>
       <c r="G73" t="n">
-        <v>308.2</v>
+        <v>297.5</v>
       </c>
       <c r="H73" t="n">
         <v>100</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-142.12</v>
+        <v>-291.06</v>
       </c>
       <c r="K73" t="n">
-        <v>-631.52</v>
+        <v>320.51</v>
       </c>
       <c r="L73" t="n">
-        <v>647.3099999999999</v>
+        <v>432.95</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:25:47</t>
+          <t>09:46:54</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.38</v>
+        <v>4.79</v>
       </c>
       <c r="F74" t="n">
-        <v>9.630000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>304.9</v>
+        <v>280.7</v>
       </c>
       <c r="H74" t="n">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>-207.2</v>
+        <v>270.03</v>
       </c>
       <c r="K74" t="n">
-        <v>-74.59999999999999</v>
+        <v>33.12</v>
       </c>
       <c r="L74" t="n">
-        <v>220.22</v>
+        <v>272.06</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:26:43</t>
+          <t>09:48:10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.62</v>
+        <v>4.72</v>
       </c>
       <c r="F75" t="n">
-        <v>9.83</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>313.8</v>
+        <v>299.5</v>
       </c>
       <c r="H75" t="n">
-        <v>92.7</v>
+        <v>100</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-24.08</v>
+        <v>513.66</v>
       </c>
       <c r="K75" t="n">
-        <v>-16.25</v>
+        <v>159.83</v>
       </c>
       <c r="L75" t="n">
-        <v>29.05</v>
+        <v>537.95</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:29:12</t>
+          <t>09:49:53</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.22</v>
+        <v>4.74</v>
       </c>
       <c r="F76" t="n">
-        <v>9.69</v>
+        <v>8.68</v>
       </c>
       <c r="G76" t="n">
-        <v>296.1</v>
+        <v>298.3</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
       </c>
       <c r="I76" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>66.02</v>
+        <v>197.61</v>
       </c>
       <c r="K76" t="n">
-        <v>118.85</v>
+        <v>-241.21</v>
       </c>
       <c r="L76" t="n">
-        <v>135.96</v>
+        <v>311.82</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:34:22</t>
+          <t>09:54:26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.49</v>
+        <v>4.38</v>
       </c>
       <c r="F77" t="n">
-        <v>9.32</v>
+        <v>9.75</v>
       </c>
       <c r="G77" t="n">
-        <v>295.2</v>
+        <v>305</v>
       </c>
       <c r="H77" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>-88.16</v>
+        <v>32.49</v>
       </c>
       <c r="K77" t="n">
-        <v>178.66</v>
+        <v>-244.49</v>
       </c>
       <c r="L77" t="n">
-        <v>199.22</v>
+        <v>246.64</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:35:51</t>
+          <t>09:56:45</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.58</v>
+        <v>3.77</v>
       </c>
       <c r="F78" t="n">
-        <v>9.24</v>
+        <v>10.13</v>
       </c>
       <c r="G78" t="n">
-        <v>304.4</v>
+        <v>309.5</v>
       </c>
       <c r="H78" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I78" t="n">
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-175.34</v>
+        <v>-200.19</v>
       </c>
       <c r="K78" t="n">
-        <v>-151.91</v>
+        <v>-62.5</v>
       </c>
       <c r="L78" t="n">
-        <v>231.99</v>
+        <v>209.71</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:37:59</t>
+          <t>09:58:31</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.41</v>
+        <v>4.59</v>
       </c>
       <c r="F79" t="n">
-        <v>9.25</v>
+        <v>9.15</v>
       </c>
       <c r="G79" t="n">
-        <v>288.8</v>
+        <v>296.7</v>
       </c>
       <c r="H79" t="n">
         <v>100</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.63</v>
+        <v>-260.29</v>
       </c>
       <c r="K79" t="n">
-        <v>-89.76000000000001</v>
+        <v>-48.18</v>
       </c>
       <c r="L79" t="n">
-        <v>89.8</v>
+        <v>264.71</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:43:09</t>
+          <t>10:02:41</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.95</v>
+        <v>4.42</v>
       </c>
       <c r="F80" t="n">
-        <v>8.880000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>306.5</v>
+        <v>280.3</v>
       </c>
       <c r="H80" t="n">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>9.539999999999999</v>
+        <v>-49.09</v>
       </c>
       <c r="K80" t="n">
-        <v>-39.25</v>
+        <v>-51.25</v>
       </c>
       <c r="L80" t="n">
-        <v>40.39</v>
+        <v>70.97</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:45:06</t>
+          <t>10:04:31</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.96</v>
+        <v>4.37</v>
       </c>
       <c r="F81" t="n">
-        <v>9.890000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="G81" t="n">
-        <v>292.5</v>
+        <v>305.3</v>
       </c>
       <c r="H81" t="n">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-40.87</v>
+        <v>156.67</v>
       </c>
       <c r="K81" t="n">
-        <v>147.42</v>
+        <v>319.73</v>
       </c>
       <c r="L81" t="n">
-        <v>152.98</v>
+        <v>356.05</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:47:22</t>
+          <t>10:05:57</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="F82" t="n">
-        <v>9.94</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>298.5</v>
+        <v>286.5</v>
       </c>
       <c r="H82" t="n">
         <v>100</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-242.36</v>
+        <v>-361.44</v>
       </c>
       <c r="K82" t="n">
-        <v>-143.5</v>
+        <v>-117.39</v>
       </c>
       <c r="L82" t="n">
-        <v>281.65</v>
+        <v>380.02</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:53:24</t>
+          <t>10:11:09</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.24</v>
+        <v>4.42</v>
       </c>
       <c r="F83" t="n">
-        <v>10.05</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G83" t="n">
-        <v>311.2</v>
+        <v>307.6</v>
       </c>
       <c r="H83" t="n">
-        <v>99.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-35.44</v>
+        <v>-364.18</v>
       </c>
       <c r="K83" t="n">
-        <v>70.05</v>
+        <v>-566.42</v>
       </c>
       <c r="L83" t="n">
-        <v>78.51000000000001</v>
+        <v>673.39</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:55:18</t>
+          <t>10:12:18</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.33</v>
+        <v>4.57</v>
       </c>
       <c r="F84" t="n">
-        <v>9.19</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>304.9</v>
+        <v>295.5</v>
       </c>
       <c r="H84" t="n">
-        <v>94.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="I84" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>151.57</v>
+        <v>-702.42</v>
       </c>
       <c r="K84" t="n">
-        <v>491.76</v>
+        <v>-518.26</v>
       </c>
       <c r="L84" t="n">
-        <v>514.59</v>
+        <v>872.92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:57:48</t>
+          <t>10:13:18</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.46</v>
+        <v>4.82</v>
       </c>
       <c r="F85" t="n">
-        <v>8.74</v>
+        <v>8.57</v>
       </c>
       <c r="G85" t="n">
-        <v>291.2</v>
+        <v>304.7</v>
       </c>
       <c r="H85" t="n">
-        <v>97.3</v>
+        <v>97.5</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-232.05</v>
+        <v>-165.88</v>
       </c>
       <c r="K85" t="n">
-        <v>-318.49</v>
+        <v>641.38</v>
       </c>
       <c r="L85" t="n">
-        <v>394.06</v>
+        <v>662.48</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:03:00</t>
+          <t>10:18:41</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.57</v>
+        <v>4.36</v>
       </c>
       <c r="F86" t="n">
-        <v>9.960000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="G86" t="n">
-        <v>305.8</v>
+        <v>316.7</v>
       </c>
       <c r="H86" t="n">
         <v>100</v>
       </c>
       <c r="I86" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>61.4</v>
+        <v>795.46</v>
       </c>
       <c r="K86" t="n">
-        <v>-147.94</v>
+        <v>-648.77</v>
       </c>
       <c r="L86" t="n">
-        <v>160.18</v>
+        <v>1026.48</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:04:27</t>
+          <t>10:20:31</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.36</v>
+        <v>4.81</v>
       </c>
       <c r="F87" t="n">
-        <v>9.24</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>294.5</v>
+        <v>292.1</v>
       </c>
       <c r="H87" t="n">
-        <v>99.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-324.85</v>
+        <v>435.22</v>
       </c>
       <c r="K87" t="n">
-        <v>323.44</v>
+        <v>-22.79</v>
       </c>
       <c r="L87" t="n">
-        <v>458.41</v>
+        <v>435.82</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:05:22</t>
+          <t>10:22:56</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.29</v>
+        <v>4.53</v>
       </c>
       <c r="F88" t="n">
-        <v>9.34</v>
+        <v>9.83</v>
       </c>
       <c r="G88" t="n">
-        <v>295.5</v>
+        <v>305.7</v>
       </c>
       <c r="H88" t="n">
-        <v>100</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-458.96</v>
+        <v>-332.14</v>
       </c>
       <c r="K88" t="n">
-        <v>218.98</v>
+        <v>-195.48</v>
       </c>
       <c r="L88" t="n">
-        <v>508.53</v>
+        <v>385.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-04.xlsx
+++ b/output/2024-04-04.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>75.65000000000001</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>110.74</v>
+        <v>122</v>
       </c>
       <c r="L14" t="n">
-        <v>134.11</v>
+        <v>147.75</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>93.59999999999999</v>
+        <v>115.82</v>
       </c>
       <c r="K15" t="n">
-        <v>126.08</v>
+        <v>156</v>
       </c>
       <c r="L15" t="n">
-        <v>157.02</v>
+        <v>194.3</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>63.27</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>96.81999999999999</v>
+        <v>141.23</v>
       </c>
       <c r="L16" t="n">
-        <v>115.66</v>
+        <v>168.71</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>137.89</v>
+        <v>161.27</v>
       </c>
       <c r="K17" t="n">
-        <v>-243.84</v>
+        <v>-285.2</v>
       </c>
       <c r="L17" t="n">
-        <v>280.13</v>
+        <v>327.64</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>-112.38</v>
+        <v>-164.11</v>
       </c>
       <c r="K18" t="n">
-        <v>40.65</v>
+        <v>59.36</v>
       </c>
       <c r="L18" t="n">
-        <v>119.51</v>
+        <v>174.51</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-237.05</v>
+        <v>-283.4</v>
       </c>
       <c r="K19" t="n">
-        <v>111.73</v>
+        <v>133.57</v>
       </c>
       <c r="L19" t="n">
-        <v>262.06</v>
+        <v>313.3</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>157.89</v>
+        <v>262.44</v>
       </c>
       <c r="K20" t="n">
-        <v>-84.79000000000001</v>
+        <v>-140.93</v>
       </c>
       <c r="L20" t="n">
-        <v>179.22</v>
+        <v>297.89</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>143.86</v>
+        <v>166.88</v>
       </c>
       <c r="K21" t="n">
-        <v>412.73</v>
+        <v>478.78</v>
       </c>
       <c r="L21" t="n">
-        <v>437.08</v>
+        <v>507.03</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-505.82</v>
+        <v>-603</v>
       </c>
       <c r="K22" t="n">
-        <v>81.11</v>
+        <v>96.69</v>
       </c>
       <c r="L22" t="n">
-        <v>512.28</v>
+        <v>610.71</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-639.83</v>
+        <v>-769.91</v>
       </c>
       <c r="K23" t="n">
-        <v>-53.38</v>
+        <v>-64.23</v>
       </c>
       <c r="L23" t="n">
-        <v>642.05</v>
+        <v>772.58</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>285.81</v>
+        <v>405.12</v>
       </c>
       <c r="K24" t="n">
-        <v>198.62</v>
+        <v>281.54</v>
       </c>
       <c r="L24" t="n">
-        <v>348.05</v>
+        <v>493.34</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-294.14</v>
+        <v>-449.5</v>
       </c>
       <c r="K25" t="n">
-        <v>190.12</v>
+        <v>290.53</v>
       </c>
       <c r="L25" t="n">
-        <v>350.23</v>
+        <v>535.22</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-209.15</v>
+        <v>-284.59</v>
       </c>
       <c r="K26" t="n">
-        <v>-591.59</v>
+        <v>-804.95</v>
       </c>
       <c r="L26" t="n">
-        <v>627.47</v>
+        <v>853.77</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-492.48</v>
+        <v>-710.36</v>
       </c>
       <c r="K27" t="n">
-        <v>401.22</v>
+        <v>578.73</v>
       </c>
       <c r="L27" t="n">
-        <v>635.23</v>
+        <v>916.26</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>606.28</v>
+        <v>864.45</v>
       </c>
       <c r="K28" t="n">
-        <v>18.9</v>
+        <v>26.95</v>
       </c>
       <c r="L28" t="n">
-        <v>606.5700000000001</v>
+        <v>864.87</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-55.52</v>
+        <v>-57.54</v>
       </c>
       <c r="K29" t="n">
-        <v>-247.14</v>
+        <v>-256.12</v>
       </c>
       <c r="L29" t="n">
-        <v>253.3</v>
+        <v>262.5</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-255.12</v>
+        <v>-265.98</v>
       </c>
       <c r="K30" t="n">
-        <v>-90.19</v>
+        <v>-94.03</v>
       </c>
       <c r="L30" t="n">
-        <v>270.6</v>
+        <v>282.11</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-123.46</v>
+        <v>-190.57</v>
       </c>
       <c r="K31" t="n">
-        <v>-47.68</v>
+        <v>-73.59999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>132.35</v>
+        <v>204.29</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>148.38</v>
+        <v>218.94</v>
       </c>
       <c r="K32" t="n">
-        <v>-41.39</v>
+        <v>-61.08</v>
       </c>
       <c r="L32" t="n">
-        <v>154.04</v>
+        <v>227.3</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>113.76</v>
+        <v>220.16</v>
       </c>
       <c r="K33" t="n">
-        <v>48.33</v>
+        <v>93.53</v>
       </c>
       <c r="L33" t="n">
-        <v>123.6</v>
+        <v>239.2</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-150.43</v>
+        <v>-197.12</v>
       </c>
       <c r="K34" t="n">
-        <v>-146.38</v>
+        <v>-191.8</v>
       </c>
       <c r="L34" t="n">
-        <v>209.89</v>
+        <v>275.04</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>84.18000000000001</v>
+        <v>199.54</v>
       </c>
       <c r="K35" t="n">
-        <v>-13.81</v>
+        <v>-32.73</v>
       </c>
       <c r="L35" t="n">
-        <v>85.31</v>
+        <v>202.2</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-347.65</v>
+        <v>-393.16</v>
       </c>
       <c r="K36" t="n">
-        <v>271.02</v>
+        <v>306.49</v>
       </c>
       <c r="L36" t="n">
-        <v>440.81</v>
+        <v>498.51</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-27.47</v>
+        <v>-35.64</v>
       </c>
       <c r="K37" t="n">
-        <v>439.2</v>
+        <v>569.87</v>
       </c>
       <c r="L37" t="n">
-        <v>440.06</v>
+        <v>570.99</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-329.85</v>
+        <v>-515.21</v>
       </c>
       <c r="K38" t="n">
-        <v>77.42</v>
+        <v>120.93</v>
       </c>
       <c r="L38" t="n">
-        <v>338.82</v>
+        <v>529.21</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>435.33</v>
+        <v>657.29</v>
       </c>
       <c r="K39" t="n">
-        <v>-176.06</v>
+        <v>-265.83</v>
       </c>
       <c r="L39" t="n">
-        <v>469.59</v>
+        <v>709.01</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>59.08</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>429.76</v>
+        <v>709.15</v>
       </c>
       <c r="L40" t="n">
-        <v>433.8</v>
+        <v>715.8200000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-45.87</v>
+        <v>-74.31999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>-529.2</v>
+        <v>-857.55</v>
       </c>
       <c r="L41" t="n">
-        <v>531.1799999999999</v>
+        <v>860.77</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-297.25</v>
+        <v>-413.83</v>
       </c>
       <c r="K42" t="n">
-        <v>-788.53</v>
+        <v>-1097.79</v>
       </c>
       <c r="L42" t="n">
-        <v>842.6900000000001</v>
+        <v>1173.2</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-154.59</v>
+        <v>-235.78</v>
       </c>
       <c r="K43" t="n">
-        <v>493.51</v>
+        <v>752.6900000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>517.15</v>
+        <v>788.76</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-61.46</v>
+        <v>-124.7</v>
       </c>
       <c r="K44" t="n">
-        <v>14.96</v>
+        <v>30.35</v>
       </c>
       <c r="L44" t="n">
-        <v>63.25</v>
+        <v>128.34</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-183.14</v>
+        <v>-227.11</v>
       </c>
       <c r="K45" t="n">
-        <v>26.24</v>
+        <v>32.53</v>
       </c>
       <c r="L45" t="n">
-        <v>185.01</v>
+        <v>229.43</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>33.14</v>
+        <v>53.88</v>
       </c>
       <c r="K46" t="n">
-        <v>128.57</v>
+        <v>209.04</v>
       </c>
       <c r="L46" t="n">
-        <v>132.77</v>
+        <v>215.87</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>298.58</v>
+        <v>377.77</v>
       </c>
       <c r="K47" t="n">
-        <v>57.08</v>
+        <v>72.22</v>
       </c>
       <c r="L47" t="n">
-        <v>303.98</v>
+        <v>384.62</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-175.59</v>
+        <v>-203.92</v>
       </c>
       <c r="K48" t="n">
-        <v>-125.67</v>
+        <v>-145.94</v>
       </c>
       <c r="L48" t="n">
-        <v>215.93</v>
+        <v>250.76</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>6.98</v>
+        <v>20.08</v>
       </c>
       <c r="K49" t="n">
-        <v>50.21</v>
+        <v>144.44</v>
       </c>
       <c r="L49" t="n">
-        <v>50.69</v>
+        <v>145.83</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-48.52</v>
+        <v>-123.7</v>
       </c>
       <c r="K50" t="n">
-        <v>101.22</v>
+        <v>258.08</v>
       </c>
       <c r="L50" t="n">
-        <v>112.25</v>
+        <v>286.2</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>72.64</v>
+        <v>123.85</v>
       </c>
       <c r="K51" t="n">
-        <v>-241.84</v>
+        <v>-412.32</v>
       </c>
       <c r="L51" t="n">
-        <v>252.51</v>
+        <v>430.52</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>-106.94</v>
+        <v>-121.9</v>
       </c>
       <c r="K52" t="n">
-        <v>707.91</v>
+        <v>806.97</v>
       </c>
       <c r="L52" t="n">
-        <v>715.9400000000001</v>
+        <v>816.12</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-79.38</v>
+        <v>-140.54</v>
       </c>
       <c r="K53" t="n">
-        <v>346.16</v>
+        <v>612.85</v>
       </c>
       <c r="L53" t="n">
-        <v>355.15</v>
+        <v>628.76</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>215.58</v>
+        <v>368.23</v>
       </c>
       <c r="K54" t="n">
-        <v>-255.54</v>
+        <v>-436.48</v>
       </c>
       <c r="L54" t="n">
-        <v>334.33</v>
+        <v>571.0599999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>361.1</v>
+        <v>411.11</v>
       </c>
       <c r="K55" t="n">
-        <v>926.59</v>
+        <v>1054.9</v>
       </c>
       <c r="L55" t="n">
-        <v>994.47</v>
+        <v>1132.18</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-572.25</v>
+        <v>-769.9</v>
       </c>
       <c r="K56" t="n">
-        <v>167.9</v>
+        <v>225.89</v>
       </c>
       <c r="L56" t="n">
-        <v>596.37</v>
+        <v>802.36</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-928.65</v>
+        <v>-1199.19</v>
       </c>
       <c r="K57" t="n">
-        <v>-411.87</v>
+        <v>-531.86</v>
       </c>
       <c r="L57" t="n">
-        <v>1015.89</v>
+        <v>1311.84</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>271.49</v>
+        <v>444.47</v>
       </c>
       <c r="K58" t="n">
-        <v>-410.69</v>
+        <v>-672.35</v>
       </c>
       <c r="L58" t="n">
-        <v>492.32</v>
+        <v>805.98</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-136.38</v>
+        <v>-178.67</v>
       </c>
       <c r="K59" t="n">
-        <v>-85.43000000000001</v>
+        <v>-111.92</v>
       </c>
       <c r="L59" t="n">
-        <v>160.93</v>
+        <v>210.82</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>77.67</v>
+        <v>118.7</v>
       </c>
       <c r="K60" t="n">
-        <v>118.45</v>
+        <v>181.03</v>
       </c>
       <c r="L60" t="n">
-        <v>141.64</v>
+        <v>216.48</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.1</v>
+        <v>-17.07</v>
       </c>
       <c r="K61" t="n">
-        <v>-36.35</v>
+        <v>-121.73</v>
       </c>
       <c r="L61" t="n">
-        <v>36.7</v>
+        <v>122.92</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-208.01</v>
+        <v>-260.07</v>
       </c>
       <c r="K62" t="n">
-        <v>46.21</v>
+        <v>57.78</v>
       </c>
       <c r="L62" t="n">
-        <v>213.08</v>
+        <v>266.42</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>315.44</v>
+        <v>389.63</v>
       </c>
       <c r="K63" t="n">
-        <v>-183.28</v>
+        <v>-226.38</v>
       </c>
       <c r="L63" t="n">
-        <v>364.82</v>
+        <v>450.63</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-145.37</v>
+        <v>-163.57</v>
       </c>
       <c r="K64" t="n">
-        <v>-234.75</v>
+        <v>-264.15</v>
       </c>
       <c r="L64" t="n">
-        <v>276.12</v>
+        <v>310.69</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-332.76</v>
+        <v>-480.06</v>
       </c>
       <c r="K65" t="n">
-        <v>-11.3</v>
+        <v>-16.3</v>
       </c>
       <c r="L65" t="n">
-        <v>332.95</v>
+        <v>480.34</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>301.1</v>
+        <v>453.43</v>
       </c>
       <c r="K66" t="n">
-        <v>181.15</v>
+        <v>272.8</v>
       </c>
       <c r="L66" t="n">
-        <v>351.4</v>
+        <v>529.17</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-70.45</v>
+        <v>-85.13</v>
       </c>
       <c r="K67" t="n">
-        <v>-439.16</v>
+        <v>-530.6799999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>444.78</v>
+        <v>537.46</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-541.53</v>
+        <v>-706.65</v>
       </c>
       <c r="K68" t="n">
-        <v>762.21</v>
+        <v>994.62</v>
       </c>
       <c r="L68" t="n">
-        <v>934.99</v>
+        <v>1220.1</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>91.15000000000001</v>
+        <v>150.77</v>
       </c>
       <c r="K69" t="n">
-        <v>298.5</v>
+        <v>493.72</v>
       </c>
       <c r="L69" t="n">
-        <v>312.1</v>
+        <v>516.23</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-245.99</v>
+        <v>-365.4</v>
       </c>
       <c r="K70" t="n">
-        <v>535.52</v>
+        <v>795.46</v>
       </c>
       <c r="L70" t="n">
-        <v>589.3099999999999</v>
+        <v>875.37</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-1407.52</v>
+        <v>-1770.64</v>
       </c>
       <c r="K71" t="n">
-        <v>-156.3</v>
+        <v>-196.62</v>
       </c>
       <c r="L71" t="n">
-        <v>1416.17</v>
+        <v>1781.53</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>334.59</v>
+        <v>602.3099999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>205.27</v>
+        <v>369.51</v>
       </c>
       <c r="L72" t="n">
-        <v>392.54</v>
+        <v>706.63</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-291.06</v>
+        <v>-587.54</v>
       </c>
       <c r="K73" t="n">
-        <v>320.51</v>
+        <v>646.99</v>
       </c>
       <c r="L73" t="n">
-        <v>432.95</v>
+        <v>873.96</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>270.03</v>
+        <v>333.56</v>
       </c>
       <c r="K74" t="n">
-        <v>33.12</v>
+        <v>40.92</v>
       </c>
       <c r="L74" t="n">
-        <v>272.06</v>
+        <v>336.06</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>513.66</v>
+        <v>562.65</v>
       </c>
       <c r="K75" t="n">
-        <v>159.83</v>
+        <v>175.08</v>
       </c>
       <c r="L75" t="n">
-        <v>537.95</v>
+        <v>589.26</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>197.61</v>
+        <v>257.33</v>
       </c>
       <c r="K76" t="n">
-        <v>-241.21</v>
+        <v>-314.11</v>
       </c>
       <c r="L76" t="n">
-        <v>311.82</v>
+        <v>406.06</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>32.49</v>
+        <v>43.88</v>
       </c>
       <c r="K77" t="n">
-        <v>-244.49</v>
+        <v>-330.16</v>
       </c>
       <c r="L77" t="n">
-        <v>246.64</v>
+        <v>333.06</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-200.19</v>
+        <v>-269.71</v>
       </c>
       <c r="K78" t="n">
-        <v>-62.5</v>
+        <v>-84.2</v>
       </c>
       <c r="L78" t="n">
-        <v>209.71</v>
+        <v>282.55</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-260.29</v>
+        <v>-360.57</v>
       </c>
       <c r="K79" t="n">
-        <v>-48.18</v>
+        <v>-66.73999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>264.71</v>
+        <v>366.7</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-49.09</v>
+        <v>-180.81</v>
       </c>
       <c r="K80" t="n">
-        <v>-51.25</v>
+        <v>-188.77</v>
       </c>
       <c r="L80" t="n">
-        <v>70.97</v>
+        <v>261.4</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>156.67</v>
+        <v>203.73</v>
       </c>
       <c r="K81" t="n">
-        <v>319.73</v>
+        <v>415.78</v>
       </c>
       <c r="L81" t="n">
-        <v>356.05</v>
+        <v>463.01</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-361.44</v>
+        <v>-489.63</v>
       </c>
       <c r="K82" t="n">
-        <v>-117.39</v>
+        <v>-159.02</v>
       </c>
       <c r="L82" t="n">
-        <v>380.02</v>
+        <v>514.8099999999999</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-364.18</v>
+        <v>-476.36</v>
       </c>
       <c r="K83" t="n">
-        <v>-566.42</v>
+        <v>-740.89</v>
       </c>
       <c r="L83" t="n">
-        <v>673.39</v>
+        <v>880.8200000000001</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-702.42</v>
+        <v>-893.95</v>
       </c>
       <c r="K84" t="n">
-        <v>-518.26</v>
+        <v>-659.5700000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>872.92</v>
+        <v>1110.93</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-165.88</v>
+        <v>-221.14</v>
       </c>
       <c r="K85" t="n">
-        <v>641.38</v>
+        <v>855.05</v>
       </c>
       <c r="L85" t="n">
-        <v>662.48</v>
+        <v>883.1900000000001</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>795.46</v>
+        <v>1038.4</v>
       </c>
       <c r="K86" t="n">
-        <v>-648.77</v>
+        <v>-846.91</v>
       </c>
       <c r="L86" t="n">
-        <v>1026.48</v>
+        <v>1339.97</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>435.22</v>
+        <v>792.99</v>
       </c>
       <c r="K87" t="n">
-        <v>-22.79</v>
+        <v>-41.53</v>
       </c>
       <c r="L87" t="n">
-        <v>435.82</v>
+        <v>794.08</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-332.14</v>
+        <v>-664.11</v>
       </c>
       <c r="K88" t="n">
-        <v>-195.48</v>
+        <v>-390.86</v>
       </c>
       <c r="L88" t="n">
-        <v>385.4</v>
+        <v>770.59</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-04.xlsx
+++ b/output/2024-04-04.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>83.34999999999999</v>
+        <v>60.01</v>
       </c>
       <c r="K14" t="n">
-        <v>122</v>
+        <v>87.83</v>
       </c>
       <c r="L14" t="n">
-        <v>147.75</v>
+        <v>106.38</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>115.82</v>
+        <v>78.91</v>
       </c>
       <c r="K15" t="n">
-        <v>156</v>
+        <v>106.29</v>
       </c>
       <c r="L15" t="n">
-        <v>194.3</v>
+        <v>132.38</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>92.29000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="K16" t="n">
-        <v>141.23</v>
+        <v>97.33</v>
       </c>
       <c r="L16" t="n">
-        <v>168.71</v>
+        <v>116.26</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>161.27</v>
+        <v>97.48</v>
       </c>
       <c r="K17" t="n">
-        <v>-285.2</v>
+        <v>-172.38</v>
       </c>
       <c r="L17" t="n">
-        <v>327.64</v>
+        <v>198.03</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>-164.11</v>
+        <v>-102.22</v>
       </c>
       <c r="K18" t="n">
-        <v>59.36</v>
+        <v>36.97</v>
       </c>
       <c r="L18" t="n">
-        <v>174.51</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-283.4</v>
+        <v>-168.48</v>
       </c>
       <c r="K19" t="n">
-        <v>133.57</v>
+        <v>79.41</v>
       </c>
       <c r="L19" t="n">
-        <v>313.3</v>
+        <v>186.26</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>262.44</v>
+        <v>137.36</v>
       </c>
       <c r="K20" t="n">
-        <v>-140.93</v>
+        <v>-73.77</v>
       </c>
       <c r="L20" t="n">
-        <v>297.89</v>
+        <v>155.92</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>166.88</v>
+        <v>94.5</v>
       </c>
       <c r="K21" t="n">
-        <v>478.78</v>
+        <v>271.11</v>
       </c>
       <c r="L21" t="n">
-        <v>507.03</v>
+        <v>287.11</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-603</v>
+        <v>-327.53</v>
       </c>
       <c r="K22" t="n">
-        <v>96.69</v>
+        <v>52.52</v>
       </c>
       <c r="L22" t="n">
-        <v>610.71</v>
+        <v>331.72</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-769.91</v>
+        <v>-373.01</v>
       </c>
       <c r="K23" t="n">
-        <v>-64.23</v>
+        <v>-31.12</v>
       </c>
       <c r="L23" t="n">
-        <v>772.58</v>
+        <v>374.31</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>405.12</v>
+        <v>204.93</v>
       </c>
       <c r="K24" t="n">
-        <v>281.54</v>
+        <v>142.42</v>
       </c>
       <c r="L24" t="n">
-        <v>493.34</v>
+        <v>249.55</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-449.5</v>
+        <v>-214.27</v>
       </c>
       <c r="K25" t="n">
-        <v>290.53</v>
+        <v>138.49</v>
       </c>
       <c r="L25" t="n">
-        <v>535.22</v>
+        <v>255.13</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-284.59</v>
+        <v>-134.08</v>
       </c>
       <c r="K26" t="n">
-        <v>-804.95</v>
+        <v>-379.25</v>
       </c>
       <c r="L26" t="n">
-        <v>853.77</v>
+        <v>402.26</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-710.36</v>
+        <v>-300.1</v>
       </c>
       <c r="K27" t="n">
-        <v>578.73</v>
+        <v>244.49</v>
       </c>
       <c r="L27" t="n">
-        <v>916.26</v>
+        <v>387.09</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>864.45</v>
+        <v>394.86</v>
       </c>
       <c r="K28" t="n">
-        <v>26.95</v>
+        <v>12.31</v>
       </c>
       <c r="L28" t="n">
-        <v>864.87</v>
+        <v>395.05</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-57.54</v>
+        <v>-38.82</v>
       </c>
       <c r="K29" t="n">
-        <v>-256.12</v>
+        <v>-172.79</v>
       </c>
       <c r="L29" t="n">
-        <v>262.5</v>
+        <v>177.09</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-265.98</v>
+        <v>-177.97</v>
       </c>
       <c r="K30" t="n">
-        <v>-94.03</v>
+        <v>-62.92</v>
       </c>
       <c r="L30" t="n">
-        <v>282.11</v>
+        <v>188.76</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-190.57</v>
+        <v>-116.61</v>
       </c>
       <c r="K31" t="n">
-        <v>-73.59999999999999</v>
+        <v>-45.04</v>
       </c>
       <c r="L31" t="n">
-        <v>204.29</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>218.94</v>
+        <v>134.52</v>
       </c>
       <c r="K32" t="n">
-        <v>-61.08</v>
+        <v>-37.53</v>
       </c>
       <c r="L32" t="n">
-        <v>227.3</v>
+        <v>139.66</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>220.16</v>
+        <v>128.27</v>
       </c>
       <c r="K33" t="n">
-        <v>93.53</v>
+        <v>54.49</v>
       </c>
       <c r="L33" t="n">
-        <v>239.2</v>
+        <v>139.36</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-197.12</v>
+        <v>-118.78</v>
       </c>
       <c r="K34" t="n">
-        <v>-191.8</v>
+        <v>-115.58</v>
       </c>
       <c r="L34" t="n">
-        <v>275.04</v>
+        <v>165.73</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>199.54</v>
+        <v>114.46</v>
       </c>
       <c r="K35" t="n">
-        <v>-32.73</v>
+        <v>-18.77</v>
       </c>
       <c r="L35" t="n">
-        <v>202.2</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-393.16</v>
+        <v>-229.12</v>
       </c>
       <c r="K36" t="n">
-        <v>306.49</v>
+        <v>178.62</v>
       </c>
       <c r="L36" t="n">
-        <v>498.51</v>
+        <v>290.52</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-35.64</v>
+        <v>-18.18</v>
       </c>
       <c r="K37" t="n">
-        <v>569.87</v>
+        <v>290.6</v>
       </c>
       <c r="L37" t="n">
-        <v>570.99</v>
+        <v>291.17</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-515.21</v>
+        <v>-255.3</v>
       </c>
       <c r="K38" t="n">
-        <v>120.93</v>
+        <v>59.92</v>
       </c>
       <c r="L38" t="n">
-        <v>529.21</v>
+        <v>262.24</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>657.29</v>
+        <v>295.75</v>
       </c>
       <c r="K39" t="n">
-        <v>-265.83</v>
+        <v>-119.61</v>
       </c>
       <c r="L39" t="n">
-        <v>709.01</v>
+        <v>319.02</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>97.48999999999999</v>
+        <v>44.91</v>
       </c>
       <c r="K40" t="n">
-        <v>709.15</v>
+        <v>326.71</v>
       </c>
       <c r="L40" t="n">
-        <v>715.8200000000001</v>
+        <v>329.78</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-74.31999999999999</v>
+        <v>-32.05</v>
       </c>
       <c r="K41" t="n">
-        <v>-857.55</v>
+        <v>-369.79</v>
       </c>
       <c r="L41" t="n">
-        <v>860.77</v>
+        <v>371.18</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-413.83</v>
+        <v>-178.28</v>
       </c>
       <c r="K42" t="n">
-        <v>-1097.79</v>
+        <v>-472.94</v>
       </c>
       <c r="L42" t="n">
-        <v>1173.2</v>
+        <v>505.43</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-235.78</v>
+        <v>-105.58</v>
       </c>
       <c r="K43" t="n">
-        <v>752.6900000000001</v>
+        <v>337.03</v>
       </c>
       <c r="L43" t="n">
-        <v>788.76</v>
+        <v>353.18</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-124.7</v>
+        <v>-86.25</v>
       </c>
       <c r="K44" t="n">
-        <v>30.35</v>
+        <v>20.99</v>
       </c>
       <c r="L44" t="n">
-        <v>128.34</v>
+        <v>88.77</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-227.11</v>
+        <v>-144.29</v>
       </c>
       <c r="K45" t="n">
-        <v>32.53</v>
+        <v>20.67</v>
       </c>
       <c r="L45" t="n">
-        <v>229.43</v>
+        <v>145.76</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>53.88</v>
+        <v>33.08</v>
       </c>
       <c r="K46" t="n">
-        <v>209.04</v>
+        <v>128.35</v>
       </c>
       <c r="L46" t="n">
-        <v>215.87</v>
+        <v>132.54</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>377.77</v>
+        <v>217.98</v>
       </c>
       <c r="K47" t="n">
-        <v>72.22</v>
+        <v>41.67</v>
       </c>
       <c r="L47" t="n">
-        <v>384.62</v>
+        <v>221.93</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-203.92</v>
+        <v>-133.95</v>
       </c>
       <c r="K48" t="n">
-        <v>-145.94</v>
+        <v>-95.86</v>
       </c>
       <c r="L48" t="n">
-        <v>250.76</v>
+        <v>164.72</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>20.08</v>
+        <v>12.77</v>
       </c>
       <c r="K49" t="n">
-        <v>144.44</v>
+        <v>91.86</v>
       </c>
       <c r="L49" t="n">
-        <v>145.83</v>
+        <v>92.73999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-123.7</v>
+        <v>-62.41</v>
       </c>
       <c r="K50" t="n">
-        <v>258.08</v>
+        <v>130.2</v>
       </c>
       <c r="L50" t="n">
-        <v>286.2</v>
+        <v>144.39</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>123.85</v>
+        <v>64.12</v>
       </c>
       <c r="K51" t="n">
-        <v>-412.32</v>
+        <v>-213.47</v>
       </c>
       <c r="L51" t="n">
-        <v>430.52</v>
+        <v>222.9</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>-121.9</v>
+        <v>-63.29</v>
       </c>
       <c r="K52" t="n">
-        <v>806.97</v>
+        <v>418.96</v>
       </c>
       <c r="L52" t="n">
-        <v>816.12</v>
+        <v>423.72</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-140.54</v>
+        <v>-62.39</v>
       </c>
       <c r="K53" t="n">
-        <v>612.85</v>
+        <v>272.06</v>
       </c>
       <c r="L53" t="n">
-        <v>628.76</v>
+        <v>279.12</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>368.23</v>
+        <v>165.98</v>
       </c>
       <c r="K54" t="n">
-        <v>-436.48</v>
+        <v>-196.74</v>
       </c>
       <c r="L54" t="n">
-        <v>571.0599999999999</v>
+        <v>257.41</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>411.11</v>
+        <v>203.71</v>
       </c>
       <c r="K55" t="n">
-        <v>1054.9</v>
+        <v>522.72</v>
       </c>
       <c r="L55" t="n">
-        <v>1132.18</v>
+        <v>561.01</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-769.9</v>
+        <v>-366.4</v>
       </c>
       <c r="K56" t="n">
-        <v>225.89</v>
+        <v>107.51</v>
       </c>
       <c r="L56" t="n">
-        <v>802.36</v>
+        <v>381.85</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-1199.19</v>
+        <v>-530.23</v>
       </c>
       <c r="K57" t="n">
-        <v>-531.86</v>
+        <v>-235.16</v>
       </c>
       <c r="L57" t="n">
-        <v>1311.84</v>
+        <v>580.04</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>444.47</v>
+        <v>186.15</v>
       </c>
       <c r="K58" t="n">
-        <v>-672.35</v>
+        <v>-281.6</v>
       </c>
       <c r="L58" t="n">
-        <v>805.98</v>
+        <v>337.57</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-178.67</v>
+        <v>-117.52</v>
       </c>
       <c r="K59" t="n">
-        <v>-111.92</v>
+        <v>-73.62</v>
       </c>
       <c r="L59" t="n">
-        <v>210.82</v>
+        <v>138.68</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>118.7</v>
+        <v>73.42</v>
       </c>
       <c r="K60" t="n">
-        <v>181.03</v>
+        <v>111.98</v>
       </c>
       <c r="L60" t="n">
-        <v>216.48</v>
+        <v>133.9</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.07</v>
+        <v>-10.85</v>
       </c>
       <c r="K61" t="n">
-        <v>-121.73</v>
+        <v>-77.37</v>
       </c>
       <c r="L61" t="n">
-        <v>122.92</v>
+        <v>78.13</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-260.07</v>
+        <v>-170.86</v>
       </c>
       <c r="K62" t="n">
-        <v>57.78</v>
+        <v>37.96</v>
       </c>
       <c r="L62" t="n">
-        <v>266.42</v>
+        <v>175.02</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>389.63</v>
+        <v>222.86</v>
       </c>
       <c r="K63" t="n">
-        <v>-226.38</v>
+        <v>-129.49</v>
       </c>
       <c r="L63" t="n">
-        <v>450.63</v>
+        <v>257.75</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-163.57</v>
+        <v>-108.05</v>
       </c>
       <c r="K64" t="n">
-        <v>-264.15</v>
+        <v>-174.48</v>
       </c>
       <c r="L64" t="n">
-        <v>310.69</v>
+        <v>205.23</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-480.06</v>
+        <v>-256.72</v>
       </c>
       <c r="K65" t="n">
-        <v>-16.3</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>480.34</v>
+        <v>256.86</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>453.43</v>
+        <v>226.18</v>
       </c>
       <c r="K66" t="n">
-        <v>272.8</v>
+        <v>136.08</v>
       </c>
       <c r="L66" t="n">
-        <v>529.17</v>
+        <v>263.96</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-85.13</v>
+        <v>-45.09</v>
       </c>
       <c r="K67" t="n">
-        <v>-530.6799999999999</v>
+        <v>-281.09</v>
       </c>
       <c r="L67" t="n">
-        <v>537.46</v>
+        <v>284.68</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-706.65</v>
+        <v>-318.67</v>
       </c>
       <c r="K68" t="n">
-        <v>994.62</v>
+        <v>448.54</v>
       </c>
       <c r="L68" t="n">
-        <v>1220.1</v>
+        <v>550.22</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>150.77</v>
+        <v>74.25</v>
       </c>
       <c r="K69" t="n">
-        <v>493.72</v>
+        <v>243.14</v>
       </c>
       <c r="L69" t="n">
-        <v>516.23</v>
+        <v>254.22</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-365.4</v>
+        <v>-171.21</v>
       </c>
       <c r="K70" t="n">
-        <v>795.46</v>
+        <v>372.71</v>
       </c>
       <c r="L70" t="n">
-        <v>875.37</v>
+        <v>410.15</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-1770.64</v>
+        <v>-765.8</v>
       </c>
       <c r="K71" t="n">
-        <v>-196.62</v>
+        <v>-85.04000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>1781.53</v>
+        <v>770.51</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>602.3099999999999</v>
+        <v>271</v>
       </c>
       <c r="K72" t="n">
-        <v>369.51</v>
+        <v>166.25</v>
       </c>
       <c r="L72" t="n">
-        <v>706.63</v>
+        <v>317.93</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-587.54</v>
+        <v>-234.24</v>
       </c>
       <c r="K73" t="n">
-        <v>646.99</v>
+        <v>257.95</v>
       </c>
       <c r="L73" t="n">
-        <v>873.96</v>
+        <v>348.43</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>333.56</v>
+        <v>212.03</v>
       </c>
       <c r="K74" t="n">
-        <v>40.92</v>
+        <v>26.01</v>
       </c>
       <c r="L74" t="n">
-        <v>336.06</v>
+        <v>213.62</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>562.65</v>
+        <v>333.49</v>
       </c>
       <c r="K75" t="n">
-        <v>175.08</v>
+        <v>103.77</v>
       </c>
       <c r="L75" t="n">
-        <v>589.26</v>
+        <v>349.26</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>257.33</v>
+        <v>152.41</v>
       </c>
       <c r="K76" t="n">
-        <v>-314.11</v>
+        <v>-186.04</v>
       </c>
       <c r="L76" t="n">
-        <v>406.06</v>
+        <v>240.5</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>43.88</v>
+        <v>26.27</v>
       </c>
       <c r="K77" t="n">
-        <v>-330.16</v>
+        <v>-197.68</v>
       </c>
       <c r="L77" t="n">
-        <v>333.06</v>
+        <v>199.41</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-269.71</v>
+        <v>-158.75</v>
       </c>
       <c r="K78" t="n">
-        <v>-84.2</v>
+        <v>-49.56</v>
       </c>
       <c r="L78" t="n">
-        <v>282.55</v>
+        <v>166.31</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-360.57</v>
+        <v>-210.06</v>
       </c>
       <c r="K79" t="n">
-        <v>-66.73999999999999</v>
+        <v>-38.88</v>
       </c>
       <c r="L79" t="n">
-        <v>366.7</v>
+        <v>213.63</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-180.81</v>
+        <v>-90.54000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-188.77</v>
+        <v>-94.53</v>
       </c>
       <c r="L80" t="n">
-        <v>261.4</v>
+        <v>130.9</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>203.73</v>
+        <v>116.08</v>
       </c>
       <c r="K81" t="n">
-        <v>415.78</v>
+        <v>236.9</v>
       </c>
       <c r="L81" t="n">
-        <v>463.01</v>
+        <v>263.81</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-489.63</v>
+        <v>-263.3</v>
       </c>
       <c r="K82" t="n">
-        <v>-159.02</v>
+        <v>-85.52</v>
       </c>
       <c r="L82" t="n">
-        <v>514.8099999999999</v>
+        <v>276.84</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-476.36</v>
+        <v>-232.47</v>
       </c>
       <c r="K83" t="n">
-        <v>-740.89</v>
+        <v>-361.57</v>
       </c>
       <c r="L83" t="n">
-        <v>880.8200000000001</v>
+        <v>429.86</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-893.95</v>
+        <v>-423.44</v>
       </c>
       <c r="K84" t="n">
-        <v>-659.5700000000001</v>
+        <v>-312.42</v>
       </c>
       <c r="L84" t="n">
-        <v>1110.93</v>
+        <v>526.22</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-221.14</v>
+        <v>-110.18</v>
       </c>
       <c r="K85" t="n">
-        <v>855.05</v>
+        <v>426</v>
       </c>
       <c r="L85" t="n">
-        <v>883.1900000000001</v>
+        <v>440.01</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>1038.4</v>
+        <v>457.33</v>
       </c>
       <c r="K86" t="n">
-        <v>-846.91</v>
+        <v>-372.99</v>
       </c>
       <c r="L86" t="n">
-        <v>1339.97</v>
+        <v>590.14</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>792.99</v>
+        <v>348.98</v>
       </c>
       <c r="K87" t="n">
-        <v>-41.53</v>
+        <v>-18.28</v>
       </c>
       <c r="L87" t="n">
-        <v>794.08</v>
+        <v>349.46</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-664.11</v>
+        <v>-275.97</v>
       </c>
       <c r="K88" t="n">
-        <v>-390.86</v>
+        <v>-162.42</v>
       </c>
       <c r="L88" t="n">
-        <v>770.59</v>
+        <v>320.22</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-04.xlsx
+++ b/output/2024-04-04.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>60.01</v>
+        <v>64.42</v>
       </c>
       <c r="K14" t="n">
-        <v>87.83</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>106.38</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>78.91</v>
+        <v>85.91</v>
       </c>
       <c r="K15" t="n">
-        <v>106.29</v>
+        <v>115.71</v>
       </c>
       <c r="L15" t="n">
-        <v>132.38</v>
+        <v>144.12</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>63.6</v>
+        <v>69.3</v>
       </c>
       <c r="K16" t="n">
-        <v>97.33</v>
+        <v>106.06</v>
       </c>
       <c r="L16" t="n">
-        <v>116.26</v>
+        <v>126.69</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>97.48</v>
+        <v>110.27</v>
       </c>
       <c r="K17" t="n">
-        <v>-172.38</v>
+        <v>-195.01</v>
       </c>
       <c r="L17" t="n">
-        <v>198.03</v>
+        <v>224.03</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>-102.22</v>
+        <v>-116.15</v>
       </c>
       <c r="K18" t="n">
-        <v>36.97</v>
+        <v>42.01</v>
       </c>
       <c r="L18" t="n">
-        <v>108.7</v>
+        <v>123.51</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-168.48</v>
+        <v>-190.83</v>
       </c>
       <c r="K19" t="n">
-        <v>79.41</v>
+        <v>89.94</v>
       </c>
       <c r="L19" t="n">
-        <v>186.26</v>
+        <v>210.97</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>137.36</v>
+        <v>161.36</v>
       </c>
       <c r="K20" t="n">
-        <v>-73.77</v>
+        <v>-86.65000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>155.92</v>
+        <v>183.15</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>94.5</v>
+        <v>108.85</v>
       </c>
       <c r="K21" t="n">
-        <v>271.11</v>
+        <v>312.27</v>
       </c>
       <c r="L21" t="n">
-        <v>287.11</v>
+        <v>330.69</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-327.53</v>
+        <v>-380.12</v>
       </c>
       <c r="K22" t="n">
-        <v>52.52</v>
+        <v>60.95</v>
       </c>
       <c r="L22" t="n">
-        <v>331.72</v>
+        <v>384.97</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-373.01</v>
+        <v>-443.97</v>
       </c>
       <c r="K23" t="n">
-        <v>-31.12</v>
+        <v>-37.04</v>
       </c>
       <c r="L23" t="n">
-        <v>374.31</v>
+        <v>445.51</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>204.93</v>
+        <v>242.23</v>
       </c>
       <c r="K24" t="n">
-        <v>142.42</v>
+        <v>168.34</v>
       </c>
       <c r="L24" t="n">
-        <v>249.55</v>
+        <v>294.98</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-214.27</v>
+        <v>-255.75</v>
       </c>
       <c r="K25" t="n">
-        <v>138.49</v>
+        <v>165.3</v>
       </c>
       <c r="L25" t="n">
-        <v>255.13</v>
+        <v>304.52</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-134.08</v>
+        <v>-161.57</v>
       </c>
       <c r="K26" t="n">
-        <v>-379.25</v>
+        <v>-457</v>
       </c>
       <c r="L26" t="n">
-        <v>402.26</v>
+        <v>484.72</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-300.1</v>
+        <v>-365.72</v>
       </c>
       <c r="K27" t="n">
-        <v>244.49</v>
+        <v>297.95</v>
       </c>
       <c r="L27" t="n">
-        <v>387.09</v>
+        <v>471.73</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>394.86</v>
+        <v>477.6</v>
       </c>
       <c r="K28" t="n">
-        <v>12.31</v>
+        <v>14.89</v>
       </c>
       <c r="L28" t="n">
-        <v>395.05</v>
+        <v>477.83</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-38.82</v>
+        <v>-41.89</v>
       </c>
       <c r="K29" t="n">
-        <v>-172.79</v>
+        <v>-186.44</v>
       </c>
       <c r="L29" t="n">
-        <v>177.09</v>
+        <v>191.09</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-177.97</v>
+        <v>-193.05</v>
       </c>
       <c r="K30" t="n">
-        <v>-62.92</v>
+        <v>-68.25</v>
       </c>
       <c r="L30" t="n">
-        <v>188.76</v>
+        <v>204.75</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-116.61</v>
+        <v>-128.66</v>
       </c>
       <c r="K31" t="n">
-        <v>-45.04</v>
+        <v>-49.69</v>
       </c>
       <c r="L31" t="n">
-        <v>125</v>
+        <v>137.92</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>134.52</v>
+        <v>151.4</v>
       </c>
       <c r="K32" t="n">
-        <v>-37.53</v>
+        <v>-42.24</v>
       </c>
       <c r="L32" t="n">
-        <v>139.66</v>
+        <v>157.18</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>128.27</v>
+        <v>144.25</v>
       </c>
       <c r="K33" t="n">
-        <v>54.49</v>
+        <v>61.28</v>
       </c>
       <c r="L33" t="n">
-        <v>139.36</v>
+        <v>156.73</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-118.78</v>
+        <v>-134.14</v>
       </c>
       <c r="K34" t="n">
-        <v>-115.58</v>
+        <v>-130.53</v>
       </c>
       <c r="L34" t="n">
-        <v>165.73</v>
+        <v>187.17</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>114.46</v>
+        <v>132.27</v>
       </c>
       <c r="K35" t="n">
-        <v>-18.77</v>
+        <v>-21.69</v>
       </c>
       <c r="L35" t="n">
-        <v>115.99</v>
+        <v>134.04</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-229.12</v>
+        <v>-262.98</v>
       </c>
       <c r="K36" t="n">
-        <v>178.62</v>
+        <v>205.01</v>
       </c>
       <c r="L36" t="n">
-        <v>290.52</v>
+        <v>333.45</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-18.18</v>
+        <v>-21.35</v>
       </c>
       <c r="K37" t="n">
-        <v>290.6</v>
+        <v>341.37</v>
       </c>
       <c r="L37" t="n">
-        <v>291.17</v>
+        <v>342.03</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-255.3</v>
+        <v>-301.83</v>
       </c>
       <c r="K38" t="n">
-        <v>59.92</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>262.24</v>
+        <v>310.04</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>295.75</v>
+        <v>356.48</v>
       </c>
       <c r="K39" t="n">
-        <v>-119.61</v>
+        <v>-144.17</v>
       </c>
       <c r="L39" t="n">
-        <v>319.02</v>
+        <v>384.53</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>44.91</v>
+        <v>53.98</v>
       </c>
       <c r="K40" t="n">
-        <v>326.71</v>
+        <v>392.67</v>
       </c>
       <c r="L40" t="n">
-        <v>329.78</v>
+        <v>396.36</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-32.05</v>
+        <v>-39.01</v>
       </c>
       <c r="K41" t="n">
-        <v>-369.79</v>
+        <v>-450.07</v>
       </c>
       <c r="L41" t="n">
-        <v>371.18</v>
+        <v>451.76</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-178.28</v>
+        <v>-218.66</v>
       </c>
       <c r="K42" t="n">
-        <v>-472.94</v>
+        <v>-580.05</v>
       </c>
       <c r="L42" t="n">
-        <v>505.43</v>
+        <v>619.89</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-105.58</v>
+        <v>-128.05</v>
       </c>
       <c r="K43" t="n">
-        <v>337.03</v>
+        <v>408.79</v>
       </c>
       <c r="L43" t="n">
-        <v>353.18</v>
+        <v>428.38</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-86.25</v>
+        <v>-93.87</v>
       </c>
       <c r="K44" t="n">
-        <v>20.99</v>
+        <v>22.85</v>
       </c>
       <c r="L44" t="n">
-        <v>88.77</v>
+        <v>96.61</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-144.29</v>
+        <v>-156.89</v>
       </c>
       <c r="K45" t="n">
-        <v>20.67</v>
+        <v>22.48</v>
       </c>
       <c r="L45" t="n">
-        <v>145.76</v>
+        <v>158.49</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>33.08</v>
+        <v>36.85</v>
       </c>
       <c r="K46" t="n">
-        <v>128.35</v>
+        <v>142.96</v>
       </c>
       <c r="L46" t="n">
-        <v>132.54</v>
+        <v>147.63</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>217.98</v>
+        <v>246.69</v>
       </c>
       <c r="K47" t="n">
-        <v>41.67</v>
+        <v>47.16</v>
       </c>
       <c r="L47" t="n">
-        <v>221.93</v>
+        <v>251.16</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-133.95</v>
+        <v>-149.81</v>
       </c>
       <c r="K48" t="n">
-        <v>-95.86</v>
+        <v>-107.21</v>
       </c>
       <c r="L48" t="n">
-        <v>164.72</v>
+        <v>184.22</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>12.77</v>
+        <v>14.21</v>
       </c>
       <c r="K49" t="n">
-        <v>91.86</v>
+        <v>102.23</v>
       </c>
       <c r="L49" t="n">
-        <v>92.73999999999999</v>
+        <v>103.22</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-62.41</v>
+        <v>-73.31</v>
       </c>
       <c r="K50" t="n">
-        <v>130.2</v>
+        <v>152.95</v>
       </c>
       <c r="L50" t="n">
-        <v>144.39</v>
+        <v>169.61</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>64.12</v>
+        <v>74.72</v>
       </c>
       <c r="K51" t="n">
-        <v>-213.47</v>
+        <v>-248.78</v>
       </c>
       <c r="L51" t="n">
-        <v>222.9</v>
+        <v>259.76</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>-63.29</v>
+        <v>-74.05</v>
       </c>
       <c r="K52" t="n">
-        <v>418.96</v>
+        <v>490.23</v>
       </c>
       <c r="L52" t="n">
-        <v>423.72</v>
+        <v>495.79</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-62.39</v>
+        <v>-75.01000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>272.06</v>
+        <v>327.09</v>
       </c>
       <c r="L53" t="n">
-        <v>279.12</v>
+        <v>335.58</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>165.98</v>
+        <v>200</v>
       </c>
       <c r="K54" t="n">
-        <v>-196.74</v>
+        <v>-237.07</v>
       </c>
       <c r="L54" t="n">
-        <v>257.41</v>
+        <v>310.17</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>203.71</v>
+        <v>241.66</v>
       </c>
       <c r="K55" t="n">
-        <v>522.72</v>
+        <v>620.1</v>
       </c>
       <c r="L55" t="n">
-        <v>561.01</v>
+        <v>665.53</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-366.4</v>
+        <v>-437.77</v>
       </c>
       <c r="K56" t="n">
-        <v>107.51</v>
+        <v>128.45</v>
       </c>
       <c r="L56" t="n">
-        <v>381.85</v>
+        <v>456.23</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-530.23</v>
+        <v>-647.39</v>
       </c>
       <c r="K57" t="n">
-        <v>-235.16</v>
+        <v>-287.13</v>
       </c>
       <c r="L57" t="n">
-        <v>580.04</v>
+        <v>708.21</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>186.15</v>
+        <v>227.73</v>
       </c>
       <c r="K58" t="n">
-        <v>-281.6</v>
+        <v>-344.5</v>
       </c>
       <c r="L58" t="n">
-        <v>337.57</v>
+        <v>412.97</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-117.52</v>
+        <v>-127.67</v>
       </c>
       <c r="K59" t="n">
-        <v>-73.62</v>
+        <v>-79.97</v>
       </c>
       <c r="L59" t="n">
-        <v>138.68</v>
+        <v>150.65</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>73.42</v>
+        <v>81.59</v>
       </c>
       <c r="K60" t="n">
-        <v>111.98</v>
+        <v>124.42</v>
       </c>
       <c r="L60" t="n">
-        <v>133.9</v>
+        <v>148.79</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.85</v>
+        <v>-11.99</v>
       </c>
       <c r="K61" t="n">
-        <v>-77.37</v>
+        <v>-85.52</v>
       </c>
       <c r="L61" t="n">
-        <v>78.13</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-170.86</v>
+        <v>-189.44</v>
       </c>
       <c r="K62" t="n">
-        <v>37.96</v>
+        <v>42.09</v>
       </c>
       <c r="L62" t="n">
-        <v>175.02</v>
+        <v>194.06</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>222.86</v>
+        <v>251.87</v>
       </c>
       <c r="K63" t="n">
-        <v>-129.49</v>
+        <v>-146.34</v>
       </c>
       <c r="L63" t="n">
-        <v>257.75</v>
+        <v>291.3</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-108.05</v>
+        <v>-119.84</v>
       </c>
       <c r="K64" t="n">
-        <v>-174.48</v>
+        <v>-193.52</v>
       </c>
       <c r="L64" t="n">
-        <v>205.23</v>
+        <v>227.62</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-256.72</v>
+        <v>-295.49</v>
       </c>
       <c r="K65" t="n">
-        <v>-8.720000000000001</v>
+        <v>-10.03</v>
       </c>
       <c r="L65" t="n">
-        <v>256.86</v>
+        <v>295.66</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>226.18</v>
+        <v>265.69</v>
       </c>
       <c r="K66" t="n">
-        <v>136.08</v>
+        <v>159.85</v>
       </c>
       <c r="L66" t="n">
-        <v>263.96</v>
+        <v>310.07</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-45.09</v>
+        <v>-52.71</v>
       </c>
       <c r="K67" t="n">
-        <v>-281.09</v>
+        <v>-328.56</v>
       </c>
       <c r="L67" t="n">
-        <v>284.68</v>
+        <v>332.76</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-318.67</v>
+        <v>-384.14</v>
       </c>
       <c r="K68" t="n">
-        <v>448.54</v>
+        <v>540.6799999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>550.22</v>
+        <v>663.24</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>74.25</v>
+        <v>88.17</v>
       </c>
       <c r="K69" t="n">
-        <v>243.14</v>
+        <v>288.75</v>
       </c>
       <c r="L69" t="n">
-        <v>254.22</v>
+        <v>301.91</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-171.21</v>
+        <v>-202.84</v>
       </c>
       <c r="K70" t="n">
-        <v>372.71</v>
+        <v>441.57</v>
       </c>
       <c r="L70" t="n">
-        <v>410.15</v>
+        <v>485.93</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-765.8</v>
+        <v>-938.59</v>
       </c>
       <c r="K71" t="n">
-        <v>-85.04000000000001</v>
+        <v>-104.23</v>
       </c>
       <c r="L71" t="n">
-        <v>770.51</v>
+        <v>944.36</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>271</v>
+        <v>330.8</v>
       </c>
       <c r="K72" t="n">
-        <v>166.25</v>
+        <v>202.94</v>
       </c>
       <c r="L72" t="n">
-        <v>317.93</v>
+        <v>388.09</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-234.24</v>
+        <v>-291.55</v>
       </c>
       <c r="K73" t="n">
-        <v>257.95</v>
+        <v>321.06</v>
       </c>
       <c r="L73" t="n">
-        <v>348.43</v>
+        <v>433.68</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>212.03</v>
+        <v>235.65</v>
       </c>
       <c r="K74" t="n">
-        <v>26.01</v>
+        <v>28.9</v>
       </c>
       <c r="L74" t="n">
-        <v>213.62</v>
+        <v>237.41</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>333.49</v>
+        <v>374.81</v>
       </c>
       <c r="K75" t="n">
-        <v>103.77</v>
+        <v>116.63</v>
       </c>
       <c r="L75" t="n">
-        <v>349.26</v>
+        <v>392.53</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>152.41</v>
+        <v>171.34</v>
       </c>
       <c r="K76" t="n">
-        <v>-186.04</v>
+        <v>-209.14</v>
       </c>
       <c r="L76" t="n">
-        <v>240.5</v>
+        <v>270.37</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>26.27</v>
+        <v>29.45</v>
       </c>
       <c r="K77" t="n">
-        <v>-197.68</v>
+        <v>-221.6</v>
       </c>
       <c r="L77" t="n">
-        <v>199.41</v>
+        <v>223.55</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-158.75</v>
+        <v>-180.2</v>
       </c>
       <c r="K78" t="n">
-        <v>-49.56</v>
+        <v>-56.26</v>
       </c>
       <c r="L78" t="n">
-        <v>166.31</v>
+        <v>188.78</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-210.06</v>
+        <v>-236.15</v>
       </c>
       <c r="K79" t="n">
-        <v>-38.88</v>
+        <v>-43.71</v>
       </c>
       <c r="L79" t="n">
-        <v>213.63</v>
+        <v>240.16</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-90.54000000000001</v>
+        <v>-106.17</v>
       </c>
       <c r="K80" t="n">
-        <v>-94.53</v>
+        <v>-110.84</v>
       </c>
       <c r="L80" t="n">
-        <v>130.9</v>
+        <v>153.48</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>116.08</v>
+        <v>133.18</v>
       </c>
       <c r="K81" t="n">
-        <v>236.9</v>
+        <v>271.8</v>
       </c>
       <c r="L81" t="n">
-        <v>263.81</v>
+        <v>302.67</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-263.3</v>
+        <v>-305.58</v>
       </c>
       <c r="K82" t="n">
-        <v>-85.52</v>
+        <v>-99.25</v>
       </c>
       <c r="L82" t="n">
-        <v>276.84</v>
+        <v>321.29</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-232.47</v>
+        <v>-275.88</v>
       </c>
       <c r="K83" t="n">
-        <v>-361.57</v>
+        <v>-429.08</v>
       </c>
       <c r="L83" t="n">
-        <v>429.86</v>
+        <v>510.12</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-423.44</v>
+        <v>-500.07</v>
       </c>
       <c r="K84" t="n">
-        <v>-312.42</v>
+        <v>-368.96</v>
       </c>
       <c r="L84" t="n">
-        <v>526.22</v>
+        <v>621.45</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-110.18</v>
+        <v>-130.24</v>
       </c>
       <c r="K85" t="n">
-        <v>426</v>
+        <v>503.58</v>
       </c>
       <c r="L85" t="n">
-        <v>440.01</v>
+        <v>520.15</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>457.33</v>
+        <v>559.54</v>
       </c>
       <c r="K86" t="n">
-        <v>-372.99</v>
+        <v>-456.36</v>
       </c>
       <c r="L86" t="n">
-        <v>590.14</v>
+        <v>722.05</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>348.98</v>
+        <v>426.69</v>
       </c>
       <c r="K87" t="n">
-        <v>-18.28</v>
+        <v>-22.35</v>
       </c>
       <c r="L87" t="n">
-        <v>349.46</v>
+        <v>427.27</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-275.97</v>
+        <v>-339.59</v>
       </c>
       <c r="K88" t="n">
-        <v>-162.42</v>
+        <v>-199.86</v>
       </c>
       <c r="L88" t="n">
-        <v>320.22</v>
+        <v>394.04</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-04.xlsx
+++ b/output/2024-04-04.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>64.42</v>
+        <v>36.15</v>
       </c>
       <c r="K14" t="n">
-        <v>94.29000000000001</v>
+        <v>52.92</v>
       </c>
       <c r="L14" t="n">
-        <v>114.2</v>
+        <v>64.09</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>85.91</v>
+        <v>40.84</v>
       </c>
       <c r="K15" t="n">
-        <v>115.71</v>
+        <v>55.01</v>
       </c>
       <c r="L15" t="n">
-        <v>144.12</v>
+        <v>68.51000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>69.3</v>
+        <v>30.68</v>
       </c>
       <c r="K16" t="n">
-        <v>106.06</v>
+        <v>46.95</v>
       </c>
       <c r="L16" t="n">
-        <v>126.69</v>
+        <v>56.08</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>110.27</v>
+        <v>53.98</v>
       </c>
       <c r="K17" t="n">
-        <v>-195.01</v>
+        <v>-95.47</v>
       </c>
       <c r="L17" t="n">
-        <v>224.03</v>
+        <v>109.67</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>-116.15</v>
+        <v>-62.14</v>
       </c>
       <c r="K18" t="n">
-        <v>42.01</v>
+        <v>22.47</v>
       </c>
       <c r="L18" t="n">
-        <v>123.51</v>
+        <v>66.08</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-190.83</v>
+        <v>-95.28</v>
       </c>
       <c r="K19" t="n">
-        <v>89.94</v>
+        <v>44.91</v>
       </c>
       <c r="L19" t="n">
-        <v>210.97</v>
+        <v>105.33</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>161.36</v>
+        <v>82.38</v>
       </c>
       <c r="K20" t="n">
-        <v>-86.65000000000001</v>
+        <v>-44.24</v>
       </c>
       <c r="L20" t="n">
-        <v>183.15</v>
+        <v>93.51000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>108.85</v>
+        <v>54.24</v>
       </c>
       <c r="K21" t="n">
-        <v>312.27</v>
+        <v>155.62</v>
       </c>
       <c r="L21" t="n">
-        <v>330.69</v>
+        <v>164.8</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-380.12</v>
+        <v>-186</v>
       </c>
       <c r="K22" t="n">
-        <v>60.95</v>
+        <v>29.83</v>
       </c>
       <c r="L22" t="n">
-        <v>384.97</v>
+        <v>188.38</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-443.97</v>
+        <v>-245.93</v>
       </c>
       <c r="K23" t="n">
-        <v>-37.04</v>
+        <v>-20.52</v>
       </c>
       <c r="L23" t="n">
-        <v>445.51</v>
+        <v>246.78</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>242.23</v>
+        <v>129.61</v>
       </c>
       <c r="K24" t="n">
-        <v>168.34</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>294.98</v>
+        <v>157.83</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-255.75</v>
+        <v>-132.94</v>
       </c>
       <c r="K25" t="n">
-        <v>165.3</v>
+        <v>85.92</v>
       </c>
       <c r="L25" t="n">
-        <v>304.52</v>
+        <v>158.29</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-161.57</v>
+        <v>-88.14</v>
       </c>
       <c r="K26" t="n">
-        <v>-457</v>
+        <v>-249.3</v>
       </c>
       <c r="L26" t="n">
-        <v>484.72</v>
+        <v>264.42</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-365.72</v>
+        <v>-204.62</v>
       </c>
       <c r="K27" t="n">
-        <v>297.95</v>
+        <v>166.71</v>
       </c>
       <c r="L27" t="n">
-        <v>471.73</v>
+        <v>263.93</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>477.6</v>
+        <v>259.56</v>
       </c>
       <c r="K28" t="n">
-        <v>14.89</v>
+        <v>8.09</v>
       </c>
       <c r="L28" t="n">
-        <v>477.83</v>
+        <v>259.69</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-41.89</v>
+        <v>-21.27</v>
       </c>
       <c r="K29" t="n">
-        <v>-186.44</v>
+        <v>-94.69</v>
       </c>
       <c r="L29" t="n">
-        <v>191.09</v>
+        <v>97.05</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-193.05</v>
+        <v>-94.98999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-68.25</v>
+        <v>-33.58</v>
       </c>
       <c r="L30" t="n">
-        <v>204.75</v>
+        <v>100.75</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-128.66</v>
+        <v>-59.08</v>
       </c>
       <c r="K31" t="n">
-        <v>-49.69</v>
+        <v>-22.82</v>
       </c>
       <c r="L31" t="n">
-        <v>137.92</v>
+        <v>63.33</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>151.4</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-42.24</v>
+        <v>-20.18</v>
       </c>
       <c r="L32" t="n">
-        <v>157.18</v>
+        <v>75.08</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>144.25</v>
+        <v>61.72</v>
       </c>
       <c r="K33" t="n">
-        <v>61.28</v>
+        <v>26.22</v>
       </c>
       <c r="L33" t="n">
-        <v>156.73</v>
+        <v>67.05</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-134.14</v>
+        <v>-65.04000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-130.53</v>
+        <v>-63.29</v>
       </c>
       <c r="L34" t="n">
-        <v>187.17</v>
+        <v>90.75</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>132.27</v>
+        <v>62.62</v>
       </c>
       <c r="K35" t="n">
-        <v>-21.69</v>
+        <v>-10.27</v>
       </c>
       <c r="L35" t="n">
-        <v>134.04</v>
+        <v>63.46</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-262.98</v>
+        <v>-131.13</v>
       </c>
       <c r="K36" t="n">
-        <v>205.01</v>
+        <v>102.22</v>
       </c>
       <c r="L36" t="n">
-        <v>333.45</v>
+        <v>166.27</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-21.35</v>
+        <v>-10.57</v>
       </c>
       <c r="K37" t="n">
-        <v>341.37</v>
+        <v>168.95</v>
       </c>
       <c r="L37" t="n">
-        <v>342.03</v>
+        <v>169.28</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-301.83</v>
+        <v>-148.31</v>
       </c>
       <c r="K38" t="n">
-        <v>70.84999999999999</v>
+        <v>34.81</v>
       </c>
       <c r="L38" t="n">
-        <v>310.04</v>
+        <v>152.34</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>356.48</v>
+        <v>177.14</v>
       </c>
       <c r="K39" t="n">
-        <v>-144.17</v>
+        <v>-71.64</v>
       </c>
       <c r="L39" t="n">
-        <v>384.53</v>
+        <v>191.08</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>53.98</v>
+        <v>23.52</v>
       </c>
       <c r="K40" t="n">
-        <v>392.67</v>
+        <v>171.08</v>
       </c>
       <c r="L40" t="n">
-        <v>396.36</v>
+        <v>172.68</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-39.01</v>
+        <v>-21.04</v>
       </c>
       <c r="K41" t="n">
-        <v>-450.07</v>
+        <v>-242.72</v>
       </c>
       <c r="L41" t="n">
-        <v>451.76</v>
+        <v>243.63</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-218.66</v>
+        <v>-117.77</v>
       </c>
       <c r="K42" t="n">
-        <v>-580.05</v>
+        <v>-312.41</v>
       </c>
       <c r="L42" t="n">
-        <v>619.89</v>
+        <v>333.87</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-128.05</v>
+        <v>-70.26000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>408.79</v>
+        <v>224.3</v>
       </c>
       <c r="L43" t="n">
-        <v>428.38</v>
+        <v>235.05</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-93.87</v>
+        <v>-42.22</v>
       </c>
       <c r="K44" t="n">
-        <v>22.85</v>
+        <v>10.28</v>
       </c>
       <c r="L44" t="n">
-        <v>96.61</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-156.89</v>
+        <v>-76.48</v>
       </c>
       <c r="K45" t="n">
-        <v>22.48</v>
+        <v>10.96</v>
       </c>
       <c r="L45" t="n">
-        <v>158.49</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>36.85</v>
+        <v>15.53</v>
       </c>
       <c r="K46" t="n">
-        <v>142.96</v>
+        <v>60.25</v>
       </c>
       <c r="L46" t="n">
-        <v>147.63</v>
+        <v>62.22</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>246.69</v>
+        <v>111.69</v>
       </c>
       <c r="K47" t="n">
-        <v>47.16</v>
+        <v>21.35</v>
       </c>
       <c r="L47" t="n">
-        <v>251.16</v>
+        <v>113.71</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-149.81</v>
+        <v>-74.95</v>
       </c>
       <c r="K48" t="n">
-        <v>-107.21</v>
+        <v>-53.64</v>
       </c>
       <c r="L48" t="n">
-        <v>184.22</v>
+        <v>92.17</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>14.21</v>
+        <v>2.87</v>
       </c>
       <c r="K49" t="n">
-        <v>102.23</v>
+        <v>20.63</v>
       </c>
       <c r="L49" t="n">
-        <v>103.22</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-73.31</v>
+        <v>-35.81</v>
       </c>
       <c r="K50" t="n">
-        <v>152.95</v>
+        <v>74.7</v>
       </c>
       <c r="L50" t="n">
-        <v>169.61</v>
+        <v>82.84</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>74.72</v>
+        <v>35.67</v>
       </c>
       <c r="K51" t="n">
-        <v>-248.78</v>
+        <v>-118.77</v>
       </c>
       <c r="L51" t="n">
-        <v>259.76</v>
+        <v>124.01</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>-74.05</v>
+        <v>-36.43</v>
       </c>
       <c r="K52" t="n">
-        <v>490.23</v>
+        <v>241.17</v>
       </c>
       <c r="L52" t="n">
-        <v>495.79</v>
+        <v>243.9</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-75.01000000000001</v>
+        <v>-35.11</v>
       </c>
       <c r="K53" t="n">
-        <v>327.09</v>
+        <v>153.12</v>
       </c>
       <c r="L53" t="n">
-        <v>335.58</v>
+        <v>157.09</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>200</v>
+        <v>100.15</v>
       </c>
       <c r="K54" t="n">
-        <v>-237.07</v>
+        <v>-118.71</v>
       </c>
       <c r="L54" t="n">
-        <v>310.17</v>
+        <v>155.31</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>241.66</v>
+        <v>118.74</v>
       </c>
       <c r="K55" t="n">
-        <v>620.1</v>
+        <v>304.69</v>
       </c>
       <c r="L55" t="n">
-        <v>665.53</v>
+        <v>327.01</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-437.77</v>
+        <v>-242.17</v>
       </c>
       <c r="K56" t="n">
-        <v>128.45</v>
+        <v>71.05</v>
       </c>
       <c r="L56" t="n">
-        <v>456.23</v>
+        <v>252.38</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-647.39</v>
+        <v>-348.98</v>
       </c>
       <c r="K57" t="n">
-        <v>-287.13</v>
+        <v>-154.78</v>
       </c>
       <c r="L57" t="n">
-        <v>708.21</v>
+        <v>381.77</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>227.73</v>
+        <v>125.91</v>
       </c>
       <c r="K58" t="n">
-        <v>-344.5</v>
+        <v>-190.47</v>
       </c>
       <c r="L58" t="n">
-        <v>412.97</v>
+        <v>228.33</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-127.67</v>
+        <v>-58.62</v>
       </c>
       <c r="K59" t="n">
-        <v>-79.97</v>
+        <v>-36.72</v>
       </c>
       <c r="L59" t="n">
-        <v>150.65</v>
+        <v>69.18000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>81.59</v>
+        <v>35.56</v>
       </c>
       <c r="K60" t="n">
-        <v>124.42</v>
+        <v>54.23</v>
       </c>
       <c r="L60" t="n">
-        <v>148.79</v>
+        <v>64.84</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.99</v>
+        <v>-1.14</v>
       </c>
       <c r="K61" t="n">
-        <v>-85.52</v>
+        <v>-8.16</v>
       </c>
       <c r="L61" t="n">
-        <v>86.36</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-189.44</v>
+        <v>-86.48</v>
       </c>
       <c r="K62" t="n">
-        <v>42.09</v>
+        <v>19.21</v>
       </c>
       <c r="L62" t="n">
-        <v>194.06</v>
+        <v>88.59</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>251.87</v>
+        <v>110.5</v>
       </c>
       <c r="K63" t="n">
-        <v>-146.34</v>
+        <v>-64.2</v>
       </c>
       <c r="L63" t="n">
-        <v>291.3</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-119.84</v>
+        <v>-55.73</v>
       </c>
       <c r="K64" t="n">
-        <v>-193.52</v>
+        <v>-90</v>
       </c>
       <c r="L64" t="n">
-        <v>227.62</v>
+        <v>105.86</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-295.49</v>
+        <v>-141.82</v>
       </c>
       <c r="K65" t="n">
-        <v>-10.03</v>
+        <v>-4.82</v>
       </c>
       <c r="L65" t="n">
-        <v>295.66</v>
+        <v>141.9</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>265.69</v>
+        <v>127.94</v>
       </c>
       <c r="K66" t="n">
-        <v>159.85</v>
+        <v>76.97</v>
       </c>
       <c r="L66" t="n">
-        <v>310.07</v>
+        <v>149.31</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-52.71</v>
+        <v>-26.56</v>
       </c>
       <c r="K67" t="n">
-        <v>-328.56</v>
+        <v>-165.6</v>
       </c>
       <c r="L67" t="n">
-        <v>332.76</v>
+        <v>167.71</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-384.14</v>
+        <v>-172.46</v>
       </c>
       <c r="K68" t="n">
-        <v>540.6799999999999</v>
+        <v>242.74</v>
       </c>
       <c r="L68" t="n">
-        <v>663.24</v>
+        <v>297.77</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>88.17</v>
+        <v>42.16</v>
       </c>
       <c r="K69" t="n">
-        <v>288.75</v>
+        <v>138.05</v>
       </c>
       <c r="L69" t="n">
-        <v>301.91</v>
+        <v>144.34</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-202.84</v>
+        <v>-89.91</v>
       </c>
       <c r="K70" t="n">
-        <v>441.57</v>
+        <v>195.74</v>
       </c>
       <c r="L70" t="n">
-        <v>485.93</v>
+        <v>215.4</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-938.59</v>
+        <v>-497.26</v>
       </c>
       <c r="K71" t="n">
-        <v>-104.23</v>
+        <v>-55.22</v>
       </c>
       <c r="L71" t="n">
-        <v>944.36</v>
+        <v>500.32</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>330.8</v>
+        <v>176.38</v>
       </c>
       <c r="K72" t="n">
-        <v>202.94</v>
+        <v>108.2</v>
       </c>
       <c r="L72" t="n">
-        <v>388.09</v>
+        <v>206.92</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-291.55</v>
+        <v>-154.15</v>
       </c>
       <c r="K73" t="n">
-        <v>321.06</v>
+        <v>169.75</v>
       </c>
       <c r="L73" t="n">
-        <v>433.68</v>
+        <v>229.3</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>235.65</v>
+        <v>93.66</v>
       </c>
       <c r="K74" t="n">
-        <v>28.9</v>
+        <v>11.49</v>
       </c>
       <c r="L74" t="n">
-        <v>237.41</v>
+        <v>94.37</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>374.81</v>
+        <v>149.55</v>
       </c>
       <c r="K75" t="n">
-        <v>116.63</v>
+        <v>46.53</v>
       </c>
       <c r="L75" t="n">
-        <v>392.53</v>
+        <v>156.62</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>171.34</v>
+        <v>68.14</v>
       </c>
       <c r="K76" t="n">
-        <v>-209.14</v>
+        <v>-83.18000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>270.37</v>
+        <v>107.53</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>29.45</v>
+        <v>12.86</v>
       </c>
       <c r="K77" t="n">
-        <v>-221.6</v>
+        <v>-96.78</v>
       </c>
       <c r="L77" t="n">
-        <v>223.55</v>
+        <v>97.63</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-180.2</v>
+        <v>-87.20999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-56.26</v>
+        <v>-27.23</v>
       </c>
       <c r="L78" t="n">
-        <v>188.78</v>
+        <v>91.36</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-236.15</v>
+        <v>-100.04</v>
       </c>
       <c r="K79" t="n">
-        <v>-43.71</v>
+        <v>-18.51</v>
       </c>
       <c r="L79" t="n">
-        <v>240.16</v>
+        <v>101.73</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-106.17</v>
+        <v>-14.05</v>
       </c>
       <c r="K80" t="n">
-        <v>-110.84</v>
+        <v>-14.67</v>
       </c>
       <c r="L80" t="n">
-        <v>153.48</v>
+        <v>20.32</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>133.18</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>271.8</v>
+        <v>131.78</v>
       </c>
       <c r="L81" t="n">
-        <v>302.67</v>
+        <v>146.75</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-305.58</v>
+        <v>-147.65</v>
       </c>
       <c r="K82" t="n">
-        <v>-99.25</v>
+        <v>-47.95</v>
       </c>
       <c r="L82" t="n">
-        <v>321.29</v>
+        <v>155.24</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-275.88</v>
+        <v>-126.54</v>
       </c>
       <c r="K83" t="n">
-        <v>-429.08</v>
+        <v>-196.81</v>
       </c>
       <c r="L83" t="n">
-        <v>510.12</v>
+        <v>233.98</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-500.07</v>
+        <v>-223.79</v>
       </c>
       <c r="K84" t="n">
-        <v>-368.96</v>
+        <v>-165.11</v>
       </c>
       <c r="L84" t="n">
-        <v>621.45</v>
+        <v>278.11</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-130.24</v>
+        <v>-56.92</v>
       </c>
       <c r="K85" t="n">
-        <v>503.58</v>
+        <v>220.07</v>
       </c>
       <c r="L85" t="n">
-        <v>520.15</v>
+        <v>227.31</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>559.54</v>
+        <v>299.95</v>
       </c>
       <c r="K86" t="n">
-        <v>-456.36</v>
+        <v>-244.63</v>
       </c>
       <c r="L86" t="n">
-        <v>722.05</v>
+        <v>387.06</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>426.69</v>
+        <v>225.69</v>
       </c>
       <c r="K87" t="n">
-        <v>-22.35</v>
+        <v>-11.82</v>
       </c>
       <c r="L87" t="n">
-        <v>427.27</v>
+        <v>225.99</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-339.59</v>
+        <v>-180.77</v>
       </c>
       <c r="K88" t="n">
-        <v>-199.86</v>
+        <v>-106.39</v>
       </c>
       <c r="L88" t="n">
-        <v>394.04</v>
+        <v>209.75</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-04.xlsx
+++ b/output/2024-04-04.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>36.15</v>
+        <v>36.39</v>
       </c>
       <c r="K14" t="n">
-        <v>52.92</v>
+        <v>53.26</v>
       </c>
       <c r="L14" t="n">
-        <v>64.09</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>40.84</v>
+        <v>40.51</v>
       </c>
       <c r="K15" t="n">
-        <v>55.01</v>
+        <v>54.56</v>
       </c>
       <c r="L15" t="n">
-        <v>68.51000000000001</v>
+        <v>67.95</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>30.68</v>
+        <v>31.02</v>
       </c>
       <c r="K16" t="n">
-        <v>46.95</v>
+        <v>47.48</v>
       </c>
       <c r="L16" t="n">
-        <v>56.08</v>
+        <v>56.72</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>53.98</v>
+        <v>52.08</v>
       </c>
       <c r="K17" t="n">
-        <v>-95.47</v>
+        <v>-92.09999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>109.67</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>-62.14</v>
+        <v>-64.48</v>
       </c>
       <c r="K18" t="n">
-        <v>22.47</v>
+        <v>23.32</v>
       </c>
       <c r="L18" t="n">
-        <v>66.08</v>
+        <v>68.56</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-95.28</v>
+        <v>-92.63</v>
       </c>
       <c r="K19" t="n">
-        <v>44.91</v>
+        <v>43.66</v>
       </c>
       <c r="L19" t="n">
-        <v>105.33</v>
+        <v>102.41</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>82.38</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-44.24</v>
+        <v>-46.03</v>
       </c>
       <c r="L20" t="n">
-        <v>93.51000000000001</v>
+        <v>97.28</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>54.24</v>
+        <v>52.3</v>
       </c>
       <c r="K21" t="n">
-        <v>155.62</v>
+        <v>150.04</v>
       </c>
       <c r="L21" t="n">
-        <v>164.8</v>
+        <v>158.89</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-186</v>
+        <v>-177.77</v>
       </c>
       <c r="K22" t="n">
-        <v>29.83</v>
+        <v>28.51</v>
       </c>
       <c r="L22" t="n">
-        <v>188.38</v>
+        <v>180.04</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-245.93</v>
+        <v>-236.78</v>
       </c>
       <c r="K23" t="n">
-        <v>-20.52</v>
+        <v>-19.75</v>
       </c>
       <c r="L23" t="n">
-        <v>246.78</v>
+        <v>237.6</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>129.61</v>
+        <v>130.68</v>
       </c>
       <c r="K24" t="n">
-        <v>90.06999999999999</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>157.83</v>
+        <v>159.14</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-132.94</v>
+        <v>-134.94</v>
       </c>
       <c r="K25" t="n">
-        <v>85.92</v>
+        <v>87.22</v>
       </c>
       <c r="L25" t="n">
-        <v>158.29</v>
+        <v>160.68</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-88.14</v>
+        <v>-90.31</v>
       </c>
       <c r="K26" t="n">
-        <v>-249.3</v>
+        <v>-255.43</v>
       </c>
       <c r="L26" t="n">
-        <v>264.42</v>
+        <v>270.92</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-204.62</v>
+        <v>-204.75</v>
       </c>
       <c r="K27" t="n">
-        <v>166.71</v>
+        <v>166.81</v>
       </c>
       <c r="L27" t="n">
-        <v>263.93</v>
+        <v>264.1</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>259.56</v>
+        <v>268.36</v>
       </c>
       <c r="K28" t="n">
-        <v>8.09</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>259.69</v>
+        <v>268.49</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-21.27</v>
+        <v>-20.54</v>
       </c>
       <c r="K29" t="n">
-        <v>-94.69</v>
+        <v>-91.45</v>
       </c>
       <c r="L29" t="n">
-        <v>97.05</v>
+        <v>93.73</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-94.98999999999999</v>
+        <v>-91.14</v>
       </c>
       <c r="K30" t="n">
-        <v>-33.58</v>
+        <v>-32.22</v>
       </c>
       <c r="L30" t="n">
-        <v>100.75</v>
+        <v>96.66</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-59.08</v>
+        <v>-60.06</v>
       </c>
       <c r="K31" t="n">
-        <v>-22.82</v>
+        <v>-23.2</v>
       </c>
       <c r="L31" t="n">
-        <v>63.33</v>
+        <v>64.38</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>72.31999999999999</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-20.18</v>
+        <v>-20.45</v>
       </c>
       <c r="L32" t="n">
-        <v>75.08</v>
+        <v>76.12</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>61.72</v>
+        <v>63.4</v>
       </c>
       <c r="K33" t="n">
-        <v>26.22</v>
+        <v>26.93</v>
       </c>
       <c r="L33" t="n">
-        <v>67.05</v>
+        <v>68.88</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-65.04000000000001</v>
+        <v>-64.44</v>
       </c>
       <c r="K34" t="n">
-        <v>-63.29</v>
+        <v>-62.71</v>
       </c>
       <c r="L34" t="n">
-        <v>90.75</v>
+        <v>89.92</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>62.62</v>
+        <v>60.89</v>
       </c>
       <c r="K35" t="n">
-        <v>-10.27</v>
+        <v>-9.99</v>
       </c>
       <c r="L35" t="n">
-        <v>63.46</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-131.13</v>
+        <v>-126.7</v>
       </c>
       <c r="K36" t="n">
-        <v>102.22</v>
+        <v>98.77</v>
       </c>
       <c r="L36" t="n">
-        <v>166.27</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-10.57</v>
+        <v>-10.3</v>
       </c>
       <c r="K37" t="n">
-        <v>168.95</v>
+        <v>164.64</v>
       </c>
       <c r="L37" t="n">
-        <v>169.28</v>
+        <v>164.96</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-148.31</v>
+        <v>-152.29</v>
       </c>
       <c r="K38" t="n">
-        <v>34.81</v>
+        <v>35.75</v>
       </c>
       <c r="L38" t="n">
-        <v>152.34</v>
+        <v>156.43</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>177.14</v>
+        <v>178.13</v>
       </c>
       <c r="K39" t="n">
-        <v>-71.64</v>
+        <v>-72.04000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>191.08</v>
+        <v>192.14</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>23.52</v>
+        <v>25.23</v>
       </c>
       <c r="K40" t="n">
-        <v>171.08</v>
+        <v>183.52</v>
       </c>
       <c r="L40" t="n">
-        <v>172.68</v>
+        <v>185.25</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-21.04</v>
+        <v>-22.39</v>
       </c>
       <c r="K41" t="n">
-        <v>-242.72</v>
+        <v>-258.29</v>
       </c>
       <c r="L41" t="n">
-        <v>243.63</v>
+        <v>259.26</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-117.77</v>
+        <v>-121.1</v>
       </c>
       <c r="K42" t="n">
-        <v>-312.41</v>
+        <v>-321.24</v>
       </c>
       <c r="L42" t="n">
-        <v>333.87</v>
+        <v>343.31</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-70.26000000000001</v>
+        <v>-73.19</v>
       </c>
       <c r="K43" t="n">
-        <v>224.3</v>
+        <v>233.63</v>
       </c>
       <c r="L43" t="n">
-        <v>235.05</v>
+        <v>244.83</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-42.22</v>
+        <v>-45.05</v>
       </c>
       <c r="K44" t="n">
-        <v>10.28</v>
+        <v>10.96</v>
       </c>
       <c r="L44" t="n">
-        <v>43.45</v>
+        <v>46.36</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-76.48</v>
+        <v>-75.67</v>
       </c>
       <c r="K45" t="n">
-        <v>10.96</v>
+        <v>10.84</v>
       </c>
       <c r="L45" t="n">
-        <v>77.26000000000001</v>
+        <v>76.44</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>15.53</v>
+        <v>15.66</v>
       </c>
       <c r="K46" t="n">
-        <v>60.25</v>
+        <v>60.75</v>
       </c>
       <c r="L46" t="n">
-        <v>62.22</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>111.69</v>
+        <v>107.09</v>
       </c>
       <c r="K47" t="n">
-        <v>21.35</v>
+        <v>20.47</v>
       </c>
       <c r="L47" t="n">
-        <v>113.71</v>
+        <v>109.03</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-74.95</v>
+        <v>-73.76000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-53.64</v>
+        <v>-52.79</v>
       </c>
       <c r="L48" t="n">
-        <v>92.17</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="K49" t="n">
-        <v>20.63</v>
+        <v>19.64</v>
       </c>
       <c r="L49" t="n">
-        <v>20.83</v>
+        <v>19.83</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-35.81</v>
+        <v>-38.27</v>
       </c>
       <c r="K50" t="n">
-        <v>74.7</v>
+        <v>79.84</v>
       </c>
       <c r="L50" t="n">
-        <v>82.84</v>
+        <v>88.54000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>35.67</v>
+        <v>36.2</v>
       </c>
       <c r="K51" t="n">
-        <v>-118.77</v>
+        <v>-120.51</v>
       </c>
       <c r="L51" t="n">
-        <v>124.01</v>
+        <v>125.83</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>-36.43</v>
+        <v>-34.28</v>
       </c>
       <c r="K52" t="n">
-        <v>241.17</v>
+        <v>226.91</v>
       </c>
       <c r="L52" t="n">
-        <v>243.9</v>
+        <v>229.49</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-35.11</v>
+        <v>-36.38</v>
       </c>
       <c r="K53" t="n">
-        <v>153.12</v>
+        <v>158.63</v>
       </c>
       <c r="L53" t="n">
-        <v>157.09</v>
+        <v>162.75</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>100.15</v>
+        <v>103.33</v>
       </c>
       <c r="K54" t="n">
-        <v>-118.71</v>
+        <v>-122.48</v>
       </c>
       <c r="L54" t="n">
-        <v>155.31</v>
+        <v>160.24</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>118.74</v>
+        <v>112.73</v>
       </c>
       <c r="K55" t="n">
-        <v>304.69</v>
+        <v>289.26</v>
       </c>
       <c r="L55" t="n">
-        <v>327.01</v>
+        <v>310.45</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-242.17</v>
+        <v>-245.78</v>
       </c>
       <c r="K56" t="n">
-        <v>71.05</v>
+        <v>72.11</v>
       </c>
       <c r="L56" t="n">
-        <v>252.38</v>
+        <v>256.14</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-348.98</v>
+        <v>-352.97</v>
       </c>
       <c r="K57" t="n">
-        <v>-154.78</v>
+        <v>-156.55</v>
       </c>
       <c r="L57" t="n">
-        <v>381.77</v>
+        <v>386.12</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>125.91</v>
+        <v>130.99</v>
       </c>
       <c r="K58" t="n">
-        <v>-190.47</v>
+        <v>-198.15</v>
       </c>
       <c r="L58" t="n">
-        <v>228.33</v>
+        <v>237.53</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-58.62</v>
+        <v>-58.27</v>
       </c>
       <c r="K59" t="n">
-        <v>-36.72</v>
+        <v>-36.5</v>
       </c>
       <c r="L59" t="n">
-        <v>69.18000000000001</v>
+        <v>68.76000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>35.56</v>
+        <v>35.74</v>
       </c>
       <c r="K60" t="n">
-        <v>54.23</v>
+        <v>54.5</v>
       </c>
       <c r="L60" t="n">
-        <v>64.84</v>
+        <v>65.18000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.14</v>
+        <v>-1.1</v>
       </c>
       <c r="K61" t="n">
-        <v>-8.16</v>
+        <v>-7.81</v>
       </c>
       <c r="L61" t="n">
-        <v>8.24</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-86.48</v>
+        <v>-84.58</v>
       </c>
       <c r="K62" t="n">
-        <v>19.21</v>
+        <v>18.79</v>
       </c>
       <c r="L62" t="n">
-        <v>88.59</v>
+        <v>86.65000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>110.5</v>
+        <v>104.29</v>
       </c>
       <c r="K63" t="n">
-        <v>-64.2</v>
+        <v>-60.59</v>
       </c>
       <c r="L63" t="n">
-        <v>127.8</v>
+        <v>120.61</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-55.73</v>
+        <v>-53.49</v>
       </c>
       <c r="K64" t="n">
-        <v>-90</v>
+        <v>-86.38</v>
       </c>
       <c r="L64" t="n">
-        <v>105.86</v>
+        <v>101.6</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-141.82</v>
+        <v>-140.76</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.82</v>
+        <v>-4.78</v>
       </c>
       <c r="L65" t="n">
-        <v>141.9</v>
+        <v>140.84</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>127.94</v>
+        <v>127.05</v>
       </c>
       <c r="K66" t="n">
-        <v>76.97</v>
+        <v>76.44</v>
       </c>
       <c r="L66" t="n">
-        <v>149.31</v>
+        <v>148.27</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-26.56</v>
+        <v>-25.78</v>
       </c>
       <c r="K67" t="n">
-        <v>-165.6</v>
+        <v>-160.73</v>
       </c>
       <c r="L67" t="n">
-        <v>167.71</v>
+        <v>162.78</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-172.46</v>
+        <v>-167.14</v>
       </c>
       <c r="K68" t="n">
-        <v>242.74</v>
+        <v>235.25</v>
       </c>
       <c r="L68" t="n">
-        <v>297.77</v>
+        <v>288.58</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>42.16</v>
+        <v>43.7</v>
       </c>
       <c r="K69" t="n">
-        <v>138.05</v>
+        <v>143.12</v>
       </c>
       <c r="L69" t="n">
-        <v>144.34</v>
+        <v>149.65</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-89.91</v>
+        <v>-95.12</v>
       </c>
       <c r="K70" t="n">
-        <v>195.74</v>
+        <v>207.08</v>
       </c>
       <c r="L70" t="n">
-        <v>215.4</v>
+        <v>227.88</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-497.26</v>
+        <v>-522.88</v>
       </c>
       <c r="K71" t="n">
-        <v>-55.22</v>
+        <v>-58.06</v>
       </c>
       <c r="L71" t="n">
-        <v>500.32</v>
+        <v>526.1</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>176.38</v>
+        <v>198.42</v>
       </c>
       <c r="K72" t="n">
-        <v>108.2</v>
+        <v>121.73</v>
       </c>
       <c r="L72" t="n">
-        <v>206.92</v>
+        <v>232.79</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-154.15</v>
+        <v>-181.26</v>
       </c>
       <c r="K73" t="n">
-        <v>169.75</v>
+        <v>199.6</v>
       </c>
       <c r="L73" t="n">
-        <v>229.3</v>
+        <v>269.62</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>93.66</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>11.49</v>
+        <v>10.78</v>
       </c>
       <c r="L74" t="n">
-        <v>94.37</v>
+        <v>88.51000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>149.55</v>
+        <v>135.58</v>
       </c>
       <c r="K75" t="n">
-        <v>46.53</v>
+        <v>42.19</v>
       </c>
       <c r="L75" t="n">
-        <v>156.62</v>
+        <v>142</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>68.14</v>
+        <v>54.34</v>
       </c>
       <c r="K76" t="n">
-        <v>-83.18000000000001</v>
+        <v>-66.33</v>
       </c>
       <c r="L76" t="n">
-        <v>107.53</v>
+        <v>85.75</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>12.86</v>
+        <v>12.49</v>
       </c>
       <c r="K77" t="n">
-        <v>-96.78</v>
+        <v>-93.95999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>97.63</v>
+        <v>94.79000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-87.20999999999999</v>
+        <v>-86.64</v>
       </c>
       <c r="K78" t="n">
-        <v>-27.23</v>
+        <v>-27.05</v>
       </c>
       <c r="L78" t="n">
-        <v>91.36</v>
+        <v>90.76000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-100.04</v>
+        <v>-96.53</v>
       </c>
       <c r="K79" t="n">
-        <v>-18.51</v>
+        <v>-17.87</v>
       </c>
       <c r="L79" t="n">
-        <v>101.73</v>
+        <v>98.17</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-14.05</v>
+        <v>-13.65</v>
       </c>
       <c r="K80" t="n">
-        <v>-14.67</v>
+        <v>-14.25</v>
       </c>
       <c r="L80" t="n">
-        <v>20.32</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>64.56999999999999</v>
+        <v>63.57</v>
       </c>
       <c r="K81" t="n">
-        <v>131.78</v>
+        <v>129.74</v>
       </c>
       <c r="L81" t="n">
-        <v>146.75</v>
+        <v>144.48</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-147.65</v>
+        <v>-145.18</v>
       </c>
       <c r="K82" t="n">
-        <v>-47.95</v>
+        <v>-47.15</v>
       </c>
       <c r="L82" t="n">
-        <v>155.24</v>
+        <v>152.64</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-126.54</v>
+        <v>-124.37</v>
       </c>
       <c r="K83" t="n">
-        <v>-196.81</v>
+        <v>-193.44</v>
       </c>
       <c r="L83" t="n">
-        <v>233.98</v>
+        <v>229.97</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-223.79</v>
+        <v>-218.62</v>
       </c>
       <c r="K84" t="n">
-        <v>-165.11</v>
+        <v>-161.3</v>
       </c>
       <c r="L84" t="n">
-        <v>278.11</v>
+        <v>271.68</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-56.92</v>
+        <v>-59.1</v>
       </c>
       <c r="K85" t="n">
-        <v>220.07</v>
+        <v>228.5</v>
       </c>
       <c r="L85" t="n">
-        <v>227.31</v>
+        <v>236.02</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>299.95</v>
+        <v>307.22</v>
       </c>
       <c r="K86" t="n">
-        <v>-244.63</v>
+        <v>-250.57</v>
       </c>
       <c r="L86" t="n">
-        <v>387.06</v>
+        <v>396.44</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>225.69</v>
+        <v>263.97</v>
       </c>
       <c r="K87" t="n">
-        <v>-11.82</v>
+        <v>-13.82</v>
       </c>
       <c r="L87" t="n">
-        <v>225.99</v>
+        <v>264.33</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-180.77</v>
+        <v>-206.58</v>
       </c>
       <c r="K88" t="n">
-        <v>-106.39</v>
+        <v>-121.58</v>
       </c>
       <c r="L88" t="n">
-        <v>209.75</v>
+        <v>239.7</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-04.xlsx
+++ b/output/2024-04-04.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>36.39</v>
+        <v>36.65</v>
       </c>
       <c r="K14" t="n">
-        <v>53.26</v>
+        <v>53.65</v>
       </c>
       <c r="L14" t="n">
-        <v>64.5</v>
+        <v>64.98</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>40.51</v>
+        <v>40.87</v>
       </c>
       <c r="K15" t="n">
-        <v>54.56</v>
+        <v>55.05</v>
       </c>
       <c r="L15" t="n">
-        <v>67.95</v>
+        <v>68.56999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>31.02</v>
+        <v>32.3</v>
       </c>
       <c r="K16" t="n">
-        <v>47.48</v>
+        <v>49.43</v>
       </c>
       <c r="L16" t="n">
-        <v>56.72</v>
+        <v>59.04</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>52.08</v>
+        <v>50.74</v>
       </c>
       <c r="K17" t="n">
-        <v>-92.09999999999999</v>
+        <v>-89.73</v>
       </c>
       <c r="L17" t="n">
-        <v>105.8</v>
+        <v>103.08</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>-64.48</v>
+        <v>-67.23999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>23.32</v>
+        <v>24.32</v>
       </c>
       <c r="L18" t="n">
-        <v>68.56</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-92.63</v>
+        <v>-90.78</v>
       </c>
       <c r="K19" t="n">
-        <v>43.66</v>
+        <v>42.79</v>
       </c>
       <c r="L19" t="n">
-        <v>102.41</v>
+        <v>100.36</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>85.70999999999999</v>
+        <v>89.67</v>
       </c>
       <c r="K20" t="n">
-        <v>-46.03</v>
+        <v>-48.15</v>
       </c>
       <c r="L20" t="n">
-        <v>97.28</v>
+        <v>101.78</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>52.3</v>
+        <v>50.44</v>
       </c>
       <c r="K21" t="n">
-        <v>150.04</v>
+        <v>144.72</v>
       </c>
       <c r="L21" t="n">
-        <v>158.89</v>
+        <v>153.26</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-177.77</v>
+        <v>-170.34</v>
       </c>
       <c r="K22" t="n">
-        <v>28.51</v>
+        <v>27.31</v>
       </c>
       <c r="L22" t="n">
-        <v>180.04</v>
+        <v>172.52</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-236.78</v>
+        <v>-225.93</v>
       </c>
       <c r="K23" t="n">
-        <v>-19.75</v>
+        <v>-18.85</v>
       </c>
       <c r="L23" t="n">
-        <v>237.6</v>
+        <v>226.71</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>130.68</v>
+        <v>131.53</v>
       </c>
       <c r="K24" t="n">
-        <v>90.81999999999999</v>
+        <v>91.41</v>
       </c>
       <c r="L24" t="n">
-        <v>159.14</v>
+        <v>160.18</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-134.94</v>
+        <v>-136.7</v>
       </c>
       <c r="K25" t="n">
-        <v>87.22</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>160.68</v>
+        <v>162.77</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-90.31</v>
+        <v>-89.18000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-255.43</v>
+        <v>-252.24</v>
       </c>
       <c r="L26" t="n">
-        <v>270.92</v>
+        <v>267.54</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-204.75</v>
+        <v>-202.03</v>
       </c>
       <c r="K27" t="n">
-        <v>166.81</v>
+        <v>164.59</v>
       </c>
       <c r="L27" t="n">
-        <v>264.1</v>
+        <v>260.59</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>268.36</v>
+        <v>266.76</v>
       </c>
       <c r="K28" t="n">
-        <v>8.369999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="L28" t="n">
-        <v>268.49</v>
+        <v>266.89</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-20.54</v>
+        <v>-19.91</v>
       </c>
       <c r="K29" t="n">
-        <v>-91.45</v>
+        <v>-88.61</v>
       </c>
       <c r="L29" t="n">
-        <v>93.73</v>
+        <v>90.81999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-91.14</v>
+        <v>-88.01000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-32.22</v>
+        <v>-31.12</v>
       </c>
       <c r="L30" t="n">
-        <v>96.66</v>
+        <v>93.34999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-60.06</v>
+        <v>-62.55</v>
       </c>
       <c r="K31" t="n">
-        <v>-23.2</v>
+        <v>-24.16</v>
       </c>
       <c r="L31" t="n">
-        <v>64.38</v>
+        <v>67.05</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>73.31999999999999</v>
+        <v>75.87</v>
       </c>
       <c r="K32" t="n">
-        <v>-20.45</v>
+        <v>-21.16</v>
       </c>
       <c r="L32" t="n">
-        <v>76.12</v>
+        <v>78.76000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>63.4</v>
+        <v>67.72</v>
       </c>
       <c r="K33" t="n">
-        <v>26.93</v>
+        <v>28.77</v>
       </c>
       <c r="L33" t="n">
-        <v>68.88</v>
+        <v>73.58</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-64.44</v>
+        <v>-64.87</v>
       </c>
       <c r="K34" t="n">
-        <v>-62.71</v>
+        <v>-63.12</v>
       </c>
       <c r="L34" t="n">
-        <v>89.92</v>
+        <v>90.51000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>60.89</v>
+        <v>66.84</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.99</v>
+        <v>-10.96</v>
       </c>
       <c r="L35" t="n">
-        <v>61.7</v>
+        <v>67.73</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-126.7</v>
+        <v>-122.52</v>
       </c>
       <c r="K36" t="n">
-        <v>98.77</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>160.65</v>
+        <v>155.35</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-10.3</v>
+        <v>-10.08</v>
       </c>
       <c r="K37" t="n">
-        <v>164.64</v>
+        <v>161.1</v>
       </c>
       <c r="L37" t="n">
-        <v>164.96</v>
+        <v>161.42</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-152.29</v>
+        <v>-155.9</v>
       </c>
       <c r="K38" t="n">
-        <v>35.75</v>
+        <v>36.59</v>
       </c>
       <c r="L38" t="n">
-        <v>156.43</v>
+        <v>160.13</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>178.13</v>
+        <v>178.21</v>
       </c>
       <c r="K39" t="n">
-        <v>-72.04000000000001</v>
+        <v>-72.06999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>192.14</v>
+        <v>192.23</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>25.23</v>
+        <v>25.81</v>
       </c>
       <c r="K40" t="n">
-        <v>183.52</v>
+        <v>187.73</v>
       </c>
       <c r="L40" t="n">
-        <v>185.25</v>
+        <v>189.49</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-22.39</v>
+        <v>-22.81</v>
       </c>
       <c r="K41" t="n">
-        <v>-258.29</v>
+        <v>-263.22</v>
       </c>
       <c r="L41" t="n">
-        <v>259.26</v>
+        <v>264.2</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-121.1</v>
+        <v>-118.44</v>
       </c>
       <c r="K42" t="n">
-        <v>-321.24</v>
+        <v>-314.2</v>
       </c>
       <c r="L42" t="n">
-        <v>343.31</v>
+        <v>335.78</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-73.19</v>
+        <v>-74.09999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>233.63</v>
+        <v>236.55</v>
       </c>
       <c r="L43" t="n">
-        <v>244.83</v>
+        <v>247.89</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-45.05</v>
+        <v>-49.37</v>
       </c>
       <c r="K44" t="n">
-        <v>10.96</v>
+        <v>12.01</v>
       </c>
       <c r="L44" t="n">
-        <v>46.36</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-75.67</v>
+        <v>-75.87</v>
       </c>
       <c r="K45" t="n">
-        <v>10.84</v>
+        <v>10.87</v>
       </c>
       <c r="L45" t="n">
-        <v>76.44</v>
+        <v>76.64</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>15.66</v>
+        <v>16.37</v>
       </c>
       <c r="K46" t="n">
-        <v>60.75</v>
+        <v>63.51</v>
       </c>
       <c r="L46" t="n">
-        <v>62.74</v>
+        <v>65.58</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>107.09</v>
+        <v>105.09</v>
       </c>
       <c r="K47" t="n">
-        <v>20.47</v>
+        <v>20.09</v>
       </c>
       <c r="L47" t="n">
-        <v>109.03</v>
+        <v>106.99</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-73.76000000000001</v>
+        <v>-73.3</v>
       </c>
       <c r="K48" t="n">
-        <v>-52.79</v>
+        <v>-52.46</v>
       </c>
       <c r="L48" t="n">
-        <v>90.7</v>
+        <v>90.13</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>2.73</v>
+        <v>2.94</v>
       </c>
       <c r="K49" t="n">
-        <v>19.64</v>
+        <v>21.15</v>
       </c>
       <c r="L49" t="n">
-        <v>19.83</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-38.27</v>
+        <v>-42.13</v>
       </c>
       <c r="K50" t="n">
-        <v>79.84</v>
+        <v>87.89</v>
       </c>
       <c r="L50" t="n">
-        <v>88.54000000000001</v>
+        <v>97.45999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>36.2</v>
+        <v>37.52</v>
       </c>
       <c r="K51" t="n">
-        <v>-120.51</v>
+        <v>-124.9</v>
       </c>
       <c r="L51" t="n">
-        <v>125.83</v>
+        <v>130.42</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>-34.28</v>
+        <v>-32.16</v>
       </c>
       <c r="K52" t="n">
-        <v>226.91</v>
+        <v>212.93</v>
       </c>
       <c r="L52" t="n">
-        <v>229.49</v>
+        <v>215.34</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-36.38</v>
+        <v>-37.53</v>
       </c>
       <c r="K53" t="n">
-        <v>158.63</v>
+        <v>163.64</v>
       </c>
       <c r="L53" t="n">
-        <v>162.75</v>
+        <v>167.89</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>103.33</v>
+        <v>106.41</v>
       </c>
       <c r="K54" t="n">
-        <v>-122.48</v>
+        <v>-126.13</v>
       </c>
       <c r="L54" t="n">
-        <v>160.24</v>
+        <v>165.03</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>112.73</v>
+        <v>105.09</v>
       </c>
       <c r="K55" t="n">
-        <v>289.26</v>
+        <v>269.66</v>
       </c>
       <c r="L55" t="n">
-        <v>310.45</v>
+        <v>289.41</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-245.78</v>
+        <v>-243.61</v>
       </c>
       <c r="K56" t="n">
-        <v>72.11</v>
+        <v>71.48</v>
       </c>
       <c r="L56" t="n">
-        <v>256.14</v>
+        <v>253.88</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-352.97</v>
+        <v>-338.65</v>
       </c>
       <c r="K57" t="n">
-        <v>-156.55</v>
+        <v>-150.2</v>
       </c>
       <c r="L57" t="n">
-        <v>386.12</v>
+        <v>370.47</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>130.99</v>
+        <v>133.47</v>
       </c>
       <c r="K58" t="n">
-        <v>-198.15</v>
+        <v>-201.9</v>
       </c>
       <c r="L58" t="n">
-        <v>237.53</v>
+        <v>242.03</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-58.27</v>
+        <v>-59.23</v>
       </c>
       <c r="K59" t="n">
-        <v>-36.5</v>
+        <v>-37.1</v>
       </c>
       <c r="L59" t="n">
-        <v>68.76000000000001</v>
+        <v>69.89</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>35.74</v>
+        <v>37.05</v>
       </c>
       <c r="K60" t="n">
-        <v>54.5</v>
+        <v>56.5</v>
       </c>
       <c r="L60" t="n">
-        <v>65.18000000000001</v>
+        <v>67.56</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.1</v>
+        <v>-1.16</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.81</v>
+        <v>-8.26</v>
       </c>
       <c r="L61" t="n">
-        <v>7.89</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-84.58</v>
+        <v>-84.8</v>
       </c>
       <c r="K62" t="n">
-        <v>18.79</v>
+        <v>18.84</v>
       </c>
       <c r="L62" t="n">
-        <v>86.65000000000001</v>
+        <v>86.86</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>104.29</v>
+        <v>101.04</v>
       </c>
       <c r="K63" t="n">
-        <v>-60.59</v>
+        <v>-58.71</v>
       </c>
       <c r="L63" t="n">
-        <v>120.61</v>
+        <v>116.86</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-53.49</v>
+        <v>-52.28</v>
       </c>
       <c r="K64" t="n">
-        <v>-86.38</v>
+        <v>-84.43000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>101.6</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-140.76</v>
+        <v>-141.61</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.78</v>
+        <v>-4.81</v>
       </c>
       <c r="L65" t="n">
-        <v>140.84</v>
+        <v>141.7</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>127.05</v>
+        <v>127.81</v>
       </c>
       <c r="K66" t="n">
-        <v>76.44</v>
+        <v>76.89</v>
       </c>
       <c r="L66" t="n">
-        <v>148.27</v>
+        <v>149.15</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-25.78</v>
+        <v>-25.01</v>
       </c>
       <c r="K67" t="n">
-        <v>-160.73</v>
+        <v>-155.92</v>
       </c>
       <c r="L67" t="n">
-        <v>162.78</v>
+        <v>157.91</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-167.14</v>
+        <v>-159.36</v>
       </c>
       <c r="K68" t="n">
-        <v>235.25</v>
+        <v>224.3</v>
       </c>
       <c r="L68" t="n">
-        <v>288.58</v>
+        <v>275.15</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>43.7</v>
+        <v>45.16</v>
       </c>
       <c r="K69" t="n">
-        <v>143.12</v>
+        <v>147.88</v>
       </c>
       <c r="L69" t="n">
-        <v>149.65</v>
+        <v>154.62</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-95.12</v>
+        <v>-94.89</v>
       </c>
       <c r="K70" t="n">
-        <v>207.08</v>
+        <v>206.58</v>
       </c>
       <c r="L70" t="n">
-        <v>227.88</v>
+        <v>227.33</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-522.88</v>
+        <v>-494.02</v>
       </c>
       <c r="K71" t="n">
-        <v>-58.06</v>
+        <v>-54.86</v>
       </c>
       <c r="L71" t="n">
-        <v>526.1</v>
+        <v>497.06</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>198.42</v>
+        <v>208.58</v>
       </c>
       <c r="K72" t="n">
-        <v>121.73</v>
+        <v>127.96</v>
       </c>
       <c r="L72" t="n">
-        <v>232.79</v>
+        <v>244.71</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-181.26</v>
+        <v>-191.39</v>
       </c>
       <c r="K73" t="n">
-        <v>199.6</v>
+        <v>210.76</v>
       </c>
       <c r="L73" t="n">
-        <v>269.62</v>
+        <v>284.7</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>87.84999999999999</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="L74" t="n">
-        <v>88.51000000000001</v>
+        <v>87.08</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>135.58</v>
+        <v>126.51</v>
       </c>
       <c r="K75" t="n">
-        <v>42.19</v>
+        <v>39.37</v>
       </c>
       <c r="L75" t="n">
-        <v>142</v>
+        <v>132.49</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>54.34</v>
+        <v>54.16</v>
       </c>
       <c r="K76" t="n">
-        <v>-66.33</v>
+        <v>-66.11</v>
       </c>
       <c r="L76" t="n">
-        <v>85.75</v>
+        <v>85.47</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>12.49</v>
+        <v>12.52</v>
       </c>
       <c r="K77" t="n">
-        <v>-93.95999999999999</v>
+        <v>-94.18000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>94.79000000000001</v>
+        <v>95.01000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-86.64</v>
+        <v>-87.5</v>
       </c>
       <c r="K78" t="n">
-        <v>-27.05</v>
+        <v>-27.32</v>
       </c>
       <c r="L78" t="n">
-        <v>90.76000000000001</v>
+        <v>91.66</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-96.53</v>
+        <v>-96.66</v>
       </c>
       <c r="K79" t="n">
-        <v>-17.87</v>
+        <v>-17.89</v>
       </c>
       <c r="L79" t="n">
-        <v>98.17</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.65</v>
+        <v>-14.54</v>
       </c>
       <c r="K80" t="n">
-        <v>-14.25</v>
+        <v>-15.18</v>
       </c>
       <c r="L80" t="n">
-        <v>19.73</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>63.57</v>
+        <v>63.23</v>
       </c>
       <c r="K81" t="n">
-        <v>129.74</v>
+        <v>129.05</v>
       </c>
       <c r="L81" t="n">
-        <v>144.48</v>
+        <v>143.71</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-145.18</v>
+        <v>-144.3</v>
       </c>
       <c r="K82" t="n">
-        <v>-47.15</v>
+        <v>-46.87</v>
       </c>
       <c r="L82" t="n">
-        <v>152.64</v>
+        <v>151.72</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-124.37</v>
+        <v>-120.71</v>
       </c>
       <c r="K83" t="n">
-        <v>-193.44</v>
+        <v>-187.74</v>
       </c>
       <c r="L83" t="n">
-        <v>229.97</v>
+        <v>223.19</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-218.62</v>
+        <v>-209.34</v>
       </c>
       <c r="K84" t="n">
-        <v>-161.3</v>
+        <v>-154.46</v>
       </c>
       <c r="L84" t="n">
-        <v>271.68</v>
+        <v>260.16</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-59.1</v>
+        <v>-57.98</v>
       </c>
       <c r="K85" t="n">
-        <v>228.5</v>
+        <v>224.19</v>
       </c>
       <c r="L85" t="n">
-        <v>236.02</v>
+        <v>231.57</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>307.22</v>
+        <v>296.9</v>
       </c>
       <c r="K86" t="n">
-        <v>-250.57</v>
+        <v>-242.15</v>
       </c>
       <c r="L86" t="n">
-        <v>396.44</v>
+        <v>383.13</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>263.97</v>
+        <v>277.05</v>
       </c>
       <c r="K87" t="n">
-        <v>-13.82</v>
+        <v>-14.51</v>
       </c>
       <c r="L87" t="n">
-        <v>264.33</v>
+        <v>277.43</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-206.58</v>
+        <v>-219.37</v>
       </c>
       <c r="K88" t="n">
-        <v>-121.58</v>
+        <v>-129.11</v>
       </c>
       <c r="L88" t="n">
-        <v>239.7</v>
+        <v>254.54</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-04.xlsx
+++ b/output/2024-04-04.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.05</v>
+        <v>3.84</v>
       </c>
       <c r="F14" t="n">
-        <v>9.57</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>299.7</v>
+        <v>282.9</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>36.65</v>
+        <v>73.17</v>
       </c>
       <c r="K14" t="n">
-        <v>53.65</v>
+        <v>40.87</v>
       </c>
       <c r="L14" t="n">
-        <v>64.98</v>
+        <v>83.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:38:24</t>
+          <t>06:38:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="F15" t="n">
-        <v>9.76</v>
+        <v>8.59</v>
       </c>
       <c r="G15" t="n">
-        <v>309.6</v>
+        <v>298</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>96.5</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>40.87</v>
+        <v>1.47</v>
       </c>
       <c r="K15" t="n">
-        <v>55.05</v>
+        <v>-84.55</v>
       </c>
       <c r="L15" t="n">
-        <v>68.56999999999999</v>
+        <v>84.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:40:29</t>
+          <t>06:40:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,28 +709,28 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.14</v>
+        <v>3.79</v>
       </c>
       <c r="F16" t="n">
-        <v>9.52</v>
+        <v>8.41</v>
       </c>
       <c r="G16" t="n">
-        <v>305.8</v>
+        <v>297.7</v>
       </c>
       <c r="H16" t="n">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>32.3</v>
+        <v>-65.95</v>
       </c>
       <c r="K16" t="n">
-        <v>49.43</v>
+        <v>-39.46</v>
       </c>
       <c r="L16" t="n">
-        <v>59.04</v>
+        <v>76.86</v>
       </c>
     </row>
     <row r="17">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="F17" t="n">
-        <v>9.27</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>292.6</v>
+        <v>300.1</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>91.8</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>50.74</v>
+        <v>-42.55</v>
       </c>
       <c r="K17" t="n">
-        <v>-89.73</v>
+        <v>64.84</v>
       </c>
       <c r="L17" t="n">
-        <v>103.08</v>
+        <v>77.55</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:46:59</t>
+          <t>06:47:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="F18" t="n">
-        <v>9.35</v>
+        <v>7.28</v>
       </c>
       <c r="G18" t="n">
-        <v>290.9</v>
+        <v>303.6</v>
       </c>
       <c r="H18" t="n">
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-67.23999999999999</v>
+        <v>-20.12</v>
       </c>
       <c r="K18" t="n">
-        <v>24.32</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>71.5</v>
+        <v>93.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:49:19</t>
+          <t>06:48:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.61</v>
+        <v>3.82</v>
       </c>
       <c r="F19" t="n">
-        <v>9.92</v>
+        <v>9.33</v>
       </c>
       <c r="G19" t="n">
-        <v>298.5</v>
+        <v>308</v>
       </c>
       <c r="H19" t="n">
-        <v>97.2</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-90.78</v>
+        <v>16.72</v>
       </c>
       <c r="K19" t="n">
-        <v>42.79</v>
+        <v>-30.64</v>
       </c>
       <c r="L19" t="n">
-        <v>100.36</v>
+        <v>34.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:55:09</t>
+          <t>06:52:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.4</v>
+        <v>3.93</v>
       </c>
       <c r="F20" t="n">
-        <v>9.56</v>
+        <v>9.01</v>
       </c>
       <c r="G20" t="n">
-        <v>302.1</v>
+        <v>295.3</v>
       </c>
       <c r="H20" t="n">
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>89.67</v>
+        <v>-140.87</v>
       </c>
       <c r="K20" t="n">
-        <v>-48.15</v>
+        <v>-95.81999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>101.78</v>
+        <v>170.37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:56:09</t>
+          <t>06:54:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.81</v>
+        <v>3.17</v>
       </c>
       <c r="F21" t="n">
-        <v>9.07</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>290.2</v>
+        <v>305.6</v>
       </c>
       <c r="H21" t="n">
-        <v>97.5</v>
+        <v>93.5</v>
       </c>
       <c r="I21" t="n">
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>50.44</v>
+        <v>-105.91</v>
       </c>
       <c r="K21" t="n">
-        <v>144.72</v>
+        <v>37</v>
       </c>
       <c r="L21" t="n">
-        <v>153.26</v>
+        <v>112.19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:57:34</t>
+          <t>06:56:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.17</v>
+        <v>3.13</v>
       </c>
       <c r="F22" t="n">
-        <v>9.32</v>
+        <v>5.44</v>
       </c>
       <c r="G22" t="n">
-        <v>311.2</v>
+        <v>287.3</v>
       </c>
       <c r="H22" t="n">
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>-170.34</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>27.31</v>
+        <v>-80.53</v>
       </c>
       <c r="L22" t="n">
-        <v>172.52</v>
+        <v>123.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:02:22</t>
+          <t>07:02:05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="F23" t="n">
-        <v>9.19</v>
+        <v>7.24</v>
       </c>
       <c r="G23" t="n">
-        <v>308</v>
+        <v>303.4</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-225.93</v>
+        <v>-180.79</v>
       </c>
       <c r="K23" t="n">
-        <v>-18.85</v>
+        <v>-47.17</v>
       </c>
       <c r="L23" t="n">
-        <v>226.71</v>
+        <v>186.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:04:46</t>
+          <t>07:03:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.6</v>
+        <v>4.09</v>
       </c>
       <c r="F24" t="n">
-        <v>9.07</v>
+        <v>8.93</v>
       </c>
       <c r="G24" t="n">
-        <v>296.2</v>
+        <v>290.5</v>
       </c>
       <c r="H24" t="n">
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>131.53</v>
+        <v>-88.5</v>
       </c>
       <c r="K24" t="n">
-        <v>91.41</v>
+        <v>-128.36</v>
       </c>
       <c r="L24" t="n">
-        <v>160.18</v>
+        <v>155.91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:05:55</t>
+          <t>07:05:46</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.74</v>
+        <v>3.91</v>
       </c>
       <c r="F25" t="n">
-        <v>9.31</v>
+        <v>9.44</v>
       </c>
       <c r="G25" t="n">
-        <v>301</v>
+        <v>309.3</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-136.7</v>
+        <v>-123.69</v>
       </c>
       <c r="K25" t="n">
-        <v>88.34999999999999</v>
+        <v>170.88</v>
       </c>
       <c r="L25" t="n">
-        <v>162.77</v>
+        <v>210.95</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:10:39</t>
+          <t>07:11:55</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.97</v>
+        <v>3.71</v>
       </c>
       <c r="F26" t="n">
-        <v>9.25</v>
+        <v>6.79</v>
       </c>
       <c r="G26" t="n">
-        <v>275.4</v>
+        <v>284.4</v>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>-89.18000000000001</v>
+        <v>-101.4</v>
       </c>
       <c r="K26" t="n">
-        <v>-252.24</v>
+        <v>-250.44</v>
       </c>
       <c r="L26" t="n">
-        <v>267.54</v>
+        <v>270.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:13:12</t>
+          <t>07:13:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.48</v>
+        <v>3.64</v>
       </c>
       <c r="F27" t="n">
-        <v>9.02</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>299.4</v>
+        <v>296.6</v>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-202.03</v>
+        <v>176.91</v>
       </c>
       <c r="K27" t="n">
-        <v>164.59</v>
+        <v>-221.36</v>
       </c>
       <c r="L27" t="n">
-        <v>260.59</v>
+        <v>283.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:15:13</t>
+          <t>07:16:10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.05</v>
+        <v>4.31</v>
       </c>
       <c r="F28" t="n">
-        <v>10.02</v>
+        <v>8.07</v>
       </c>
       <c r="G28" t="n">
-        <v>292.9</v>
+        <v>293.4</v>
       </c>
       <c r="H28" t="n">
-        <v>98.40000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>266.76</v>
+        <v>-74.02</v>
       </c>
       <c r="K28" t="n">
-        <v>8.32</v>
+        <v>-290.63</v>
       </c>
       <c r="L28" t="n">
-        <v>266.89</v>
+        <v>299.91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:26:29</t>
+          <t>07:26:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.52</v>
+        <v>3.21</v>
       </c>
       <c r="F29" t="n">
-        <v>9.01</v>
+        <v>4.75</v>
       </c>
       <c r="G29" t="n">
-        <v>300.6</v>
+        <v>292.8</v>
       </c>
       <c r="H29" t="n">
-        <v>94.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-19.91</v>
+        <v>3.62</v>
       </c>
       <c r="K29" t="n">
-        <v>-88.61</v>
+        <v>51.52</v>
       </c>
       <c r="L29" t="n">
-        <v>90.81999999999999</v>
+        <v>51.64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:28:46</t>
+          <t>07:28:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="F30" t="n">
-        <v>9.52</v>
+        <v>7.89</v>
       </c>
       <c r="G30" t="n">
-        <v>315.8</v>
+        <v>307.1</v>
       </c>
       <c r="H30" t="n">
-        <v>96.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-88.01000000000001</v>
+        <v>-35.13</v>
       </c>
       <c r="K30" t="n">
-        <v>-31.12</v>
+        <v>-61.38</v>
       </c>
       <c r="L30" t="n">
-        <v>93.34999999999999</v>
+        <v>70.72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:30:41</t>
+          <t>07:29:58</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="F31" t="n">
-        <v>9.27</v>
+        <v>8.58</v>
       </c>
       <c r="G31" t="n">
-        <v>297.5</v>
+        <v>303.7</v>
       </c>
       <c r="H31" t="n">
-        <v>95.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-62.55</v>
+        <v>-21.47</v>
       </c>
       <c r="K31" t="n">
-        <v>-24.16</v>
+        <v>-66.04000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>67.05</v>
+        <v>69.44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:35:19</t>
+          <t>07:34:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.84</v>
+        <v>4.15</v>
       </c>
       <c r="F32" t="n">
-        <v>9.460000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>301.7</v>
+        <v>313.4</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>75.87</v>
+        <v>47.65</v>
       </c>
       <c r="K32" t="n">
-        <v>-21.16</v>
+        <v>-125.01</v>
       </c>
       <c r="L32" t="n">
-        <v>78.76000000000001</v>
+        <v>133.79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:38:02</t>
+          <t>07:36:58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.52</v>
+        <v>3.99</v>
       </c>
       <c r="F33" t="n">
-        <v>9.59</v>
+        <v>9.81</v>
       </c>
       <c r="G33" t="n">
-        <v>284.7</v>
+        <v>300</v>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="I33" t="n">
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>67.72</v>
+        <v>-95.45999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>28.77</v>
+        <v>-26.27</v>
       </c>
       <c r="L33" t="n">
-        <v>73.58</v>
+        <v>99.01000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:39:19</t>
+          <t>07:37:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.76</v>
+        <v>3.98</v>
       </c>
       <c r="F34" t="n">
-        <v>9.380000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="G34" t="n">
-        <v>293.5</v>
+        <v>302.9</v>
       </c>
       <c r="H34" t="n">
-        <v>99</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I34" t="n">
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-64.87</v>
+        <v>14.14</v>
       </c>
       <c r="K34" t="n">
-        <v>-63.12</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>90.51000000000001</v>
+        <v>98.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:43:52</t>
+          <t>07:42:49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.54</v>
+        <v>3.97</v>
       </c>
       <c r="F35" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>307.5</v>
+        <v>317.5</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>66.84</v>
+        <v>-119.6</v>
       </c>
       <c r="K35" t="n">
-        <v>-10.96</v>
+        <v>88.39</v>
       </c>
       <c r="L35" t="n">
-        <v>67.73</v>
+        <v>148.72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:45:46</t>
+          <t>07:43:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.8</v>
+        <v>4.03</v>
       </c>
       <c r="F36" t="n">
-        <v>9.67</v>
+        <v>10.83</v>
       </c>
       <c r="G36" t="n">
-        <v>294.5</v>
+        <v>290.9</v>
       </c>
       <c r="H36" t="n">
-        <v>98.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-122.52</v>
+        <v>51.29</v>
       </c>
       <c r="K36" t="n">
-        <v>95.51000000000001</v>
+        <v>-153.1</v>
       </c>
       <c r="L36" t="n">
-        <v>155.35</v>
+        <v>161.46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:47:18</t>
+          <t>07:45:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
       <c r="F37" t="n">
-        <v>10.21</v>
+        <v>10.34</v>
       </c>
       <c r="G37" t="n">
-        <v>289.7</v>
+        <v>299.6</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-10.08</v>
+        <v>66.88</v>
       </c>
       <c r="K37" t="n">
-        <v>161.1</v>
+        <v>120.28</v>
       </c>
       <c r="L37" t="n">
-        <v>161.42</v>
+        <v>137.62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:51:45</t>
+          <t>07:51:11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="F38" t="n">
-        <v>9.69</v>
+        <v>9.4</v>
       </c>
       <c r="G38" t="n">
-        <v>304.5</v>
+        <v>289.1</v>
       </c>
       <c r="H38" t="n">
-        <v>97.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-155.9</v>
+        <v>20.63</v>
       </c>
       <c r="K38" t="n">
-        <v>36.59</v>
+        <v>-272.29</v>
       </c>
       <c r="L38" t="n">
-        <v>160.13</v>
+        <v>273.07</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:53:34</t>
+          <t>07:53:22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,13 +1675,13 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.97</v>
+        <v>4.05</v>
       </c>
       <c r="F39" t="n">
-        <v>9.58</v>
+        <v>10.92</v>
       </c>
       <c r="G39" t="n">
-        <v>279</v>
+        <v>296.6</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
@@ -1690,19 +1690,19 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>178.21</v>
+        <v>140.26</v>
       </c>
       <c r="K39" t="n">
-        <v>-72.06999999999999</v>
+        <v>-104.85</v>
       </c>
       <c r="L39" t="n">
-        <v>192.23</v>
+        <v>175.12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:54:13</t>
+          <t>07:55:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.74</v>
+        <v>4.3</v>
       </c>
       <c r="F40" t="n">
-        <v>9.9</v>
+        <v>10.38</v>
       </c>
       <c r="G40" t="n">
-        <v>296.1</v>
+        <v>305.1</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>25.81</v>
+        <v>-170.83</v>
       </c>
       <c r="K40" t="n">
-        <v>187.73</v>
+        <v>-179.98</v>
       </c>
       <c r="L40" t="n">
-        <v>189.49</v>
+        <v>248.14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:58:54</t>
+          <t>08:00:31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.22</v>
+        <v>3.72</v>
       </c>
       <c r="F41" t="n">
-        <v>9.76</v>
+        <v>9.35</v>
       </c>
       <c r="G41" t="n">
-        <v>291.8</v>
+        <v>305.9</v>
       </c>
       <c r="H41" t="n">
-        <v>94.5</v>
+        <v>95.5</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-22.81</v>
+        <v>125.94</v>
       </c>
       <c r="K41" t="n">
-        <v>-263.22</v>
+        <v>466.39</v>
       </c>
       <c r="L41" t="n">
-        <v>264.2</v>
+        <v>483.09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:00:13</t>
+          <t>08:02:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.25</v>
+        <v>4.14</v>
       </c>
       <c r="F42" t="n">
-        <v>9.65</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>322.7</v>
+        <v>295</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-118.44</v>
+        <v>-286.32</v>
       </c>
       <c r="K42" t="n">
-        <v>-314.2</v>
+        <v>299.28</v>
       </c>
       <c r="L42" t="n">
-        <v>335.78</v>
+        <v>414.18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:02:18</t>
+          <t>08:03:37</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.85</v>
+        <v>4.12</v>
       </c>
       <c r="F43" t="n">
-        <v>9.65</v>
+        <v>9.17</v>
       </c>
       <c r="G43" t="n">
-        <v>302</v>
+        <v>299.5</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>-74.09999999999999</v>
+        <v>-234.09</v>
       </c>
       <c r="K43" t="n">
-        <v>236.55</v>
+        <v>-62.46</v>
       </c>
       <c r="L43" t="n">
-        <v>247.89</v>
+        <v>242.28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:13:13</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.06</v>
+        <v>3.66</v>
       </c>
       <c r="F44" t="n">
-        <v>8.94</v>
+        <v>8.23</v>
       </c>
       <c r="G44" t="n">
-        <v>297.1</v>
+        <v>289.5</v>
       </c>
       <c r="H44" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-49.37</v>
+        <v>0.5</v>
       </c>
       <c r="K44" t="n">
-        <v>12.01</v>
+        <v>-115.18</v>
       </c>
       <c r="L44" t="n">
-        <v>50.81</v>
+        <v>115.18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:14:19</t>
+          <t>08:17:43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.69</v>
+        <v>3.81</v>
       </c>
       <c r="F45" t="n">
-        <v>9.66</v>
+        <v>9.51</v>
       </c>
       <c r="G45" t="n">
-        <v>292.5</v>
+        <v>308</v>
       </c>
       <c r="H45" t="n">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-75.87</v>
+        <v>-21.04</v>
       </c>
       <c r="K45" t="n">
-        <v>10.87</v>
+        <v>-68.79000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>76.64</v>
+        <v>71.94</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:17:06</t>
+          <t>08:19:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.4</v>
+        <v>3.91</v>
       </c>
       <c r="F46" t="n">
-        <v>9.25</v>
+        <v>9.48</v>
       </c>
       <c r="G46" t="n">
-        <v>296.1</v>
+        <v>300.9</v>
       </c>
       <c r="H46" t="n">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>16.37</v>
+        <v>5.17</v>
       </c>
       <c r="K46" t="n">
-        <v>63.51</v>
+        <v>81.45</v>
       </c>
       <c r="L46" t="n">
-        <v>65.58</v>
+        <v>81.61</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:22:23</t>
+          <t>08:24:24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.15</v>
+        <v>4.38</v>
       </c>
       <c r="F47" t="n">
-        <v>9.18</v>
+        <v>7.81</v>
       </c>
       <c r="G47" t="n">
-        <v>306.8</v>
+        <v>286.1</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>105.09</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>20.09</v>
+        <v>-29.04</v>
       </c>
       <c r="L47" t="n">
-        <v>106.99</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:23:58</t>
+          <t>08:25:42</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.6</v>
+        <v>3.97</v>
       </c>
       <c r="F48" t="n">
-        <v>9.300000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="G48" t="n">
-        <v>297.6</v>
+        <v>301.5</v>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-73.3</v>
+        <v>35.99</v>
       </c>
       <c r="K48" t="n">
-        <v>-52.46</v>
+        <v>84.19</v>
       </c>
       <c r="L48" t="n">
-        <v>90.13</v>
+        <v>91.56</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:25:45</t>
+          <t>08:26:58</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2098,31 +2098,31 @@
         <v>4.19</v>
       </c>
       <c r="F49" t="n">
-        <v>9.699999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>301.4</v>
+        <v>301.5</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>2.94</v>
+        <v>84.22</v>
       </c>
       <c r="K49" t="n">
-        <v>21.15</v>
+        <v>17.88</v>
       </c>
       <c r="L49" t="n">
-        <v>21.35</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:31:45</t>
+          <t>08:32:50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.21</v>
+        <v>3.91</v>
       </c>
       <c r="F50" t="n">
-        <v>9.18</v>
+        <v>9.25</v>
       </c>
       <c r="G50" t="n">
-        <v>300.2</v>
+        <v>317.5</v>
       </c>
       <c r="H50" t="n">
         <v>100</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-42.13</v>
+        <v>30.43</v>
       </c>
       <c r="K50" t="n">
-        <v>87.89</v>
+        <v>145.98</v>
       </c>
       <c r="L50" t="n">
-        <v>97.45999999999999</v>
+        <v>149.12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:33:27</t>
+          <t>08:33:53</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.83</v>
+        <v>4.19</v>
       </c>
       <c r="F51" t="n">
-        <v>10.44</v>
+        <v>9.43</v>
       </c>
       <c r="G51" t="n">
-        <v>300.6</v>
+        <v>297</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I51" t="n">
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>37.52</v>
+        <v>112.03</v>
       </c>
       <c r="K51" t="n">
-        <v>-124.9</v>
+        <v>79.25</v>
       </c>
       <c r="L51" t="n">
-        <v>130.42</v>
+        <v>137.23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:36:17</t>
+          <t>08:34:49</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.06</v>
+        <v>4.54</v>
       </c>
       <c r="F52" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="G52" t="n">
-        <v>302.4</v>
+        <v>303</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
       </c>
       <c r="I52" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-32.16</v>
+        <v>-121.39</v>
       </c>
       <c r="K52" t="n">
-        <v>212.93</v>
+        <v>-103.34</v>
       </c>
       <c r="L52" t="n">
-        <v>215.34</v>
+        <v>159.42</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:40:57</t>
+          <t>08:39:44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.3</v>
+        <v>4.46</v>
       </c>
       <c r="F53" t="n">
-        <v>9.35</v>
+        <v>10.82</v>
       </c>
       <c r="G53" t="n">
-        <v>307.3</v>
+        <v>293</v>
       </c>
       <c r="H53" t="n">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>-37.53</v>
+        <v>-35.85</v>
       </c>
       <c r="K53" t="n">
-        <v>163.64</v>
+        <v>188.63</v>
       </c>
       <c r="L53" t="n">
-        <v>167.89</v>
+        <v>192.01</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:42:06</t>
+          <t>08:41:10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.93</v>
+        <v>4.29</v>
       </c>
       <c r="F54" t="n">
-        <v>9.630000000000001</v>
+        <v>10.92</v>
       </c>
       <c r="G54" t="n">
-        <v>304.6</v>
+        <v>295.6</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I54" t="n">
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>106.41</v>
+        <v>171.2</v>
       </c>
       <c r="K54" t="n">
-        <v>-126.13</v>
+        <v>146.77</v>
       </c>
       <c r="L54" t="n">
-        <v>165.03</v>
+        <v>225.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:43:07</t>
+          <t>08:42:56</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.03</v>
+        <v>4.38</v>
       </c>
       <c r="F55" t="n">
-        <v>9.75</v>
+        <v>10.92</v>
       </c>
       <c r="G55" t="n">
-        <v>310.2</v>
+        <v>294.9</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>105.09</v>
+        <v>-226.54</v>
       </c>
       <c r="K55" t="n">
-        <v>269.66</v>
+        <v>-20.64</v>
       </c>
       <c r="L55" t="n">
-        <v>289.41</v>
+        <v>227.48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:47:47</t>
+          <t>08:48:31</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.69</v>
+        <v>3.84</v>
       </c>
       <c r="F56" t="n">
-        <v>9.07</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>293</v>
+        <v>303.9</v>
       </c>
       <c r="H56" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-243.61</v>
+        <v>-111.15</v>
       </c>
       <c r="K56" t="n">
-        <v>71.48</v>
+        <v>369.38</v>
       </c>
       <c r="L56" t="n">
-        <v>253.88</v>
+        <v>385.74</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:50:13</t>
+          <t>08:50:16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.23</v>
+        <v>4.29</v>
       </c>
       <c r="F57" t="n">
-        <v>10.35</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>296.8</v>
+        <v>298.8</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-338.65</v>
+        <v>322.76</v>
       </c>
       <c r="K57" t="n">
-        <v>-150.2</v>
+        <v>144.17</v>
       </c>
       <c r="L57" t="n">
-        <v>370.47</v>
+        <v>353.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:52:22</t>
+          <t>08:51:39</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.7</v>
+        <v>4.44</v>
       </c>
       <c r="F58" t="n">
-        <v>10.3</v>
+        <v>9.27</v>
       </c>
       <c r="G58" t="n">
-        <v>296.1</v>
+        <v>301.2</v>
       </c>
       <c r="H58" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>133.47</v>
+        <v>-238.16</v>
       </c>
       <c r="K58" t="n">
-        <v>-201.9</v>
+        <v>100.87</v>
       </c>
       <c r="L58" t="n">
-        <v>242.03</v>
+        <v>258.64</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:03:46</t>
+          <t>09:02:37</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="F59" t="n">
-        <v>9.51</v>
+        <v>9.4</v>
       </c>
       <c r="G59" t="n">
-        <v>298.4</v>
+        <v>304.6</v>
       </c>
       <c r="H59" t="n">
-        <v>92.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-59.23</v>
+        <v>-42.2</v>
       </c>
       <c r="K59" t="n">
-        <v>-37.1</v>
+        <v>-52.99</v>
       </c>
       <c r="L59" t="n">
-        <v>69.89</v>
+        <v>67.73</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:05:09</t>
+          <t>09:03:42</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="F60" t="n">
-        <v>9.380000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="G60" t="n">
-        <v>308.4</v>
+        <v>307.6</v>
       </c>
       <c r="H60" t="n">
         <v>100</v>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>37.05</v>
+        <v>95.48</v>
       </c>
       <c r="K60" t="n">
-        <v>56.5</v>
+        <v>-45.82</v>
       </c>
       <c r="L60" t="n">
-        <v>67.56</v>
+        <v>105.91</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:06:41</t>
+          <t>09:05:59</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.15</v>
+        <v>4.28</v>
       </c>
       <c r="F61" t="n">
-        <v>9.15</v>
+        <v>10.23</v>
       </c>
       <c r="G61" t="n">
-        <v>314</v>
+        <v>300.5</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.16</v>
+        <v>4.08</v>
       </c>
       <c r="K61" t="n">
-        <v>-8.26</v>
+        <v>-81</v>
       </c>
       <c r="L61" t="n">
-        <v>8.34</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:11:21</t>
+          <t>09:11:32</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.1</v>
+        <v>4.61</v>
       </c>
       <c r="F62" t="n">
-        <v>9.529999999999999</v>
+        <v>10.92</v>
       </c>
       <c r="G62" t="n">
-        <v>293.7</v>
+        <v>302</v>
       </c>
       <c r="H62" t="n">
         <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>-84.8</v>
+        <v>-84.79000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>18.84</v>
+        <v>-88.44</v>
       </c>
       <c r="L62" t="n">
-        <v>86.86</v>
+        <v>122.51</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:12:57</t>
+          <t>09:13:46</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.35</v>
+        <v>4.78</v>
       </c>
       <c r="F63" t="n">
-        <v>9.07</v>
+        <v>10.16</v>
       </c>
       <c r="G63" t="n">
-        <v>303.7</v>
+        <v>292.6</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>101.04</v>
+        <v>94.5</v>
       </c>
       <c r="K63" t="n">
-        <v>-58.71</v>
+        <v>-64.19</v>
       </c>
       <c r="L63" t="n">
-        <v>116.86</v>
+        <v>114.24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:14:15</t>
+          <t>09:15:09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.99</v>
+        <v>3.88</v>
       </c>
       <c r="F64" t="n">
-        <v>9.380000000000001</v>
+        <v>10.14</v>
       </c>
       <c r="G64" t="n">
-        <v>292.6</v>
+        <v>287.1</v>
       </c>
       <c r="H64" t="n">
-        <v>99.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="I64" t="n">
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-52.28</v>
+        <v>-12.43</v>
       </c>
       <c r="K64" t="n">
-        <v>-84.43000000000001</v>
+        <v>100.74</v>
       </c>
       <c r="L64" t="n">
-        <v>99.3</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:18:42</t>
+          <t>09:20:02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.61</v>
+        <v>4.01</v>
       </c>
       <c r="F65" t="n">
-        <v>9.48</v>
+        <v>10.74</v>
       </c>
       <c r="G65" t="n">
-        <v>293.8</v>
+        <v>290.3</v>
       </c>
       <c r="H65" t="n">
-        <v>93.7</v>
+        <v>100</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-141.61</v>
+        <v>2.16</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.81</v>
+        <v>165.85</v>
       </c>
       <c r="L65" t="n">
-        <v>141.7</v>
+        <v>165.86</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:19:47</t>
+          <t>09:21:20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="F66" t="n">
-        <v>9.630000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>290.3</v>
+        <v>298.2</v>
       </c>
       <c r="H66" t="n">
         <v>100</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>127.81</v>
+        <v>90.17</v>
       </c>
       <c r="K66" t="n">
-        <v>76.89</v>
+        <v>122.25</v>
       </c>
       <c r="L66" t="n">
-        <v>149.15</v>
+        <v>151.91</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:22:06</t>
+          <t>09:23:14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.61</v>
+        <v>4.27</v>
       </c>
       <c r="F67" t="n">
-        <v>9.82</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>303.6</v>
+        <v>304.9</v>
       </c>
       <c r="H67" t="n">
-        <v>99.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-25.01</v>
+        <v>-7.16</v>
       </c>
       <c r="K67" t="n">
-        <v>-155.92</v>
+        <v>-235.21</v>
       </c>
       <c r="L67" t="n">
-        <v>157.91</v>
+        <v>235.32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:26:16</t>
+          <t>09:27:25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.55</v>
+        <v>3.96</v>
       </c>
       <c r="F68" t="n">
-        <v>9.550000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="G68" t="n">
-        <v>307.1</v>
+        <v>309.7</v>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-159.36</v>
+        <v>162.78</v>
       </c>
       <c r="K68" t="n">
-        <v>224.3</v>
+        <v>108.73</v>
       </c>
       <c r="L68" t="n">
-        <v>275.15</v>
+        <v>195.75</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:28:11</t>
+          <t>09:29:22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,13 +2935,13 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.18</v>
+        <v>4.49</v>
       </c>
       <c r="F69" t="n">
-        <v>9.609999999999999</v>
+        <v>10.92</v>
       </c>
       <c r="G69" t="n">
-        <v>308.6</v>
+        <v>287.2</v>
       </c>
       <c r="H69" t="n">
         <v>100</v>
@@ -2950,19 +2950,19 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>45.16</v>
+        <v>114.87</v>
       </c>
       <c r="K69" t="n">
-        <v>147.88</v>
+        <v>199.82</v>
       </c>
       <c r="L69" t="n">
-        <v>154.62</v>
+        <v>230.48</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:30:02</t>
+          <t>09:30:13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.05</v>
+        <v>4.23</v>
       </c>
       <c r="F70" t="n">
-        <v>9.960000000000001</v>
+        <v>10.92</v>
       </c>
       <c r="G70" t="n">
-        <v>303.4</v>
+        <v>293.8</v>
       </c>
       <c r="H70" t="n">
-        <v>93.7</v>
+        <v>100</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-94.89</v>
+        <v>-171.15</v>
       </c>
       <c r="K70" t="n">
-        <v>206.58</v>
+        <v>-83.73</v>
       </c>
       <c r="L70" t="n">
-        <v>227.33</v>
+        <v>190.53</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:34:30</t>
+          <t>09:33:47</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="F71" t="n">
-        <v>9.300000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>297.4</v>
+        <v>315.3</v>
       </c>
       <c r="H71" t="n">
         <v>98</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>-494.02</v>
+        <v>259.1</v>
       </c>
       <c r="K71" t="n">
-        <v>-54.86</v>
+        <v>140.05</v>
       </c>
       <c r="L71" t="n">
-        <v>497.06</v>
+        <v>294.52</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:36:11</t>
+          <t>09:35:37</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.49</v>
+        <v>4.62</v>
       </c>
       <c r="F72" t="n">
-        <v>10.02</v>
+        <v>10.92</v>
       </c>
       <c r="G72" t="n">
-        <v>299.9</v>
+        <v>303.8</v>
       </c>
       <c r="H72" t="n">
         <v>100</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>208.58</v>
+        <v>-233.27</v>
       </c>
       <c r="K72" t="n">
-        <v>127.96</v>
+        <v>235.83</v>
       </c>
       <c r="L72" t="n">
-        <v>244.71</v>
+        <v>331.71</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:37:55</t>
+          <t>09:36:53</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.8</v>
+        <v>5.06</v>
       </c>
       <c r="F73" t="n">
-        <v>9.66</v>
+        <v>10.92</v>
       </c>
       <c r="G73" t="n">
-        <v>297.5</v>
+        <v>299.9</v>
       </c>
       <c r="H73" t="n">
         <v>100</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-191.39</v>
+        <v>42.64</v>
       </c>
       <c r="K73" t="n">
-        <v>210.76</v>
+        <v>-506.85</v>
       </c>
       <c r="L73" t="n">
-        <v>284.7</v>
+        <v>508.65</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:46:54</t>
+          <t>09:47:31</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.79</v>
+        <v>4.86</v>
       </c>
       <c r="F74" t="n">
-        <v>9.710000000000001</v>
+        <v>10.92</v>
       </c>
       <c r="G74" t="n">
-        <v>280.7</v>
+        <v>287.4</v>
       </c>
       <c r="H74" t="n">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>86.43000000000001</v>
+        <v>-13.95</v>
       </c>
       <c r="K74" t="n">
-        <v>10.6</v>
+        <v>-70.73</v>
       </c>
       <c r="L74" t="n">
-        <v>87.08</v>
+        <v>72.09</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:48:10</t>
+          <t>09:49:36</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.72</v>
+        <v>4.44</v>
       </c>
       <c r="F75" t="n">
-        <v>9.300000000000001</v>
+        <v>10.92</v>
       </c>
       <c r="G75" t="n">
-        <v>299.5</v>
+        <v>311.6</v>
       </c>
       <c r="H75" t="n">
         <v>100</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>126.51</v>
+        <v>-117.15</v>
       </c>
       <c r="K75" t="n">
-        <v>39.37</v>
+        <v>-8.41</v>
       </c>
       <c r="L75" t="n">
-        <v>132.49</v>
+        <v>117.45</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:49:53</t>
+          <t>09:51:04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.74</v>
+        <v>4.67</v>
       </c>
       <c r="F76" t="n">
-        <v>8.68</v>
+        <v>10.92</v>
       </c>
       <c r="G76" t="n">
-        <v>298.3</v>
+        <v>311.8</v>
       </c>
       <c r="H76" t="n">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>54.16</v>
+        <v>53.56</v>
       </c>
       <c r="K76" t="n">
-        <v>-66.11</v>
+        <v>58.41</v>
       </c>
       <c r="L76" t="n">
-        <v>85.47</v>
+        <v>79.25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:54:26</t>
+          <t>09:56:09</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.38</v>
+        <v>4.42</v>
       </c>
       <c r="F77" t="n">
-        <v>9.75</v>
+        <v>9.31</v>
       </c>
       <c r="G77" t="n">
-        <v>305</v>
+        <v>302.4</v>
       </c>
       <c r="H77" t="n">
         <v>100</v>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>12.52</v>
+        <v>95.16</v>
       </c>
       <c r="K77" t="n">
-        <v>-94.18000000000001</v>
+        <v>104.89</v>
       </c>
       <c r="L77" t="n">
-        <v>95.01000000000001</v>
+        <v>141.63</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:56:45</t>
+          <t>09:58:02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,13 +3313,13 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.77</v>
+        <v>4.14</v>
       </c>
       <c r="F78" t="n">
-        <v>10.13</v>
+        <v>10.92</v>
       </c>
       <c r="G78" t="n">
-        <v>309.5</v>
+        <v>311.6</v>
       </c>
       <c r="H78" t="n">
         <v>100</v>
@@ -3328,19 +3328,19 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-87.5</v>
+        <v>-51.29</v>
       </c>
       <c r="K78" t="n">
-        <v>-27.32</v>
+        <v>-89.81</v>
       </c>
       <c r="L78" t="n">
-        <v>91.66</v>
+        <v>103.42</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:58:31</t>
+          <t>10:00:25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.59</v>
+        <v>4.69</v>
       </c>
       <c r="F79" t="n">
-        <v>9.15</v>
+        <v>10.92</v>
       </c>
       <c r="G79" t="n">
-        <v>296.7</v>
+        <v>297</v>
       </c>
       <c r="H79" t="n">
         <v>100</v>
       </c>
       <c r="I79" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-96.66</v>
+        <v>48.2</v>
       </c>
       <c r="K79" t="n">
-        <v>-17.89</v>
+        <v>-77.81999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>98.3</v>
+        <v>91.53</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:02:41</t>
+          <t>10:05:56</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="F80" t="n">
-        <v>9.699999999999999</v>
+        <v>10.76</v>
       </c>
       <c r="G80" t="n">
-        <v>280.3</v>
+        <v>287.5</v>
       </c>
       <c r="H80" t="n">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>-14.54</v>
+        <v>84.14</v>
       </c>
       <c r="K80" t="n">
-        <v>-15.18</v>
+        <v>-106.03</v>
       </c>
       <c r="L80" t="n">
-        <v>21.02</v>
+        <v>135.36</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:04:31</t>
+          <t>10:06:57</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.37</v>
+        <v>3.97</v>
       </c>
       <c r="F81" t="n">
-        <v>9.25</v>
+        <v>10.92</v>
       </c>
       <c r="G81" t="n">
-        <v>305.3</v>
+        <v>305.4</v>
       </c>
       <c r="H81" t="n">
-        <v>97.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>63.23</v>
+        <v>19.56</v>
       </c>
       <c r="K81" t="n">
-        <v>129.05</v>
+        <v>-133.05</v>
       </c>
       <c r="L81" t="n">
-        <v>143.71</v>
+        <v>134.48</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:05:57</t>
+          <t>10:07:50</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.45</v>
+        <v>4.11</v>
       </c>
       <c r="F82" t="n">
-        <v>9.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="G82" t="n">
-        <v>286.5</v>
+        <v>304.5</v>
       </c>
       <c r="H82" t="n">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-144.3</v>
+        <v>120.65</v>
       </c>
       <c r="K82" t="n">
-        <v>-46.87</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>151.72</v>
+        <v>137.69</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:11:09</t>
+          <t>10:13:18</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.42</v>
+        <v>4.27</v>
       </c>
       <c r="F83" t="n">
-        <v>9.609999999999999</v>
+        <v>10.92</v>
       </c>
       <c r="G83" t="n">
-        <v>307.6</v>
+        <v>302.1</v>
       </c>
       <c r="H83" t="n">
-        <v>98.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-120.71</v>
+        <v>-318.46</v>
       </c>
       <c r="K83" t="n">
-        <v>-187.74</v>
+        <v>-37.96</v>
       </c>
       <c r="L83" t="n">
-        <v>223.19</v>
+        <v>320.71</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:12:18</t>
+          <t>10:14:06</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.57</v>
+        <v>4.21</v>
       </c>
       <c r="F84" t="n">
-        <v>9.140000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>295.5</v>
+        <v>308.7</v>
       </c>
       <c r="H84" t="n">
-        <v>90.5</v>
+        <v>94.2</v>
       </c>
       <c r="I84" t="n">
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-209.34</v>
+        <v>-180.13</v>
       </c>
       <c r="K84" t="n">
-        <v>-154.46</v>
+        <v>-65.09</v>
       </c>
       <c r="L84" t="n">
-        <v>260.16</v>
+        <v>191.53</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:13:18</t>
+          <t>10:15:22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="F85" t="n">
-        <v>8.57</v>
+        <v>9.08</v>
       </c>
       <c r="G85" t="n">
-        <v>304.7</v>
+        <v>296.3</v>
       </c>
       <c r="H85" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-57.98</v>
+        <v>96.11</v>
       </c>
       <c r="K85" t="n">
-        <v>224.19</v>
+        <v>283.18</v>
       </c>
       <c r="L85" t="n">
-        <v>231.57</v>
+        <v>299.05</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:18:41</t>
+          <t>10:19:26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="F86" t="n">
-        <v>9.27</v>
+        <v>10.92</v>
       </c>
       <c r="G86" t="n">
-        <v>316.7</v>
+        <v>308</v>
       </c>
       <c r="H86" t="n">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>296.9</v>
+        <v>-159.49</v>
       </c>
       <c r="K86" t="n">
-        <v>-242.15</v>
+        <v>2.73</v>
       </c>
       <c r="L86" t="n">
-        <v>383.13</v>
+        <v>159.51</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:20:31</t>
+          <t>10:21:23</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.81</v>
+        <v>4.21</v>
       </c>
       <c r="F87" t="n">
-        <v>9.109999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>292.1</v>
+        <v>307.8</v>
       </c>
       <c r="H87" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>277.05</v>
+        <v>-74.3</v>
       </c>
       <c r="K87" t="n">
-        <v>-14.51</v>
+        <v>246.62</v>
       </c>
       <c r="L87" t="n">
-        <v>277.43</v>
+        <v>257.57</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:22:56</t>
+          <t>10:23:23</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.53</v>
+        <v>4.21</v>
       </c>
       <c r="F88" t="n">
-        <v>9.83</v>
+        <v>10.92</v>
       </c>
       <c r="G88" t="n">
-        <v>305.7</v>
+        <v>296.8</v>
       </c>
       <c r="H88" t="n">
-        <v>96.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-219.37</v>
+        <v>112.16</v>
       </c>
       <c r="K88" t="n">
-        <v>-129.11</v>
+        <v>272.14</v>
       </c>
       <c r="L88" t="n">
-        <v>254.54</v>
+        <v>294.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-04.xlsx
+++ b/output/2024-04-04.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>73.17</v>
+        <v>77.09</v>
       </c>
       <c r="K14" t="n">
-        <v>40.87</v>
+        <v>43.06</v>
       </c>
       <c r="L14" t="n">
-        <v>83.81</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="K15" t="n">
-        <v>-84.55</v>
+        <v>-96.15000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>84.56</v>
+        <v>96.16</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-65.95</v>
+        <v>-69.5</v>
       </c>
       <c r="K16" t="n">
-        <v>-39.46</v>
+        <v>-41.58</v>
       </c>
       <c r="L16" t="n">
-        <v>76.86</v>
+        <v>80.98999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>-42.55</v>
+        <v>-44.86</v>
       </c>
       <c r="K17" t="n">
-        <v>64.84</v>
+        <v>68.36</v>
       </c>
       <c r="L17" t="n">
-        <v>77.55</v>
+        <v>81.76000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-20.12</v>
+        <v>-22.24</v>
       </c>
       <c r="K18" t="n">
-        <v>90.95999999999999</v>
+        <v>100.58</v>
       </c>
       <c r="L18" t="n">
-        <v>93.16</v>
+        <v>103.01</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>16.72</v>
+        <v>18.19</v>
       </c>
       <c r="K19" t="n">
-        <v>-30.64</v>
+        <v>-33.34</v>
       </c>
       <c r="L19" t="n">
-        <v>34.91</v>
+        <v>37.98</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-140.87</v>
+        <v>-155.78</v>
       </c>
       <c r="K20" t="n">
-        <v>-95.81999999999999</v>
+        <v>-105.96</v>
       </c>
       <c r="L20" t="n">
-        <v>170.37</v>
+        <v>188.4</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-105.91</v>
+        <v>-113.76</v>
       </c>
       <c r="K21" t="n">
-        <v>37</v>
+        <v>39.74</v>
       </c>
       <c r="L21" t="n">
-        <v>112.19</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>93.26000000000001</v>
+        <v>104.71</v>
       </c>
       <c r="K22" t="n">
-        <v>-80.53</v>
+        <v>-90.42</v>
       </c>
       <c r="L22" t="n">
-        <v>123.22</v>
+        <v>138.35</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-180.79</v>
+        <v>-191.07</v>
       </c>
       <c r="K23" t="n">
-        <v>-47.17</v>
+        <v>-49.85</v>
       </c>
       <c r="L23" t="n">
-        <v>186.84</v>
+        <v>197.46</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-88.5</v>
+        <v>-100.8</v>
       </c>
       <c r="K24" t="n">
-        <v>-128.36</v>
+        <v>-146.21</v>
       </c>
       <c r="L24" t="n">
-        <v>155.91</v>
+        <v>177.59</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-123.69</v>
+        <v>-132.96</v>
       </c>
       <c r="K25" t="n">
-        <v>170.88</v>
+        <v>183.68</v>
       </c>
       <c r="L25" t="n">
-        <v>210.95</v>
+        <v>226.75</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>-101.4</v>
+        <v>-115.83</v>
       </c>
       <c r="K26" t="n">
-        <v>-250.44</v>
+        <v>-286.06</v>
       </c>
       <c r="L26" t="n">
-        <v>270.19</v>
+        <v>308.62</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>176.91</v>
+        <v>187.53</v>
       </c>
       <c r="K27" t="n">
-        <v>-221.36</v>
+        <v>-234.65</v>
       </c>
       <c r="L27" t="n">
-        <v>283.37</v>
+        <v>300.38</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-74.02</v>
+        <v>-85.36</v>
       </c>
       <c r="K28" t="n">
-        <v>-290.63</v>
+        <v>-335.17</v>
       </c>
       <c r="L28" t="n">
-        <v>299.91</v>
+        <v>345.87</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>3.62</v>
+        <v>3.94</v>
       </c>
       <c r="K29" t="n">
-        <v>51.52</v>
+        <v>56.2</v>
       </c>
       <c r="L29" t="n">
-        <v>51.64</v>
+        <v>56.34</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-35.13</v>
+        <v>-38.31</v>
       </c>
       <c r="K30" t="n">
-        <v>-61.38</v>
+        <v>-66.93000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>70.72</v>
+        <v>77.12</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-21.47</v>
+        <v>-24.35</v>
       </c>
       <c r="K31" t="n">
-        <v>-66.04000000000001</v>
+        <v>-74.89</v>
       </c>
       <c r="L31" t="n">
-        <v>69.44</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>47.65</v>
+        <v>53.99</v>
       </c>
       <c r="K32" t="n">
-        <v>-125.01</v>
+        <v>-141.65</v>
       </c>
       <c r="L32" t="n">
-        <v>133.79</v>
+        <v>151.59</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-95.45999999999999</v>
+        <v>-106.8</v>
       </c>
       <c r="K33" t="n">
-        <v>-26.27</v>
+        <v>-29.39</v>
       </c>
       <c r="L33" t="n">
-        <v>99.01000000000001</v>
+        <v>110.77</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>14.14</v>
+        <v>15.82</v>
       </c>
       <c r="K34" t="n">
-        <v>97.29000000000001</v>
+        <v>108.85</v>
       </c>
       <c r="L34" t="n">
-        <v>98.31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>-119.6</v>
+        <v>-132.25</v>
       </c>
       <c r="K35" t="n">
-        <v>88.39</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>148.72</v>
+        <v>164.45</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>51.29</v>
+        <v>55.88</v>
       </c>
       <c r="K36" t="n">
-        <v>-153.1</v>
+        <v>-166.8</v>
       </c>
       <c r="L36" t="n">
-        <v>161.46</v>
+        <v>175.91</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>66.88</v>
+        <v>71.69</v>
       </c>
       <c r="K37" t="n">
-        <v>120.28</v>
+        <v>128.93</v>
       </c>
       <c r="L37" t="n">
-        <v>137.62</v>
+        <v>147.53</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>20.63</v>
+        <v>21.81</v>
       </c>
       <c r="K38" t="n">
-        <v>-272.29</v>
+        <v>-287.95</v>
       </c>
       <c r="L38" t="n">
-        <v>273.07</v>
+        <v>288.77</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>140.26</v>
+        <v>159.75</v>
       </c>
       <c r="K39" t="n">
-        <v>-104.85</v>
+        <v>-119.42</v>
       </c>
       <c r="L39" t="n">
-        <v>175.12</v>
+        <v>199.46</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-170.83</v>
+        <v>-194.62</v>
       </c>
       <c r="K40" t="n">
-        <v>-179.98</v>
+        <v>-205.05</v>
       </c>
       <c r="L40" t="n">
-        <v>248.14</v>
+        <v>282.71</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>125.94</v>
+        <v>143.86</v>
       </c>
       <c r="K41" t="n">
-        <v>466.39</v>
+        <v>532.76</v>
       </c>
       <c r="L41" t="n">
-        <v>483.09</v>
+        <v>551.84</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-286.32</v>
+        <v>-304.57</v>
       </c>
       <c r="K42" t="n">
-        <v>299.28</v>
+        <v>318.35</v>
       </c>
       <c r="L42" t="n">
-        <v>414.18</v>
+        <v>440.58</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>-234.09</v>
+        <v>-253.09</v>
       </c>
       <c r="K43" t="n">
-        <v>-62.46</v>
+        <v>-67.53</v>
       </c>
       <c r="L43" t="n">
-        <v>242.28</v>
+        <v>261.94</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="K44" t="n">
-        <v>-115.18</v>
+        <v>-130.8</v>
       </c>
       <c r="L44" t="n">
-        <v>115.18</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-21.04</v>
+        <v>-23.88</v>
       </c>
       <c r="K45" t="n">
-        <v>-68.79000000000001</v>
+        <v>-78.06999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>71.94</v>
+        <v>81.64</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>5.17</v>
+        <v>5.86</v>
       </c>
       <c r="K46" t="n">
-        <v>81.45</v>
+        <v>92.39</v>
       </c>
       <c r="L46" t="n">
-        <v>81.61</v>
+        <v>92.56999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>77.65000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-29.04</v>
+        <v>-30.52</v>
       </c>
       <c r="L47" t="n">
-        <v>82.90000000000001</v>
+        <v>87.12</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>35.99</v>
+        <v>37.9</v>
       </c>
       <c r="K48" t="n">
-        <v>84.19</v>
+        <v>88.64</v>
       </c>
       <c r="L48" t="n">
-        <v>91.56</v>
+        <v>96.41</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>84.22</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>17.88</v>
+        <v>20.26</v>
       </c>
       <c r="L49" t="n">
-        <v>86.09999999999999</v>
+        <v>97.53</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>30.43</v>
+        <v>32.12</v>
       </c>
       <c r="K50" t="n">
-        <v>145.98</v>
+        <v>154.07</v>
       </c>
       <c r="L50" t="n">
-        <v>149.12</v>
+        <v>157.38</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>112.03</v>
+        <v>123.84</v>
       </c>
       <c r="K51" t="n">
-        <v>79.25</v>
+        <v>87.61</v>
       </c>
       <c r="L51" t="n">
-        <v>137.23</v>
+        <v>151.7</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-121.39</v>
+        <v>-128</v>
       </c>
       <c r="K52" t="n">
-        <v>-103.34</v>
+        <v>-108.97</v>
       </c>
       <c r="L52" t="n">
-        <v>159.42</v>
+        <v>168.1</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>-35.85</v>
+        <v>-40.31</v>
       </c>
       <c r="K53" t="n">
-        <v>188.63</v>
+        <v>212.09</v>
       </c>
       <c r="L53" t="n">
-        <v>192.01</v>
+        <v>215.89</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>171.2</v>
+        <v>195.05</v>
       </c>
       <c r="K54" t="n">
-        <v>146.77</v>
+        <v>167.22</v>
       </c>
       <c r="L54" t="n">
-        <v>225.5</v>
+        <v>256.91</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>-226.54</v>
+        <v>-247.46</v>
       </c>
       <c r="K55" t="n">
-        <v>-20.64</v>
+        <v>-22.55</v>
       </c>
       <c r="L55" t="n">
-        <v>227.48</v>
+        <v>248.48</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-111.15</v>
+        <v>-118</v>
       </c>
       <c r="K56" t="n">
-        <v>369.38</v>
+        <v>392.13</v>
       </c>
       <c r="L56" t="n">
-        <v>385.74</v>
+        <v>409.5</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>322.76</v>
+        <v>345.49</v>
       </c>
       <c r="K57" t="n">
-        <v>144.17</v>
+        <v>154.33</v>
       </c>
       <c r="L57" t="n">
-        <v>353.5</v>
+        <v>378.39</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-238.16</v>
+        <v>-259.52</v>
       </c>
       <c r="K58" t="n">
-        <v>100.87</v>
+        <v>109.92</v>
       </c>
       <c r="L58" t="n">
-        <v>258.64</v>
+        <v>281.84</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-42.2</v>
+        <v>-44.38</v>
       </c>
       <c r="K59" t="n">
-        <v>-52.99</v>
+        <v>-55.73</v>
       </c>
       <c r="L59" t="n">
-        <v>67.73</v>
+        <v>71.23999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>95.48</v>
+        <v>102</v>
       </c>
       <c r="K60" t="n">
-        <v>-45.82</v>
+        <v>-48.95</v>
       </c>
       <c r="L60" t="n">
-        <v>105.91</v>
+        <v>113.13</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>4.08</v>
+        <v>4.62</v>
       </c>
       <c r="K61" t="n">
-        <v>-81</v>
+        <v>-91.72</v>
       </c>
       <c r="L61" t="n">
-        <v>81.09999999999999</v>
+        <v>91.83</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>-84.79000000000001</v>
+        <v>-90.48999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-88.44</v>
+        <v>-94.39</v>
       </c>
       <c r="L62" t="n">
-        <v>122.51</v>
+        <v>130.76</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>94.5</v>
+        <v>103.9</v>
       </c>
       <c r="K63" t="n">
-        <v>-64.19</v>
+        <v>-70.56999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>114.24</v>
+        <v>125.59</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-12.43</v>
+        <v>-13.1</v>
       </c>
       <c r="K64" t="n">
-        <v>100.74</v>
+        <v>106.11</v>
       </c>
       <c r="L64" t="n">
-        <v>101.5</v>
+        <v>106.92</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="K65" t="n">
-        <v>165.85</v>
+        <v>188.48</v>
       </c>
       <c r="L65" t="n">
-        <v>165.86</v>
+        <v>188.5</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>90.17</v>
+        <v>99.64</v>
       </c>
       <c r="K66" t="n">
-        <v>122.25</v>
+        <v>135.08</v>
       </c>
       <c r="L66" t="n">
-        <v>151.91</v>
+        <v>167.85</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-7.16</v>
+        <v>-7.67</v>
       </c>
       <c r="K67" t="n">
-        <v>-235.21</v>
+        <v>-252.21</v>
       </c>
       <c r="L67" t="n">
-        <v>235.32</v>
+        <v>252.33</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>162.78</v>
+        <v>185.39</v>
       </c>
       <c r="K68" t="n">
-        <v>108.73</v>
+        <v>123.83</v>
       </c>
       <c r="L68" t="n">
-        <v>195.75</v>
+        <v>222.94</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>114.87</v>
+        <v>123.55</v>
       </c>
       <c r="K69" t="n">
-        <v>199.82</v>
+        <v>214.93</v>
       </c>
       <c r="L69" t="n">
-        <v>230.48</v>
+        <v>247.91</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-171.15</v>
+        <v>-192.38</v>
       </c>
       <c r="K70" t="n">
-        <v>-83.73</v>
+        <v>-94.12</v>
       </c>
       <c r="L70" t="n">
-        <v>190.53</v>
+        <v>214.17</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>259.1</v>
+        <v>280.09</v>
       </c>
       <c r="K71" t="n">
-        <v>140.05</v>
+        <v>151.39</v>
       </c>
       <c r="L71" t="n">
-        <v>294.52</v>
+        <v>318.39</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-233.27</v>
+        <v>-266.08</v>
       </c>
       <c r="K72" t="n">
-        <v>235.83</v>
+        <v>269.01</v>
       </c>
       <c r="L72" t="n">
-        <v>331.71</v>
+        <v>378.37</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>42.64</v>
+        <v>48.77</v>
       </c>
       <c r="K73" t="n">
-        <v>-506.85</v>
+        <v>-579.76</v>
       </c>
       <c r="L73" t="n">
-        <v>508.65</v>
+        <v>581.8</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>-13.95</v>
+        <v>-15.55</v>
       </c>
       <c r="K74" t="n">
-        <v>-70.73</v>
+        <v>-78.81999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>72.09</v>
+        <v>80.34</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>-117.15</v>
+        <v>-130.79</v>
       </c>
       <c r="K75" t="n">
-        <v>-8.41</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>117.45</v>
+        <v>131.13</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>53.56</v>
+        <v>57.15</v>
       </c>
       <c r="K76" t="n">
-        <v>58.41</v>
+        <v>62.32</v>
       </c>
       <c r="L76" t="n">
-        <v>79.25</v>
+        <v>84.55</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>95.16</v>
+        <v>107.7</v>
       </c>
       <c r="K77" t="n">
-        <v>104.89</v>
+        <v>118.71</v>
       </c>
       <c r="L77" t="n">
-        <v>141.63</v>
+        <v>160.28</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-51.29</v>
+        <v>-58.11</v>
       </c>
       <c r="K78" t="n">
-        <v>-89.81</v>
+        <v>-101.76</v>
       </c>
       <c r="L78" t="n">
-        <v>103.42</v>
+        <v>117.18</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>48.2</v>
+        <v>51.43</v>
       </c>
       <c r="K79" t="n">
-        <v>-77.81999999999999</v>
+        <v>-83.03</v>
       </c>
       <c r="L79" t="n">
-        <v>91.53</v>
+        <v>97.66</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>84.14</v>
+        <v>90.2</v>
       </c>
       <c r="K80" t="n">
-        <v>-106.03</v>
+        <v>-113.66</v>
       </c>
       <c r="L80" t="n">
-        <v>135.36</v>
+        <v>145.1</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>19.56</v>
+        <v>21.31</v>
       </c>
       <c r="K81" t="n">
-        <v>-133.05</v>
+        <v>-144.97</v>
       </c>
       <c r="L81" t="n">
-        <v>134.48</v>
+        <v>146.53</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>120.65</v>
+        <v>129.4</v>
       </c>
       <c r="K82" t="n">
-        <v>66.34999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="L82" t="n">
-        <v>137.69</v>
+        <v>147.67</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-318.46</v>
+        <v>-362.81</v>
       </c>
       <c r="K83" t="n">
-        <v>-37.96</v>
+        <v>-43.25</v>
       </c>
       <c r="L83" t="n">
-        <v>320.71</v>
+        <v>365.38</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-180.13</v>
+        <v>-196.73</v>
       </c>
       <c r="K84" t="n">
-        <v>-65.09</v>
+        <v>-71.08</v>
       </c>
       <c r="L84" t="n">
-        <v>191.53</v>
+        <v>209.17</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>96.11</v>
+        <v>108.77</v>
       </c>
       <c r="K85" t="n">
-        <v>283.18</v>
+        <v>320.51</v>
       </c>
       <c r="L85" t="n">
-        <v>299.05</v>
+        <v>338.46</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-159.49</v>
+        <v>-178.97</v>
       </c>
       <c r="K86" t="n">
-        <v>2.73</v>
+        <v>3.07</v>
       </c>
       <c r="L86" t="n">
-        <v>159.51</v>
+        <v>179</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>-74.3</v>
+        <v>-79.06999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>246.62</v>
+        <v>262.45</v>
       </c>
       <c r="L87" t="n">
-        <v>257.57</v>
+        <v>274.1</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>112.16</v>
+        <v>119.36</v>
       </c>
       <c r="K88" t="n">
-        <v>272.14</v>
+        <v>289.6</v>
       </c>
       <c r="L88" t="n">
-        <v>294.34</v>
+        <v>313.24</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-04.xlsx
+++ b/output/2024-04-04.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.84</v>
+        <v>3.49</v>
       </c>
       <c r="F14" t="n">
-        <v>9.050000000000001</v>
+        <v>3.79</v>
       </c>
       <c r="G14" t="n">
-        <v>282.9</v>
+        <v>302.8</v>
       </c>
       <c r="H14" t="n">
-        <v>99</v>
+        <v>53.8</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>77.09</v>
+        <v>52.44</v>
       </c>
       <c r="K14" t="n">
-        <v>43.06</v>
+        <v>-29.88</v>
       </c>
       <c r="L14" t="n">
-        <v>88.3</v>
+        <v>60.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:38:22</t>
+          <t>06:38:13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.38</v>
+        <v>3.74</v>
       </c>
       <c r="F15" t="n">
-        <v>8.59</v>
+        <v>8.24</v>
       </c>
       <c r="G15" t="n">
-        <v>298</v>
+        <v>297.5</v>
       </c>
       <c r="H15" t="n">
-        <v>96.5</v>
+        <v>69.8</v>
       </c>
       <c r="I15" t="n">
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>1.67</v>
+        <v>-54.51</v>
       </c>
       <c r="K15" t="n">
-        <v>-96.15000000000001</v>
+        <v>-30.83</v>
       </c>
       <c r="L15" t="n">
-        <v>96.16</v>
+        <v>62.62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:40:00</t>
+          <t>06:40:37</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.79</v>
+        <v>3.67</v>
       </c>
       <c r="F16" t="n">
-        <v>8.41</v>
+        <v>8.75</v>
       </c>
       <c r="G16" t="n">
-        <v>297.7</v>
+        <v>311.6</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>18.1</v>
       </c>
       <c r="I16" t="n">
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-69.5</v>
+        <v>-53.46</v>
       </c>
       <c r="K16" t="n">
-        <v>-41.58</v>
+        <v>13.82</v>
       </c>
       <c r="L16" t="n">
-        <v>80.98999999999999</v>
+        <v>55.22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:45:11</t>
+          <t>06:45:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.69</v>
+        <v>3.53</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>10.92</v>
       </c>
       <c r="G17" t="n">
-        <v>300.1</v>
+        <v>306.6</v>
       </c>
       <c r="H17" t="n">
-        <v>91.8</v>
+        <v>83.5</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-44.86</v>
+        <v>-47.11</v>
       </c>
       <c r="K17" t="n">
-        <v>68.36</v>
+        <v>36.58</v>
       </c>
       <c r="L17" t="n">
-        <v>81.76000000000001</v>
+        <v>59.65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:47:00</t>
+          <t>06:46:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="F18" t="n">
-        <v>7.28</v>
+        <v>10.11</v>
       </c>
       <c r="G18" t="n">
-        <v>303.6</v>
+        <v>305</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>77.5</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-22.24</v>
+        <v>86.08</v>
       </c>
       <c r="K18" t="n">
-        <v>100.58</v>
+        <v>29.7</v>
       </c>
       <c r="L18" t="n">
-        <v>103.01</v>
+        <v>91.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:48:00</t>
+          <t>06:47:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="F19" t="n">
-        <v>9.33</v>
+        <v>10.54</v>
       </c>
       <c r="G19" t="n">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>42.5</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>18.19</v>
+        <v>-111.76</v>
       </c>
       <c r="K19" t="n">
-        <v>-33.34</v>
+        <v>0.61</v>
       </c>
       <c r="L19" t="n">
-        <v>37.98</v>
+        <v>111.76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:52:51</t>
+          <t>06:52:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="F20" t="n">
-        <v>9.01</v>
+        <v>8.41</v>
       </c>
       <c r="G20" t="n">
-        <v>295.3</v>
+        <v>312.5</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>60.2</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-155.78</v>
+        <v>114.65</v>
       </c>
       <c r="K20" t="n">
-        <v>-105.96</v>
+        <v>96.64</v>
       </c>
       <c r="L20" t="n">
-        <v>188.4</v>
+        <v>149.95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:54:27</t>
+          <t>06:53:29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.17</v>
+        <v>3.64</v>
       </c>
       <c r="F21" t="n">
-        <v>9.550000000000001</v>
+        <v>5.89</v>
       </c>
       <c r="G21" t="n">
-        <v>305.6</v>
+        <v>294.9</v>
       </c>
       <c r="H21" t="n">
-        <v>93.5</v>
+        <v>76.2</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-113.76</v>
+        <v>-108.17</v>
       </c>
       <c r="K21" t="n">
-        <v>39.74</v>
+        <v>100.75</v>
       </c>
       <c r="L21" t="n">
-        <v>120.5</v>
+        <v>147.82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:56:32</t>
+          <t>06:55:37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.13</v>
+        <v>3.46</v>
       </c>
       <c r="F22" t="n">
-        <v>5.44</v>
+        <v>7.04</v>
       </c>
       <c r="G22" t="n">
-        <v>287.3</v>
+        <v>294.6</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>58.8</v>
       </c>
       <c r="I22" t="n">
         <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>104.71</v>
+        <v>56.56</v>
       </c>
       <c r="K22" t="n">
-        <v>-90.42</v>
+        <v>124.55</v>
       </c>
       <c r="L22" t="n">
-        <v>138.35</v>
+        <v>136.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:02:05</t>
+          <t>06:59:55</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.42</v>
+        <v>3.93</v>
       </c>
       <c r="F23" t="n">
-        <v>7.24</v>
+        <v>6.42</v>
       </c>
       <c r="G23" t="n">
-        <v>303.4</v>
+        <v>280.8</v>
       </c>
       <c r="H23" t="n">
-        <v>93.8</v>
+        <v>55.4</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-191.07</v>
+        <v>-218.17</v>
       </c>
       <c r="K23" t="n">
-        <v>-49.85</v>
+        <v>154.92</v>
       </c>
       <c r="L23" t="n">
-        <v>197.46</v>
+        <v>267.58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:03:22</t>
+          <t>07:01:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="F24" t="n">
-        <v>8.93</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>290.5</v>
+        <v>281.2</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>74.8</v>
       </c>
       <c r="I24" t="n">
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-100.8</v>
+        <v>-284.67</v>
       </c>
       <c r="K24" t="n">
-        <v>-146.21</v>
+        <v>29.3</v>
       </c>
       <c r="L24" t="n">
-        <v>177.59</v>
+        <v>286.18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:05:46</t>
+          <t>07:02:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.91</v>
+        <v>4.41</v>
       </c>
       <c r="F25" t="n">
-        <v>9.44</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>309.3</v>
+        <v>308</v>
       </c>
       <c r="H25" t="n">
-        <v>88.3</v>
+        <v>32.1</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-132.96</v>
+        <v>223.27</v>
       </c>
       <c r="K25" t="n">
-        <v>183.68</v>
+        <v>82.91</v>
       </c>
       <c r="L25" t="n">
-        <v>226.75</v>
+        <v>238.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:11:55</t>
+          <t>07:07:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.71</v>
+        <v>3.49</v>
       </c>
       <c r="F26" t="n">
-        <v>6.79</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>284.4</v>
+        <v>300.4</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>59.9</v>
       </c>
       <c r="I26" t="n">
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>-115.83</v>
+        <v>44.08</v>
       </c>
       <c r="K26" t="n">
-        <v>-286.06</v>
+        <v>-256.29</v>
       </c>
       <c r="L26" t="n">
-        <v>308.62</v>
+        <v>260.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:13:52</t>
+          <t>07:09:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="F27" t="n">
-        <v>9.390000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="G27" t="n">
-        <v>296.6</v>
+        <v>304.1</v>
       </c>
       <c r="H27" t="n">
-        <v>93.09999999999999</v>
+        <v>54.4</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>187.53</v>
+        <v>-232.7</v>
       </c>
       <c r="K27" t="n">
-        <v>-234.65</v>
+        <v>-100.39</v>
       </c>
       <c r="L27" t="n">
-        <v>300.38</v>
+        <v>253.43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:16:10</t>
+          <t>07:11:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.31</v>
+        <v>3.22</v>
       </c>
       <c r="F28" t="n">
-        <v>8.07</v>
+        <v>5.38</v>
       </c>
       <c r="G28" t="n">
-        <v>293.4</v>
+        <v>290.3</v>
       </c>
       <c r="H28" t="n">
-        <v>97.3</v>
+        <v>59.4</v>
       </c>
       <c r="I28" t="n">
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-85.36</v>
+        <v>23.37</v>
       </c>
       <c r="K28" t="n">
-        <v>-335.17</v>
+        <v>194.94</v>
       </c>
       <c r="L28" t="n">
-        <v>345.87</v>
+        <v>196.34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:26:26</t>
+          <t>07:19:54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.21</v>
+        <v>3.7</v>
       </c>
       <c r="F29" t="n">
-        <v>4.75</v>
+        <v>8.81</v>
       </c>
       <c r="G29" t="n">
-        <v>292.8</v>
+        <v>300.1</v>
       </c>
       <c r="H29" t="n">
-        <v>96.40000000000001</v>
+        <v>44.3</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>3.94</v>
+        <v>-51.57</v>
       </c>
       <c r="K29" t="n">
-        <v>56.2</v>
+        <v>-56.54</v>
       </c>
       <c r="L29" t="n">
-        <v>56.34</v>
+        <v>76.53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:28:00</t>
+          <t>07:21:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.34</v>
+        <v>3.82</v>
       </c>
       <c r="F30" t="n">
-        <v>7.89</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>307.1</v>
+        <v>310.8</v>
       </c>
       <c r="H30" t="n">
-        <v>95.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-38.31</v>
+        <v>46.06</v>
       </c>
       <c r="K30" t="n">
-        <v>-66.93000000000001</v>
+        <v>-54.33</v>
       </c>
       <c r="L30" t="n">
-        <v>77.12</v>
+        <v>71.23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:29:58</t>
+          <t>07:23:01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.94</v>
+        <v>3.63</v>
       </c>
       <c r="F31" t="n">
-        <v>8.58</v>
+        <v>10.92</v>
       </c>
       <c r="G31" t="n">
-        <v>303.7</v>
+        <v>295.4</v>
       </c>
       <c r="H31" t="n">
-        <v>97.09999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="I31" t="n">
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-24.35</v>
+        <v>-13.7</v>
       </c>
       <c r="K31" t="n">
-        <v>-74.89</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>78.75</v>
+        <v>68.29000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:34:55</t>
+          <t>07:27:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.15</v>
+        <v>4.03</v>
       </c>
       <c r="F32" t="n">
-        <v>9.039999999999999</v>
+        <v>10.44</v>
       </c>
       <c r="G32" t="n">
-        <v>313.4</v>
+        <v>302.7</v>
       </c>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>53.99</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-141.65</v>
+        <v>64.78</v>
       </c>
       <c r="L32" t="n">
-        <v>151.59</v>
+        <v>94.20999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:36:58</t>
+          <t>07:29:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.99</v>
+        <v>3.92</v>
       </c>
       <c r="F33" t="n">
-        <v>9.81</v>
+        <v>8.92</v>
       </c>
       <c r="G33" t="n">
-        <v>300</v>
+        <v>286.1</v>
       </c>
       <c r="H33" t="n">
-        <v>97.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>-106.8</v>
+        <v>43.4</v>
       </c>
       <c r="K33" t="n">
-        <v>-29.39</v>
+        <v>-86.76000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>110.77</v>
+        <v>97.01000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:37:32</t>
+          <t>07:30:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.98</v>
+        <v>3.87</v>
       </c>
       <c r="F34" t="n">
-        <v>7.97</v>
+        <v>10.32</v>
       </c>
       <c r="G34" t="n">
-        <v>302.9</v>
+        <v>309</v>
       </c>
       <c r="H34" t="n">
-        <v>94.59999999999999</v>
+        <v>51.7</v>
       </c>
       <c r="I34" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>15.82</v>
+        <v>-64.25</v>
       </c>
       <c r="K34" t="n">
-        <v>108.85</v>
+        <v>-78.34</v>
       </c>
       <c r="L34" t="n">
-        <v>110</v>
+        <v>101.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:42:49</t>
+          <t>07:35:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.97</v>
+        <v>3.65</v>
       </c>
       <c r="F35" t="n">
-        <v>9.539999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>317.5</v>
+        <v>303.1</v>
       </c>
       <c r="H35" t="n">
-        <v>97.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-132.25</v>
+        <v>-107.79</v>
       </c>
       <c r="K35" t="n">
-        <v>97.73999999999999</v>
+        <v>80.08</v>
       </c>
       <c r="L35" t="n">
-        <v>164.45</v>
+        <v>134.28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:43:40</t>
+          <t>07:37:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.03</v>
+        <v>3.4</v>
       </c>
       <c r="F36" t="n">
-        <v>10.83</v>
+        <v>5.42</v>
       </c>
       <c r="G36" t="n">
-        <v>290.9</v>
+        <v>296.3</v>
       </c>
       <c r="H36" t="n">
-        <v>99.59999999999999</v>
+        <v>60.3</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>55.88</v>
+        <v>0.13</v>
       </c>
       <c r="K36" t="n">
-        <v>-166.8</v>
+        <v>117.38</v>
       </c>
       <c r="L36" t="n">
-        <v>175.91</v>
+        <v>117.38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:45:47</t>
+          <t>07:39:15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="F37" t="n">
-        <v>10.34</v>
+        <v>10.09</v>
       </c>
       <c r="G37" t="n">
-        <v>299.6</v>
+        <v>308.9</v>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>71.69</v>
+        <v>-182.87</v>
       </c>
       <c r="K37" t="n">
-        <v>128.93</v>
+        <v>3.25</v>
       </c>
       <c r="L37" t="n">
-        <v>147.53</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:51:11</t>
+          <t>07:44:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="F38" t="n">
-        <v>9.4</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>289.1</v>
+        <v>302.9</v>
       </c>
       <c r="H38" t="n">
-        <v>99.7</v>
+        <v>61</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>21.81</v>
+        <v>276.89</v>
       </c>
       <c r="K38" t="n">
-        <v>-287.95</v>
+        <v>95.09</v>
       </c>
       <c r="L38" t="n">
-        <v>288.77</v>
+        <v>292.77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:53:22</t>
+          <t>07:45:37</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.05</v>
+        <v>3.93</v>
       </c>
       <c r="F39" t="n">
-        <v>10.92</v>
+        <v>9.69</v>
       </c>
       <c r="G39" t="n">
-        <v>296.6</v>
+        <v>311.1</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>64.2</v>
       </c>
       <c r="I39" t="n">
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>159.75</v>
+        <v>156.72</v>
       </c>
       <c r="K39" t="n">
-        <v>-119.42</v>
+        <v>-127.04</v>
       </c>
       <c r="L39" t="n">
-        <v>199.46</v>
+        <v>201.74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:55:53</t>
+          <t>07:47:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.3</v>
+        <v>3.47</v>
       </c>
       <c r="F40" t="n">
-        <v>10.38</v>
+        <v>9.73</v>
       </c>
       <c r="G40" t="n">
-        <v>305.1</v>
+        <v>284.5</v>
       </c>
       <c r="H40" t="n">
-        <v>100</v>
+        <v>68.2</v>
       </c>
       <c r="I40" t="n">
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-194.62</v>
+        <v>-195.01</v>
       </c>
       <c r="K40" t="n">
-        <v>-205.05</v>
+        <v>-132.04</v>
       </c>
       <c r="L40" t="n">
-        <v>282.71</v>
+        <v>235.51</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:00:31</t>
+          <t>07:51:15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="F41" t="n">
-        <v>9.35</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>305.9</v>
+        <v>286.5</v>
       </c>
       <c r="H41" t="n">
-        <v>95.5</v>
+        <v>35.9</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>143.86</v>
+        <v>-65.63</v>
       </c>
       <c r="K41" t="n">
-        <v>532.76</v>
+        <v>246.87</v>
       </c>
       <c r="L41" t="n">
-        <v>551.84</v>
+        <v>255.44</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:02:30</t>
+          <t>07:52:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.14</v>
+        <v>4.27</v>
       </c>
       <c r="F42" t="n">
-        <v>8.949999999999999</v>
+        <v>10.92</v>
       </c>
       <c r="G42" t="n">
-        <v>295</v>
+        <v>294.3</v>
       </c>
       <c r="H42" t="n">
-        <v>92.8</v>
+        <v>48.8</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-304.57</v>
+        <v>-294.93</v>
       </c>
       <c r="K42" t="n">
-        <v>318.35</v>
+        <v>-35.7</v>
       </c>
       <c r="L42" t="n">
-        <v>440.58</v>
+        <v>297.08</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:03:37</t>
+          <t>07:53:51</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.12</v>
+        <v>3.74</v>
       </c>
       <c r="F43" t="n">
-        <v>9.17</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>299.5</v>
+        <v>299.8</v>
       </c>
       <c r="H43" t="n">
-        <v>100</v>
+        <v>61.4</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-253.09</v>
+        <v>48.8</v>
       </c>
       <c r="K43" t="n">
-        <v>-67.53</v>
+        <v>-298.76</v>
       </c>
       <c r="L43" t="n">
-        <v>261.94</v>
+        <v>302.72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:16:07</t>
+          <t>08:05:40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.66</v>
+        <v>4.24</v>
       </c>
       <c r="F44" t="n">
-        <v>8.23</v>
+        <v>10.72</v>
       </c>
       <c r="G44" t="n">
-        <v>289.5</v>
+        <v>292</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>60.7</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>0.57</v>
+        <v>-49.72</v>
       </c>
       <c r="K44" t="n">
-        <v>-130.8</v>
+        <v>52.98</v>
       </c>
       <c r="L44" t="n">
-        <v>130.8</v>
+        <v>72.66</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:17:43</t>
+          <t>08:06:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.81</v>
+        <v>4.77</v>
       </c>
       <c r="F45" t="n">
-        <v>9.51</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>308</v>
+        <v>299.6</v>
       </c>
       <c r="H45" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="I45" t="n">
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-23.88</v>
+        <v>-118.37</v>
       </c>
       <c r="K45" t="n">
-        <v>-78.06999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="L45" t="n">
-        <v>81.64</v>
+        <v>119.15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:19:22</t>
+          <t>08:08:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.91</v>
+        <v>4.19</v>
       </c>
       <c r="F46" t="n">
-        <v>9.48</v>
+        <v>8.81</v>
       </c>
       <c r="G46" t="n">
-        <v>300.9</v>
+        <v>288.4</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>5.86</v>
+        <v>43.17</v>
       </c>
       <c r="K46" t="n">
-        <v>92.39</v>
+        <v>-52.88</v>
       </c>
       <c r="L46" t="n">
-        <v>92.56999999999999</v>
+        <v>68.26000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:24:24</t>
+          <t>08:11:23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.38</v>
+        <v>4.28</v>
       </c>
       <c r="F47" t="n">
-        <v>7.81</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>286.1</v>
+        <v>302.7</v>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>57.7</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>81.59999999999999</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-30.52</v>
+        <v>17.96</v>
       </c>
       <c r="L47" t="n">
-        <v>87.12</v>
+        <v>75.22</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:25:42</t>
+          <t>08:12:39</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.97</v>
+        <v>4.37</v>
       </c>
       <c r="F48" t="n">
-        <v>7.92</v>
+        <v>8.16</v>
       </c>
       <c r="G48" t="n">
-        <v>301.5</v>
+        <v>285.7</v>
       </c>
       <c r="H48" t="n">
-        <v>96.8</v>
+        <v>65.3</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>37.9</v>
+        <v>63.77</v>
       </c>
       <c r="K48" t="n">
-        <v>88.64</v>
+        <v>41.6</v>
       </c>
       <c r="L48" t="n">
-        <v>96.41</v>
+        <v>76.14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:26:58</t>
+          <t>08:13:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.19</v>
+        <v>3.96</v>
       </c>
       <c r="F49" t="n">
-        <v>9.550000000000001</v>
+        <v>10.63</v>
       </c>
       <c r="G49" t="n">
-        <v>301.5</v>
+        <v>302.9</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>95.40000000000001</v>
+        <v>-4.73</v>
       </c>
       <c r="K49" t="n">
-        <v>20.26</v>
+        <v>73.64</v>
       </c>
       <c r="L49" t="n">
-        <v>97.53</v>
+        <v>73.79000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:32:50</t>
+          <t>08:18:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.91</v>
+        <v>3.23</v>
       </c>
       <c r="F50" t="n">
-        <v>9.25</v>
+        <v>7.44</v>
       </c>
       <c r="G50" t="n">
-        <v>317.5</v>
+        <v>305.5</v>
       </c>
       <c r="H50" t="n">
-        <v>100</v>
+        <v>61.5</v>
       </c>
       <c r="I50" t="n">
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>32.12</v>
+        <v>-85.06999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>154.07</v>
+        <v>-54.13</v>
       </c>
       <c r="L50" t="n">
-        <v>157.38</v>
+        <v>100.83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:33:53</t>
+          <t>08:20:23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.19</v>
+        <v>4.42</v>
       </c>
       <c r="F51" t="n">
-        <v>9.43</v>
+        <v>10.66</v>
       </c>
       <c r="G51" t="n">
-        <v>297</v>
+        <v>301.2</v>
       </c>
       <c r="H51" t="n">
-        <v>96.8</v>
+        <v>27.8</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>123.84</v>
+        <v>-128.73</v>
       </c>
       <c r="K51" t="n">
-        <v>87.61</v>
+        <v>-27.48</v>
       </c>
       <c r="L51" t="n">
-        <v>151.7</v>
+        <v>131.63</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:34:49</t>
+          <t>08:21:45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.54</v>
+        <v>3.75</v>
       </c>
       <c r="F52" t="n">
-        <v>10.33</v>
+        <v>10.92</v>
       </c>
       <c r="G52" t="n">
-        <v>303</v>
+        <v>299.6</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>53.3</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>-128</v>
+        <v>101.98</v>
       </c>
       <c r="K52" t="n">
-        <v>-108.97</v>
+        <v>-59.17</v>
       </c>
       <c r="L52" t="n">
-        <v>168.1</v>
+        <v>117.91</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:39:44</t>
+          <t>08:27:24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.46</v>
+        <v>4.33</v>
       </c>
       <c r="F53" t="n">
-        <v>10.82</v>
+        <v>7.76</v>
       </c>
       <c r="G53" t="n">
-        <v>293</v>
+        <v>308.2</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="I53" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-40.31</v>
+        <v>40.81</v>
       </c>
       <c r="K53" t="n">
-        <v>212.09</v>
+        <v>144.9</v>
       </c>
       <c r="L53" t="n">
-        <v>215.89</v>
+        <v>150.54</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:41:10</t>
+          <t>08:29:08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.29</v>
+        <v>4.02</v>
       </c>
       <c r="F54" t="n">
-        <v>10.92</v>
+        <v>9.69</v>
       </c>
       <c r="G54" t="n">
-        <v>295.6</v>
+        <v>290.2</v>
       </c>
       <c r="H54" t="n">
-        <v>97</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>195.05</v>
+        <v>207.94</v>
       </c>
       <c r="K54" t="n">
-        <v>167.22</v>
+        <v>-101.51</v>
       </c>
       <c r="L54" t="n">
-        <v>256.91</v>
+        <v>231.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:42:56</t>
+          <t>08:31:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.38</v>
+        <v>3.98</v>
       </c>
       <c r="F55" t="n">
-        <v>10.92</v>
+        <v>6.89</v>
       </c>
       <c r="G55" t="n">
-        <v>294.9</v>
+        <v>306</v>
       </c>
       <c r="H55" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-247.46</v>
+        <v>-120.57</v>
       </c>
       <c r="K55" t="n">
-        <v>-22.55</v>
+        <v>-156.96</v>
       </c>
       <c r="L55" t="n">
-        <v>248.48</v>
+        <v>197.92</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:48:31</t>
+          <t>08:36:05</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.84</v>
+        <v>4.33</v>
       </c>
       <c r="F56" t="n">
-        <v>9.279999999999999</v>
+        <v>10.92</v>
       </c>
       <c r="G56" t="n">
-        <v>303.9</v>
+        <v>311.8</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>42.3</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-118</v>
+        <v>-273.6</v>
       </c>
       <c r="K56" t="n">
-        <v>392.13</v>
+        <v>192.36</v>
       </c>
       <c r="L56" t="n">
-        <v>409.5</v>
+        <v>334.46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:50:16</t>
+          <t>08:37:53</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.29</v>
+        <v>4.15</v>
       </c>
       <c r="F57" t="n">
-        <v>8.890000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="G57" t="n">
-        <v>298.8</v>
+        <v>293.5</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>60.3</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>345.49</v>
+        <v>-274.79</v>
       </c>
       <c r="K57" t="n">
-        <v>154.33</v>
+        <v>-126.44</v>
       </c>
       <c r="L57" t="n">
-        <v>378.39</v>
+        <v>302.49</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:51:39</t>
+          <t>08:40:09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.44</v>
+        <v>3.98</v>
       </c>
       <c r="F58" t="n">
-        <v>9.27</v>
+        <v>10.86</v>
       </c>
       <c r="G58" t="n">
-        <v>301.2</v>
+        <v>291.9</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-259.52</v>
+        <v>241.6</v>
       </c>
       <c r="K58" t="n">
-        <v>109.92</v>
+        <v>-352</v>
       </c>
       <c r="L58" t="n">
-        <v>281.84</v>
+        <v>426.94</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:02:37</t>
+          <t>08:52:15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.2</v>
+        <v>4.31</v>
       </c>
       <c r="F59" t="n">
-        <v>9.4</v>
+        <v>9.56</v>
       </c>
       <c r="G59" t="n">
-        <v>304.6</v>
+        <v>296.4</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>55.2</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-44.38</v>
+        <v>-70.01000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-55.73</v>
+        <v>-72.39</v>
       </c>
       <c r="L59" t="n">
-        <v>71.23999999999999</v>
+        <v>100.71</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:03:42</t>
+          <t>08:54:27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.4</v>
+        <v>4.47</v>
       </c>
       <c r="F60" t="n">
-        <v>10.04</v>
+        <v>10.92</v>
       </c>
       <c r="G60" t="n">
-        <v>307.6</v>
+        <v>302.2</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>31.7</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>102</v>
+        <v>30.98</v>
       </c>
       <c r="K60" t="n">
-        <v>-48.95</v>
+        <v>77.66</v>
       </c>
       <c r="L60" t="n">
-        <v>113.13</v>
+        <v>83.61</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:05:59</t>
+          <t>08:56:20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.28</v>
+        <v>3.96</v>
       </c>
       <c r="F61" t="n">
-        <v>10.23</v>
+        <v>10.9</v>
       </c>
       <c r="G61" t="n">
-        <v>300.5</v>
+        <v>298.9</v>
       </c>
       <c r="H61" t="n">
-        <v>94.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>4.62</v>
+        <v>-22.63</v>
       </c>
       <c r="K61" t="n">
-        <v>-91.72</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>91.83</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:11:32</t>
+          <t>09:00:56</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.61</v>
+        <v>4.43</v>
       </c>
       <c r="F62" t="n">
-        <v>10.92</v>
+        <v>9.77</v>
       </c>
       <c r="G62" t="n">
-        <v>302</v>
+        <v>295.3</v>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>41.6</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-90.48999999999999</v>
+        <v>-95.04000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-94.39</v>
+        <v>84.02</v>
       </c>
       <c r="L62" t="n">
-        <v>130.76</v>
+        <v>126.86</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:13:46</t>
+          <t>09:02:38</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.78</v>
+        <v>4.34</v>
       </c>
       <c r="F63" t="n">
-        <v>10.16</v>
+        <v>10.92</v>
       </c>
       <c r="G63" t="n">
-        <v>292.6</v>
+        <v>297.1</v>
       </c>
       <c r="H63" t="n">
-        <v>99.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>103.9</v>
+        <v>23.92</v>
       </c>
       <c r="K63" t="n">
-        <v>-70.56999999999999</v>
+        <v>114</v>
       </c>
       <c r="L63" t="n">
-        <v>125.59</v>
+        <v>116.48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:15:09</t>
+          <t>09:03:44</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="F64" t="n">
-        <v>10.14</v>
+        <v>10.92</v>
       </c>
       <c r="G64" t="n">
-        <v>287.1</v>
+        <v>304.4</v>
       </c>
       <c r="H64" t="n">
-        <v>97.5</v>
+        <v>63.8</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-13.1</v>
+        <v>-34.97</v>
       </c>
       <c r="K64" t="n">
-        <v>106.11</v>
+        <v>65.16</v>
       </c>
       <c r="L64" t="n">
-        <v>106.92</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:20:02</t>
+          <t>09:08:02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
       <c r="F65" t="n">
-        <v>10.74</v>
+        <v>8.24</v>
       </c>
       <c r="G65" t="n">
-        <v>290.3</v>
+        <v>307</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>2.45</v>
+        <v>-120.54</v>
       </c>
       <c r="K65" t="n">
-        <v>188.48</v>
+        <v>44.17</v>
       </c>
       <c r="L65" t="n">
-        <v>188.5</v>
+        <v>128.38</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:21:20</t>
+          <t>09:10:41</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.5</v>
+        <v>4.17</v>
       </c>
       <c r="F66" t="n">
-        <v>9.890000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="G66" t="n">
-        <v>298.2</v>
+        <v>299</v>
       </c>
       <c r="H66" t="n">
-        <v>100</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>99.64</v>
+        <v>119.88</v>
       </c>
       <c r="K66" t="n">
-        <v>135.08</v>
+        <v>-43.02</v>
       </c>
       <c r="L66" t="n">
-        <v>167.85</v>
+        <v>127.37</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:23:14</t>
+          <t>09:11:37</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.27</v>
+        <v>4.32</v>
       </c>
       <c r="F67" t="n">
-        <v>9.800000000000001</v>
+        <v>10.92</v>
       </c>
       <c r="G67" t="n">
-        <v>304.9</v>
+        <v>308</v>
       </c>
       <c r="H67" t="n">
-        <v>95.59999999999999</v>
+        <v>34.4</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-7.67</v>
+        <v>143.61</v>
       </c>
       <c r="K67" t="n">
-        <v>-252.21</v>
+        <v>-42.69</v>
       </c>
       <c r="L67" t="n">
-        <v>252.33</v>
+        <v>149.82</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:27:25</t>
+          <t>09:17:38</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.96</v>
+        <v>4.48</v>
       </c>
       <c r="F68" t="n">
-        <v>8.94</v>
+        <v>10.92</v>
       </c>
       <c r="G68" t="n">
-        <v>309.7</v>
+        <v>281.9</v>
       </c>
       <c r="H68" t="n">
-        <v>92.09999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="I68" t="n">
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>185.39</v>
+        <v>-292.11</v>
       </c>
       <c r="K68" t="n">
-        <v>123.83</v>
+        <v>25.96</v>
       </c>
       <c r="L68" t="n">
-        <v>222.94</v>
+        <v>293.26</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:29:22</t>
+          <t>09:18:50</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.49</v>
+        <v>4.1</v>
       </c>
       <c r="F69" t="n">
-        <v>10.92</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>287.2</v>
+        <v>307</v>
       </c>
       <c r="H69" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="I69" t="n">
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>123.55</v>
+        <v>100.41</v>
       </c>
       <c r="K69" t="n">
-        <v>214.93</v>
+        <v>138.82</v>
       </c>
       <c r="L69" t="n">
-        <v>247.91</v>
+        <v>171.33</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:30:13</t>
+          <t>09:19:57</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.23</v>
+        <v>4.68</v>
       </c>
       <c r="F70" t="n">
-        <v>10.92</v>
+        <v>10.36</v>
       </c>
       <c r="G70" t="n">
-        <v>293.8</v>
+        <v>285.7</v>
       </c>
       <c r="H70" t="n">
-        <v>100</v>
+        <v>7.7</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-192.38</v>
+        <v>-196.95</v>
       </c>
       <c r="K70" t="n">
-        <v>-94.12</v>
+        <v>100.07</v>
       </c>
       <c r="L70" t="n">
-        <v>214.17</v>
+        <v>220.92</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:33:47</t>
+          <t>09:22:52</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.1</v>
+        <v>4.24</v>
       </c>
       <c r="F71" t="n">
-        <v>9.470000000000001</v>
+        <v>10.68</v>
       </c>
       <c r="G71" t="n">
-        <v>315.3</v>
+        <v>305.6</v>
       </c>
       <c r="H71" t="n">
-        <v>98</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>280.09</v>
+        <v>-153.71</v>
       </c>
       <c r="K71" t="n">
-        <v>151.39</v>
+        <v>276.8</v>
       </c>
       <c r="L71" t="n">
-        <v>318.39</v>
+        <v>316.61</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:35:37</t>
+          <t>09:25:17</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.62</v>
+        <v>3.69</v>
       </c>
       <c r="F72" t="n">
-        <v>10.92</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>303.8</v>
+        <v>301.3</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>64.8</v>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>-266.08</v>
+        <v>1.76</v>
       </c>
       <c r="K72" t="n">
-        <v>269.01</v>
+        <v>-237.49</v>
       </c>
       <c r="L72" t="n">
-        <v>378.37</v>
+        <v>237.49</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:36:53</t>
+          <t>09:26:46</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.06</v>
+        <v>3.86</v>
       </c>
       <c r="F73" t="n">
-        <v>10.92</v>
+        <v>8.5</v>
       </c>
       <c r="G73" t="n">
-        <v>299.9</v>
+        <v>308</v>
       </c>
       <c r="H73" t="n">
-        <v>100</v>
+        <v>61.9</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>48.77</v>
+        <v>205.49</v>
       </c>
       <c r="K73" t="n">
-        <v>-579.76</v>
+        <v>106.24</v>
       </c>
       <c r="L73" t="n">
-        <v>581.8</v>
+        <v>231.33</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:47:31</t>
+          <t>09:36:43</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.86</v>
+        <v>3.97</v>
       </c>
       <c r="F74" t="n">
-        <v>10.92</v>
+        <v>9.6</v>
       </c>
       <c r="G74" t="n">
-        <v>287.4</v>
+        <v>318.2</v>
       </c>
       <c r="H74" t="n">
-        <v>96.40000000000001</v>
+        <v>50.3</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-15.55</v>
+        <v>-21.67</v>
       </c>
       <c r="K74" t="n">
-        <v>-78.81999999999999</v>
+        <v>-60.78</v>
       </c>
       <c r="L74" t="n">
-        <v>80.34</v>
+        <v>64.53</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:49:36</t>
+          <t>09:38:47</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.44</v>
+        <v>4.82</v>
       </c>
       <c r="F75" t="n">
         <v>10.92</v>
       </c>
       <c r="G75" t="n">
-        <v>311.6</v>
+        <v>304.9</v>
       </c>
       <c r="H75" t="n">
-        <v>100</v>
+        <v>90.2</v>
       </c>
       <c r="I75" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-130.79</v>
+        <v>-127.2</v>
       </c>
       <c r="K75" t="n">
-        <v>-9.390000000000001</v>
+        <v>-34.31</v>
       </c>
       <c r="L75" t="n">
-        <v>131.13</v>
+        <v>131.74</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:51:04</t>
+          <t>09:40:52</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.67</v>
+        <v>5.1</v>
       </c>
       <c r="F76" t="n">
         <v>10.92</v>
       </c>
       <c r="G76" t="n">
-        <v>311.8</v>
+        <v>305.3</v>
       </c>
       <c r="H76" t="n">
-        <v>97.2</v>
+        <v>87.5</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>57.15</v>
+        <v>-34.49</v>
       </c>
       <c r="K76" t="n">
-        <v>62.32</v>
+        <v>96.97</v>
       </c>
       <c r="L76" t="n">
-        <v>84.55</v>
+        <v>102.93</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:56:09</t>
+          <t>09:44:50</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.42</v>
+        <v>4.32</v>
       </c>
       <c r="F77" t="n">
-        <v>9.31</v>
+        <v>10.92</v>
       </c>
       <c r="G77" t="n">
-        <v>302.4</v>
+        <v>300.7</v>
       </c>
       <c r="H77" t="n">
-        <v>100</v>
+        <v>54.1</v>
       </c>
       <c r="I77" t="n">
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>107.7</v>
+        <v>13.97</v>
       </c>
       <c r="K77" t="n">
-        <v>118.71</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>160.28</v>
+        <v>96.26000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:58:02</t>
+          <t>09:46:04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.14</v>
+        <v>4.24</v>
       </c>
       <c r="F78" t="n">
-        <v>10.92</v>
+        <v>8.76</v>
       </c>
       <c r="G78" t="n">
-        <v>311.6</v>
+        <v>303</v>
       </c>
       <c r="H78" t="n">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>-58.11</v>
+        <v>97.34</v>
       </c>
       <c r="K78" t="n">
-        <v>-101.76</v>
+        <v>-32.73</v>
       </c>
       <c r="L78" t="n">
-        <v>117.18</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:00:25</t>
+          <t>09:48:20</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.69</v>
+        <v>4.49</v>
       </c>
       <c r="F79" t="n">
         <v>10.92</v>
       </c>
       <c r="G79" t="n">
-        <v>297</v>
+        <v>308.5</v>
       </c>
       <c r="H79" t="n">
-        <v>100</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I79" t="n">
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>51.43</v>
+        <v>-55.86</v>
       </c>
       <c r="K79" t="n">
-        <v>-83.03</v>
+        <v>-98.02</v>
       </c>
       <c r="L79" t="n">
-        <v>97.66</v>
+        <v>112.82</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:05:56</t>
+          <t>09:52:33</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.47</v>
+        <v>4.39</v>
       </c>
       <c r="F80" t="n">
-        <v>10.76</v>
+        <v>10.2</v>
       </c>
       <c r="G80" t="n">
-        <v>287.5</v>
+        <v>296.8</v>
       </c>
       <c r="H80" t="n">
-        <v>100</v>
+        <v>66.5</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>90.2</v>
+        <v>-156.45</v>
       </c>
       <c r="K80" t="n">
-        <v>-113.66</v>
+        <v>-76.52</v>
       </c>
       <c r="L80" t="n">
-        <v>145.1</v>
+        <v>174.17</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:06:57</t>
+          <t>09:54:04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.97</v>
+        <v>4.15</v>
       </c>
       <c r="F81" t="n">
-        <v>10.92</v>
+        <v>9.66</v>
       </c>
       <c r="G81" t="n">
-        <v>305.4</v>
+        <v>296</v>
       </c>
       <c r="H81" t="n">
-        <v>92.2</v>
+        <v>53.7</v>
       </c>
       <c r="I81" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>21.31</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-144.97</v>
+        <v>54.14</v>
       </c>
       <c r="L81" t="n">
-        <v>146.53</v>
+        <v>87.18000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:07:50</t>
+          <t>09:55:47</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.11</v>
+        <v>5.18</v>
       </c>
       <c r="F82" t="n">
-        <v>10</v>
+        <v>10.92</v>
       </c>
       <c r="G82" t="n">
-        <v>304.5</v>
+        <v>301.9</v>
       </c>
       <c r="H82" t="n">
-        <v>97.40000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>129.4</v>
+        <v>155.38</v>
       </c>
       <c r="K82" t="n">
-        <v>71.16</v>
+        <v>65.95</v>
       </c>
       <c r="L82" t="n">
-        <v>147.67</v>
+        <v>168.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:13:18</t>
+          <t>09:59:09</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.27</v>
+        <v>4.68</v>
       </c>
       <c r="F83" t="n">
-        <v>10.92</v>
+        <v>10.44</v>
       </c>
       <c r="G83" t="n">
-        <v>302.1</v>
+        <v>289.7</v>
       </c>
       <c r="H83" t="n">
-        <v>93.40000000000001</v>
+        <v>28</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-362.81</v>
+        <v>-186.83</v>
       </c>
       <c r="K83" t="n">
-        <v>-43.25</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>365.38</v>
+        <v>209.3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:14:06</t>
+          <t>10:00:49</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.21</v>
+        <v>4.67</v>
       </c>
       <c r="F84" t="n">
-        <v>8.140000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="G84" t="n">
-        <v>308.7</v>
+        <v>307.6</v>
       </c>
       <c r="H84" t="n">
-        <v>94.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-196.73</v>
+        <v>-155.6</v>
       </c>
       <c r="K84" t="n">
-        <v>-71.08</v>
+        <v>239.59</v>
       </c>
       <c r="L84" t="n">
-        <v>209.17</v>
+        <v>285.68</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:15:22</t>
+          <t>10:02:24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.67</v>
+        <v>4.86</v>
       </c>
       <c r="F85" t="n">
-        <v>9.08</v>
+        <v>10.92</v>
       </c>
       <c r="G85" t="n">
-        <v>296.3</v>
+        <v>295.6</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>42.2</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>108.77</v>
+        <v>-216.65</v>
       </c>
       <c r="K85" t="n">
-        <v>320.51</v>
+        <v>-141.84</v>
       </c>
       <c r="L85" t="n">
-        <v>338.46</v>
+        <v>258.96</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:19:26</t>
+          <t>10:06:16</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.32</v>
+        <v>4.07</v>
       </c>
       <c r="F86" t="n">
-        <v>10.92</v>
+        <v>10.48</v>
       </c>
       <c r="G86" t="n">
-        <v>308</v>
+        <v>312.7</v>
       </c>
       <c r="H86" t="n">
-        <v>93.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-178.97</v>
+        <v>-133.87</v>
       </c>
       <c r="K86" t="n">
-        <v>3.07</v>
+        <v>273.35</v>
       </c>
       <c r="L86" t="n">
-        <v>179</v>
+        <v>304.37</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:21:23</t>
+          <t>10:08:23</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.21</v>
+        <v>4.09</v>
       </c>
       <c r="F87" t="n">
-        <v>8.210000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="G87" t="n">
-        <v>307.8</v>
+        <v>301.7</v>
       </c>
       <c r="H87" t="n">
-        <v>100</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-79.06999999999999</v>
+        <v>290.31</v>
       </c>
       <c r="K87" t="n">
-        <v>262.45</v>
+        <v>-33.46</v>
       </c>
       <c r="L87" t="n">
-        <v>274.1</v>
+        <v>292.23</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:23:23</t>
+          <t>10:10:01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.21</v>
+        <v>4.61</v>
       </c>
       <c r="F88" t="n">
-        <v>10.92</v>
+        <v>10.78</v>
       </c>
       <c r="G88" t="n">
-        <v>296.8</v>
+        <v>309.9</v>
       </c>
       <c r="H88" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>119.36</v>
+        <v>-370.91</v>
       </c>
       <c r="K88" t="n">
-        <v>289.6</v>
+        <v>171.99</v>
       </c>
       <c r="L88" t="n">
-        <v>313.24</v>
+        <v>408.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-04.xlsx
+++ b/output/2024-04-04.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.49</v>
+        <v>3.62</v>
       </c>
       <c r="F14" t="n">
-        <v>3.79</v>
+        <v>4.54</v>
       </c>
       <c r="G14" t="n">
-        <v>302.8</v>
+        <v>290.3</v>
       </c>
       <c r="H14" t="n">
-        <v>53.8</v>
+        <v>83.2</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>52.44</v>
+        <v>-71.33</v>
       </c>
       <c r="K14" t="n">
-        <v>-29.88</v>
+        <v>11.12</v>
       </c>
       <c r="L14" t="n">
-        <v>60.35</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:38:13</t>
+          <t>06:38:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="F15" t="n">
-        <v>8.24</v>
+        <v>9.15</v>
       </c>
       <c r="G15" t="n">
-        <v>297.5</v>
+        <v>296.2</v>
       </c>
       <c r="H15" t="n">
-        <v>69.8</v>
+        <v>25.6</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-54.51</v>
+        <v>21.83</v>
       </c>
       <c r="K15" t="n">
-        <v>-30.83</v>
+        <v>52.4</v>
       </c>
       <c r="L15" t="n">
-        <v>62.62</v>
+        <v>56.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:40:37</t>
+          <t>06:39:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="F16" t="n">
-        <v>8.75</v>
+        <v>6.29</v>
       </c>
       <c r="G16" t="n">
-        <v>311.6</v>
+        <v>295.4</v>
       </c>
       <c r="H16" t="n">
-        <v>18.1</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>-53.46</v>
+        <v>27.95</v>
       </c>
       <c r="K16" t="n">
-        <v>13.82</v>
+        <v>-56.7</v>
       </c>
       <c r="L16" t="n">
-        <v>55.22</v>
+        <v>63.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:45:00</t>
+          <t>06:43:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.53</v>
+        <v>3.78</v>
       </c>
       <c r="F17" t="n">
         <v>10.92</v>
       </c>
       <c r="G17" t="n">
-        <v>306.6</v>
+        <v>303.4</v>
       </c>
       <c r="H17" t="n">
-        <v>83.5</v>
+        <v>30.9</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-47.11</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>36.58</v>
+        <v>37.37</v>
       </c>
       <c r="L17" t="n">
-        <v>59.65</v>
+        <v>82.73999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:46:18</t>
+          <t>06:44:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="F18" t="n">
-        <v>10.11</v>
+        <v>7.14</v>
       </c>
       <c r="G18" t="n">
-        <v>305</v>
+        <v>292.7</v>
       </c>
       <c r="H18" t="n">
-        <v>77.5</v>
+        <v>52.7</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>86.08</v>
+        <v>80.58</v>
       </c>
       <c r="K18" t="n">
-        <v>29.7</v>
+        <v>32.21</v>
       </c>
       <c r="L18" t="n">
-        <v>91.06</v>
+        <v>86.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:47:19</t>
+          <t>06:46:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.79</v>
+        <v>4.08</v>
       </c>
       <c r="F19" t="n">
-        <v>10.54</v>
+        <v>10.12</v>
       </c>
       <c r="G19" t="n">
-        <v>297</v>
+        <v>300.2</v>
       </c>
       <c r="H19" t="n">
-        <v>42.5</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J19" t="n">
-        <v>-111.76</v>
+        <v>4.34</v>
       </c>
       <c r="K19" t="n">
-        <v>0.61</v>
+        <v>93.13</v>
       </c>
       <c r="L19" t="n">
-        <v>111.76</v>
+        <v>93.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:52:09</t>
+          <t>06:49:54</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.96</v>
+        <v>3.83</v>
       </c>
       <c r="F20" t="n">
-        <v>8.41</v>
+        <v>10.04</v>
       </c>
       <c r="G20" t="n">
-        <v>312.5</v>
+        <v>280.7</v>
       </c>
       <c r="H20" t="n">
-        <v>60.2</v>
+        <v>62.7</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>114.65</v>
+        <v>-139.7</v>
       </c>
       <c r="K20" t="n">
-        <v>96.64</v>
+        <v>80.59</v>
       </c>
       <c r="L20" t="n">
-        <v>149.95</v>
+        <v>161.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:53:29</t>
+          <t>06:50:50</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.64</v>
+        <v>3.24</v>
       </c>
       <c r="F21" t="n">
-        <v>5.89</v>
+        <v>7.1</v>
       </c>
       <c r="G21" t="n">
-        <v>294.9</v>
+        <v>321.9</v>
       </c>
       <c r="H21" t="n">
-        <v>76.2</v>
+        <v>64.2</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-108.17</v>
+        <v>-88.36</v>
       </c>
       <c r="K21" t="n">
-        <v>100.75</v>
+        <v>-84.65000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>147.82</v>
+        <v>122.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:55:37</t>
+          <t>06:53:20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.46</v>
+        <v>3.66</v>
       </c>
       <c r="F22" t="n">
-        <v>7.04</v>
+        <v>6.73</v>
       </c>
       <c r="G22" t="n">
-        <v>294.6</v>
+        <v>294.3</v>
       </c>
       <c r="H22" t="n">
-        <v>58.8</v>
+        <v>59</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>56.56</v>
+        <v>128.13</v>
       </c>
       <c r="K22" t="n">
-        <v>124.55</v>
+        <v>50.1</v>
       </c>
       <c r="L22" t="n">
-        <v>136.79</v>
+        <v>137.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:59:55</t>
+          <t>06:58:29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.93</v>
+        <v>3.39</v>
       </c>
       <c r="F23" t="n">
-        <v>6.42</v>
+        <v>7.73</v>
       </c>
       <c r="G23" t="n">
-        <v>280.8</v>
+        <v>312.4</v>
       </c>
       <c r="H23" t="n">
-        <v>55.4</v>
+        <v>86.7</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>-218.17</v>
+        <v>-130.87</v>
       </c>
       <c r="K23" t="n">
-        <v>154.92</v>
+        <v>-120.89</v>
       </c>
       <c r="L23" t="n">
-        <v>267.58</v>
+        <v>178.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:01:11</t>
+          <t>06:59:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.17</v>
+        <v>4.09</v>
       </c>
       <c r="F24" t="n">
-        <v>8.390000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="G24" t="n">
-        <v>281.2</v>
+        <v>291</v>
       </c>
       <c r="H24" t="n">
-        <v>74.8</v>
+        <v>78.3</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-284.67</v>
+        <v>215.83</v>
       </c>
       <c r="K24" t="n">
-        <v>29.3</v>
+        <v>-206.63</v>
       </c>
       <c r="L24" t="n">
-        <v>286.18</v>
+        <v>298.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:02:43</t>
+          <t>07:02:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.41</v>
+        <v>3.55</v>
       </c>
       <c r="F25" t="n">
-        <v>9.800000000000001</v>
+        <v>7.78</v>
       </c>
       <c r="G25" t="n">
-        <v>308</v>
+        <v>287.5</v>
       </c>
       <c r="H25" t="n">
-        <v>32.1</v>
+        <v>78.3</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>223.27</v>
+        <v>-43.61</v>
       </c>
       <c r="K25" t="n">
-        <v>82.91</v>
+        <v>-178.93</v>
       </c>
       <c r="L25" t="n">
-        <v>238.16</v>
+        <v>184.17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:07:28</t>
+          <t>07:07:16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.49</v>
+        <v>3.77</v>
       </c>
       <c r="F26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="G26" t="n">
-        <v>300.4</v>
+        <v>302.3</v>
       </c>
       <c r="H26" t="n">
-        <v>59.9</v>
+        <v>29.3</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>44.08</v>
+        <v>13.97</v>
       </c>
       <c r="K26" t="n">
-        <v>-256.29</v>
+        <v>244.18</v>
       </c>
       <c r="L26" t="n">
-        <v>260.06</v>
+        <v>244.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:09:15</t>
+          <t>07:09:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1174,31 +1174,31 @@
         <v>3.66</v>
       </c>
       <c r="F27" t="n">
-        <v>9.34</v>
+        <v>8.59</v>
       </c>
       <c r="G27" t="n">
-        <v>304.1</v>
+        <v>286.6</v>
       </c>
       <c r="H27" t="n">
-        <v>54.4</v>
+        <v>45.2</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-232.7</v>
+        <v>99.73</v>
       </c>
       <c r="K27" t="n">
-        <v>-100.39</v>
+        <v>129.13</v>
       </c>
       <c r="L27" t="n">
-        <v>253.43</v>
+        <v>163.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:11:28</t>
+          <t>07:11:29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="F28" t="n">
-        <v>5.38</v>
+        <v>8.93</v>
       </c>
       <c r="G28" t="n">
-        <v>290.3</v>
+        <v>293.8</v>
       </c>
       <c r="H28" t="n">
-        <v>59.4</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J28" t="n">
-        <v>23.37</v>
+        <v>18.03</v>
       </c>
       <c r="K28" t="n">
-        <v>194.94</v>
+        <v>-142.2</v>
       </c>
       <c r="L28" t="n">
-        <v>196.34</v>
+        <v>143.34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:19:54</t>
+          <t>07:21:34</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="F29" t="n">
-        <v>8.81</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>300.1</v>
+        <v>299.7</v>
       </c>
       <c r="H29" t="n">
-        <v>44.3</v>
+        <v>51</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-51.57</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>-56.54</v>
+        <v>14.55</v>
       </c>
       <c r="L29" t="n">
-        <v>76.53</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:21:04</t>
+          <t>07:22:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.82</v>
+        <v>3.56</v>
       </c>
       <c r="F30" t="n">
-        <v>8.779999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="G30" t="n">
-        <v>310.8</v>
+        <v>302</v>
       </c>
       <c r="H30" t="n">
-        <v>79.5</v>
+        <v>42.8</v>
       </c>
       <c r="I30" t="n">
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>46.06</v>
+        <v>-40.33</v>
       </c>
       <c r="K30" t="n">
-        <v>-54.33</v>
+        <v>-47.79</v>
       </c>
       <c r="L30" t="n">
-        <v>71.23</v>
+        <v>62.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:23:01</t>
+          <t>07:24:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.63</v>
+        <v>4.11</v>
       </c>
       <c r="F31" t="n">
-        <v>10.92</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>295.4</v>
+        <v>306.4</v>
       </c>
       <c r="H31" t="n">
-        <v>18.6</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.7</v>
+        <v>20.31</v>
       </c>
       <c r="K31" t="n">
-        <v>66.90000000000001</v>
+        <v>-40.76</v>
       </c>
       <c r="L31" t="n">
-        <v>68.29000000000001</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:27:50</t>
+          <t>07:28:53</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.03</v>
+        <v>3.76</v>
       </c>
       <c r="F32" t="n">
-        <v>10.44</v>
+        <v>9.94</v>
       </c>
       <c r="G32" t="n">
-        <v>302.7</v>
+        <v>285.1</v>
       </c>
       <c r="H32" t="n">
-        <v>92.90000000000001</v>
+        <v>50.4</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-68.40000000000001</v>
+        <v>-59.15</v>
       </c>
       <c r="K32" t="n">
-        <v>64.78</v>
+        <v>43.32</v>
       </c>
       <c r="L32" t="n">
-        <v>94.20999999999999</v>
+        <v>73.31999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:29:07</t>
+          <t>07:30:18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.92</v>
+        <v>3.65</v>
       </c>
       <c r="F33" t="n">
-        <v>8.92</v>
+        <v>10.16</v>
       </c>
       <c r="G33" t="n">
-        <v>286.1</v>
+        <v>296.1</v>
       </c>
       <c r="H33" t="n">
-        <v>73.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J33" t="n">
-        <v>43.4</v>
+        <v>95.06</v>
       </c>
       <c r="K33" t="n">
-        <v>-86.76000000000001</v>
+        <v>19.62</v>
       </c>
       <c r="L33" t="n">
-        <v>97.01000000000001</v>
+        <v>97.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:30:33</t>
+          <t>07:31:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.87</v>
+        <v>3.96</v>
       </c>
       <c r="F34" t="n">
-        <v>10.32</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>309</v>
+        <v>292.8</v>
       </c>
       <c r="H34" t="n">
-        <v>51.7</v>
+        <v>98.8</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-64.25</v>
+        <v>-53.48</v>
       </c>
       <c r="K34" t="n">
-        <v>-78.34</v>
+        <v>-78.03</v>
       </c>
       <c r="L34" t="n">
-        <v>101.31</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:35:38</t>
+          <t>07:36:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.65</v>
+        <v>4.34</v>
       </c>
       <c r="F35" t="n">
-        <v>9.199999999999999</v>
+        <v>10.24</v>
       </c>
       <c r="G35" t="n">
-        <v>303.1</v>
+        <v>294.2</v>
       </c>
       <c r="H35" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J35" t="n">
-        <v>-107.79</v>
+        <v>31.06</v>
       </c>
       <c r="K35" t="n">
-        <v>80.08</v>
+        <v>184.06</v>
       </c>
       <c r="L35" t="n">
-        <v>134.28</v>
+        <v>186.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:37:48</t>
+          <t>07:37:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="F36" t="n">
-        <v>5.42</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>296.3</v>
+        <v>307.9</v>
       </c>
       <c r="H36" t="n">
-        <v>60.3</v>
+        <v>67.5</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>0.13</v>
+        <v>143.57</v>
       </c>
       <c r="K36" t="n">
-        <v>117.38</v>
+        <v>45.43</v>
       </c>
       <c r="L36" t="n">
-        <v>117.38</v>
+        <v>150.59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:39:15</t>
+          <t>07:39:11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.38</v>
+        <v>3.84</v>
       </c>
       <c r="F37" t="n">
-        <v>10.09</v>
+        <v>10.92</v>
       </c>
       <c r="G37" t="n">
-        <v>308.9</v>
+        <v>300.8</v>
       </c>
       <c r="H37" t="n">
-        <v>96.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-182.87</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>3.25</v>
+        <v>148.49</v>
       </c>
       <c r="L37" t="n">
-        <v>182.9</v>
+        <v>165.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:44:00</t>
+          <t>07:43:39</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.15</v>
+        <v>4.49</v>
       </c>
       <c r="F38" t="n">
-        <v>9.789999999999999</v>
+        <v>10.92</v>
       </c>
       <c r="G38" t="n">
-        <v>302.9</v>
+        <v>285.4</v>
       </c>
       <c r="H38" t="n">
-        <v>61</v>
+        <v>58.2</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>276.89</v>
+        <v>-170.04</v>
       </c>
       <c r="K38" t="n">
-        <v>95.09</v>
+        <v>-205.09</v>
       </c>
       <c r="L38" t="n">
-        <v>292.77</v>
+        <v>266.41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:45:37</t>
+          <t>07:45:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.93</v>
+        <v>4.31</v>
       </c>
       <c r="F39" t="n">
-        <v>9.69</v>
+        <v>10.26</v>
       </c>
       <c r="G39" t="n">
-        <v>311.1</v>
+        <v>308.2</v>
       </c>
       <c r="H39" t="n">
-        <v>64.2</v>
+        <v>59</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>156.72</v>
+        <v>176.5</v>
       </c>
       <c r="K39" t="n">
-        <v>-127.04</v>
+        <v>-222.05</v>
       </c>
       <c r="L39" t="n">
-        <v>201.74</v>
+        <v>283.65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:47:00</t>
+          <t>07:46:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.47</v>
+        <v>3.87</v>
       </c>
       <c r="F40" t="n">
-        <v>9.73</v>
+        <v>8.85</v>
       </c>
       <c r="G40" t="n">
-        <v>284.5</v>
+        <v>297.3</v>
       </c>
       <c r="H40" t="n">
-        <v>68.2</v>
+        <v>52.8</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J40" t="n">
-        <v>-195.01</v>
+        <v>-45.9</v>
       </c>
       <c r="K40" t="n">
-        <v>-132.04</v>
+        <v>245.68</v>
       </c>
       <c r="L40" t="n">
-        <v>235.51</v>
+        <v>249.93</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:51:15</t>
+          <t>07:51:55</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.71</v>
+        <v>3.35</v>
       </c>
       <c r="F41" t="n">
-        <v>8.289999999999999</v>
+        <v>7.21</v>
       </c>
       <c r="G41" t="n">
-        <v>286.5</v>
+        <v>311.3</v>
       </c>
       <c r="H41" t="n">
-        <v>35.9</v>
+        <v>79.3</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-65.63</v>
+        <v>199.96</v>
       </c>
       <c r="K41" t="n">
-        <v>246.87</v>
+        <v>-126.98</v>
       </c>
       <c r="L41" t="n">
-        <v>255.44</v>
+        <v>236.87</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:52:27</t>
+          <t>07:54:38</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.27</v>
+        <v>3.71</v>
       </c>
       <c r="F42" t="n">
-        <v>10.92</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>294.3</v>
+        <v>303.6</v>
       </c>
       <c r="H42" t="n">
-        <v>48.8</v>
+        <v>26.3</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-294.93</v>
+        <v>320.23</v>
       </c>
       <c r="K42" t="n">
-        <v>-35.7</v>
+        <v>-48.1</v>
       </c>
       <c r="L42" t="n">
-        <v>297.08</v>
+        <v>323.82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:53:51</t>
+          <t>07:57:06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="F43" t="n">
-        <v>8.779999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="G43" t="n">
-        <v>299.8</v>
+        <v>307.5</v>
       </c>
       <c r="H43" t="n">
-        <v>61.4</v>
+        <v>42.7</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>48.8</v>
+        <v>-48.19</v>
       </c>
       <c r="K43" t="n">
-        <v>-298.76</v>
+        <v>286.09</v>
       </c>
       <c r="L43" t="n">
-        <v>302.72</v>
+        <v>290.12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:05:40</t>
+          <t>08:05:21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.24</v>
+        <v>4.14</v>
       </c>
       <c r="F44" t="n">
-        <v>10.72</v>
+        <v>8.49</v>
       </c>
       <c r="G44" t="n">
-        <v>292</v>
+        <v>303.6</v>
       </c>
       <c r="H44" t="n">
-        <v>60.7</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>-49.72</v>
+        <v>66.22</v>
       </c>
       <c r="K44" t="n">
-        <v>52.98</v>
+        <v>-20.05</v>
       </c>
       <c r="L44" t="n">
-        <v>72.66</v>
+        <v>69.19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:06:27</t>
+          <t>08:06:52</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.77</v>
+        <v>4.36</v>
       </c>
       <c r="F45" t="n">
-        <v>8.470000000000001</v>
+        <v>10.92</v>
       </c>
       <c r="G45" t="n">
-        <v>299.6</v>
+        <v>309.2</v>
       </c>
       <c r="H45" t="n">
-        <v>46</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-118.37</v>
+        <v>-73.78</v>
       </c>
       <c r="K45" t="n">
-        <v>13.6</v>
+        <v>41.61</v>
       </c>
       <c r="L45" t="n">
-        <v>119.15</v>
+        <v>84.70999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:08:01</t>
+          <t>08:09:11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.19</v>
+        <v>4.31</v>
       </c>
       <c r="F46" t="n">
-        <v>8.81</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>288.4</v>
+        <v>294.4</v>
       </c>
       <c r="H46" t="n">
-        <v>55.6</v>
+        <v>25.4</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>43.17</v>
+        <v>63.06</v>
       </c>
       <c r="K46" t="n">
-        <v>-52.88</v>
+        <v>40.53</v>
       </c>
       <c r="L46" t="n">
-        <v>68.26000000000001</v>
+        <v>74.95999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:11:23</t>
+          <t>08:14:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.28</v>
+        <v>4.55</v>
       </c>
       <c r="F47" t="n">
-        <v>9.369999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="G47" t="n">
-        <v>302.7</v>
+        <v>311.5</v>
       </c>
       <c r="H47" t="n">
-        <v>57.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>73.04000000000001</v>
+        <v>113.11</v>
       </c>
       <c r="K47" t="n">
-        <v>17.96</v>
+        <v>-63.85</v>
       </c>
       <c r="L47" t="n">
-        <v>75.22</v>
+        <v>129.89</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:12:39</t>
+          <t>08:16:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.37</v>
+        <v>4.43</v>
       </c>
       <c r="F48" t="n">
-        <v>8.16</v>
+        <v>10.92</v>
       </c>
       <c r="G48" t="n">
-        <v>285.7</v>
+        <v>297.2</v>
       </c>
       <c r="H48" t="n">
-        <v>65.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>63.77</v>
+        <v>34.83</v>
       </c>
       <c r="K48" t="n">
-        <v>41.6</v>
+        <v>105.88</v>
       </c>
       <c r="L48" t="n">
-        <v>76.14</v>
+        <v>111.46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:13:45</t>
+          <t>08:17:22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="F49" t="n">
-        <v>10.63</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>302.9</v>
+        <v>302.1</v>
       </c>
       <c r="H49" t="n">
-        <v>65.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.73</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>73.64</v>
+        <v>-1.08</v>
       </c>
       <c r="L49" t="n">
-        <v>73.79000000000001</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:18:26</t>
+          <t>08:21:46</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.23</v>
+        <v>4.58</v>
       </c>
       <c r="F50" t="n">
-        <v>7.44</v>
+        <v>10.55</v>
       </c>
       <c r="G50" t="n">
-        <v>305.5</v>
+        <v>291.7</v>
       </c>
       <c r="H50" t="n">
-        <v>61.5</v>
+        <v>71.5</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-85.06999999999999</v>
+        <v>45.48</v>
       </c>
       <c r="K50" t="n">
-        <v>-54.13</v>
+        <v>-132.94</v>
       </c>
       <c r="L50" t="n">
-        <v>100.83</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:20:23</t>
+          <t>08:24:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="F51" t="n">
-        <v>10.66</v>
+        <v>10.92</v>
       </c>
       <c r="G51" t="n">
-        <v>301.2</v>
+        <v>303.7</v>
       </c>
       <c r="H51" t="n">
-        <v>27.8</v>
+        <v>53.2</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-128.73</v>
+        <v>116.05</v>
       </c>
       <c r="K51" t="n">
-        <v>-27.48</v>
+        <v>184.72</v>
       </c>
       <c r="L51" t="n">
-        <v>131.63</v>
+        <v>218.14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:21:45</t>
+          <t>08:25:24</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="F52" t="n">
         <v>10.92</v>
       </c>
       <c r="G52" t="n">
-        <v>299.6</v>
+        <v>287.9</v>
       </c>
       <c r="H52" t="n">
-        <v>53.3</v>
+        <v>48.7</v>
       </c>
       <c r="I52" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>101.98</v>
+        <v>-108.04</v>
       </c>
       <c r="K52" t="n">
-        <v>-59.17</v>
+        <v>126.8</v>
       </c>
       <c r="L52" t="n">
-        <v>117.91</v>
+        <v>166.59</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:27:24</t>
+          <t>08:30:43</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.33</v>
+        <v>3.83</v>
       </c>
       <c r="F53" t="n">
-        <v>7.76</v>
+        <v>8.57</v>
       </c>
       <c r="G53" t="n">
-        <v>308.2</v>
+        <v>303.8</v>
       </c>
       <c r="H53" t="n">
-        <v>85.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J53" t="n">
-        <v>40.81</v>
+        <v>-194.35</v>
       </c>
       <c r="K53" t="n">
-        <v>144.9</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>150.54</v>
+        <v>205.98</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:29:08</t>
+          <t>08:31:38</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.02</v>
+        <v>4.51</v>
       </c>
       <c r="F54" t="n">
-        <v>9.69</v>
+        <v>10.46</v>
       </c>
       <c r="G54" t="n">
-        <v>290.2</v>
+        <v>276.9</v>
       </c>
       <c r="H54" t="n">
-        <v>84.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J54" t="n">
-        <v>207.94</v>
+        <v>-276.12</v>
       </c>
       <c r="K54" t="n">
-        <v>-101.51</v>
+        <v>0.7</v>
       </c>
       <c r="L54" t="n">
-        <v>231.4</v>
+        <v>276.12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:31:00</t>
+          <t>08:34:19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.98</v>
+        <v>4.12</v>
       </c>
       <c r="F55" t="n">
-        <v>6.89</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>306</v>
+        <v>291.1</v>
       </c>
       <c r="H55" t="n">
-        <v>79</v>
+        <v>83.3</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-120.57</v>
+        <v>130.83</v>
       </c>
       <c r="K55" t="n">
-        <v>-156.96</v>
+        <v>138.38</v>
       </c>
       <c r="L55" t="n">
-        <v>197.92</v>
+        <v>190.43</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:36:05</t>
+          <t>08:39:48</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="F56" t="n">
         <v>10.92</v>
       </c>
       <c r="G56" t="n">
-        <v>311.8</v>
+        <v>290.4</v>
       </c>
       <c r="H56" t="n">
-        <v>42.3</v>
+        <v>37.2</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-273.6</v>
+        <v>138.94</v>
       </c>
       <c r="K56" t="n">
-        <v>192.36</v>
+        <v>235.67</v>
       </c>
       <c r="L56" t="n">
-        <v>334.46</v>
+        <v>273.58</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:37:53</t>
+          <t>08:40:23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="F57" t="n">
-        <v>9.26</v>
+        <v>10.92</v>
       </c>
       <c r="G57" t="n">
-        <v>293.5</v>
+        <v>293.1</v>
       </c>
       <c r="H57" t="n">
-        <v>60.3</v>
+        <v>75.5</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-274.79</v>
+        <v>-365.16</v>
       </c>
       <c r="K57" t="n">
-        <v>-126.44</v>
+        <v>-19.91</v>
       </c>
       <c r="L57" t="n">
-        <v>302.49</v>
+        <v>365.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:40:09</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.98</v>
+        <v>4.74</v>
       </c>
       <c r="F58" t="n">
-        <v>10.86</v>
+        <v>9.06</v>
       </c>
       <c r="G58" t="n">
-        <v>291.9</v>
+        <v>308.4</v>
       </c>
       <c r="H58" t="n">
-        <v>80</v>
+        <v>64.8</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>241.6</v>
+        <v>319.13</v>
       </c>
       <c r="K58" t="n">
-        <v>-352</v>
+        <v>212.74</v>
       </c>
       <c r="L58" t="n">
-        <v>426.94</v>
+        <v>383.54</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:52:15</t>
+          <t>08:52:25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.31</v>
+        <v>3.73</v>
       </c>
       <c r="F59" t="n">
-        <v>9.56</v>
+        <v>10.21</v>
       </c>
       <c r="G59" t="n">
-        <v>296.4</v>
+        <v>285.2</v>
       </c>
       <c r="H59" t="n">
-        <v>55.2</v>
+        <v>48.6</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-70.01000000000001</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-72.39</v>
+        <v>31.13</v>
       </c>
       <c r="L59" t="n">
-        <v>100.71</v>
+        <v>78.70999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:54:27</t>
+          <t>08:53:49</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.47</v>
+        <v>4.18</v>
       </c>
       <c r="F60" t="n">
         <v>10.92</v>
       </c>
       <c r="G60" t="n">
-        <v>302.2</v>
+        <v>296.1</v>
       </c>
       <c r="H60" t="n">
-        <v>31.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>30.98</v>
+        <v>-103.36</v>
       </c>
       <c r="K60" t="n">
-        <v>77.66</v>
+        <v>-6.79</v>
       </c>
       <c r="L60" t="n">
-        <v>83.61</v>
+        <v>103.58</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:56:20</t>
+          <t>08:54:58</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.96</v>
+        <v>4.35</v>
       </c>
       <c r="F61" t="n">
-        <v>10.9</v>
+        <v>10.49</v>
       </c>
       <c r="G61" t="n">
-        <v>298.9</v>
+        <v>296.2</v>
       </c>
       <c r="H61" t="n">
-        <v>72.40000000000001</v>
+        <v>51</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>-22.63</v>
+        <v>53.17</v>
       </c>
       <c r="K61" t="n">
-        <v>74.15000000000001</v>
+        <v>59.88</v>
       </c>
       <c r="L61" t="n">
-        <v>77.52</v>
+        <v>80.08</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:00:56</t>
+          <t>08:57:58</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.43</v>
+        <v>4.07</v>
       </c>
       <c r="F62" t="n">
-        <v>9.77</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>295.3</v>
+        <v>294.7</v>
       </c>
       <c r="H62" t="n">
-        <v>41.6</v>
+        <v>74</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-95.04000000000001</v>
+        <v>-57.56</v>
       </c>
       <c r="K62" t="n">
-        <v>84.02</v>
+        <v>-107.33</v>
       </c>
       <c r="L62" t="n">
-        <v>126.86</v>
+        <v>121.79</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:02:38</t>
+          <t>08:59:22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.34</v>
+        <v>4.78</v>
       </c>
       <c r="F63" t="n">
         <v>10.92</v>
       </c>
       <c r="G63" t="n">
-        <v>297.1</v>
+        <v>294.7</v>
       </c>
       <c r="H63" t="n">
-        <v>65</v>
+        <v>51.1</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>23.92</v>
+        <v>-122.13</v>
       </c>
       <c r="K63" t="n">
-        <v>114</v>
+        <v>55.83</v>
       </c>
       <c r="L63" t="n">
-        <v>116.48</v>
+        <v>134.29</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:03:44</t>
+          <t>09:00:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.89</v>
+        <v>4.49</v>
       </c>
       <c r="F64" t="n">
         <v>10.92</v>
       </c>
       <c r="G64" t="n">
-        <v>304.4</v>
+        <v>302.2</v>
       </c>
       <c r="H64" t="n">
-        <v>63.8</v>
+        <v>31.7</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-34.97</v>
+        <v>81.59</v>
       </c>
       <c r="K64" t="n">
-        <v>65.16</v>
+        <v>101.68</v>
       </c>
       <c r="L64" t="n">
-        <v>73.95</v>
+        <v>130.37</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:08:02</t>
+          <t>09:05:56</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
-        <v>8.24</v>
+        <v>10.92</v>
       </c>
       <c r="G65" t="n">
-        <v>307</v>
+        <v>298.9</v>
       </c>
       <c r="H65" t="n">
-        <v>68.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J65" t="n">
-        <v>-120.54</v>
+        <v>-15.25</v>
       </c>
       <c r="K65" t="n">
-        <v>44.17</v>
+        <v>179.81</v>
       </c>
       <c r="L65" t="n">
-        <v>128.38</v>
+        <v>180.45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:10:41</t>
+          <t>09:07:25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.17</v>
+        <v>4.46</v>
       </c>
       <c r="F66" t="n">
-        <v>8.98</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>299</v>
+        <v>295.3</v>
       </c>
       <c r="H66" t="n">
-        <v>70.90000000000001</v>
+        <v>41.6</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>119.88</v>
+        <v>-139.73</v>
       </c>
       <c r="K66" t="n">
-        <v>-43.02</v>
+        <v>149.51</v>
       </c>
       <c r="L66" t="n">
-        <v>127.37</v>
+        <v>204.64</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:11:37</t>
+          <t>09:09:06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="F67" t="n">
         <v>10.92</v>
       </c>
       <c r="G67" t="n">
-        <v>308</v>
+        <v>297.1</v>
       </c>
       <c r="H67" t="n">
-        <v>34.4</v>
+        <v>65</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>143.61</v>
+        <v>90.47</v>
       </c>
       <c r="K67" t="n">
-        <v>-42.69</v>
+        <v>166.94</v>
       </c>
       <c r="L67" t="n">
-        <v>149.82</v>
+        <v>189.88</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:17:38</t>
+          <t>09:12:46</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.48</v>
+        <v>3.92</v>
       </c>
       <c r="F68" t="n">
         <v>10.92</v>
       </c>
       <c r="G68" t="n">
-        <v>281.9</v>
+        <v>304.4</v>
       </c>
       <c r="H68" t="n">
-        <v>62.5</v>
+        <v>63.8</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-292.11</v>
+        <v>-74.28</v>
       </c>
       <c r="K68" t="n">
-        <v>25.96</v>
+        <v>203.32</v>
       </c>
       <c r="L68" t="n">
-        <v>293.26</v>
+        <v>216.47</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:18:50</t>
+          <t>09:14:12</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="F69" t="n">
-        <v>8.210000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="G69" t="n">
         <v>307</v>
       </c>
       <c r="H69" t="n">
-        <v>49</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>100.41</v>
+        <v>-244.79</v>
       </c>
       <c r="K69" t="n">
-        <v>138.82</v>
+        <v>65.2</v>
       </c>
       <c r="L69" t="n">
-        <v>171.33</v>
+        <v>253.32</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:19:57</t>
+          <t>09:15:41</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.68</v>
+        <v>4.19</v>
       </c>
       <c r="F70" t="n">
-        <v>10.36</v>
+        <v>9.06</v>
       </c>
       <c r="G70" t="n">
-        <v>285.7</v>
+        <v>299</v>
       </c>
       <c r="H70" t="n">
-        <v>7.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I70" t="n">
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-196.95</v>
+        <v>228.64</v>
       </c>
       <c r="K70" t="n">
-        <v>100.07</v>
+        <v>-92.56</v>
       </c>
       <c r="L70" t="n">
-        <v>220.92</v>
+        <v>246.67</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:22:52</t>
+          <t>09:19:49</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.24</v>
+        <v>4.35</v>
       </c>
       <c r="F71" t="n">
-        <v>10.68</v>
+        <v>10.92</v>
       </c>
       <c r="G71" t="n">
-        <v>305.6</v>
+        <v>308</v>
       </c>
       <c r="H71" t="n">
-        <v>70.90000000000001</v>
+        <v>34.4</v>
       </c>
       <c r="I71" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J71" t="n">
-        <v>-153.71</v>
+        <v>321.25</v>
       </c>
       <c r="K71" t="n">
-        <v>276.8</v>
+        <v>-129.14</v>
       </c>
       <c r="L71" t="n">
-        <v>316.61</v>
+        <v>346.24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:25:17</t>
+          <t>09:21:51</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.69</v>
+        <v>4.49</v>
       </c>
       <c r="F72" t="n">
-        <v>9.779999999999999</v>
+        <v>10.92</v>
       </c>
       <c r="G72" t="n">
-        <v>301.3</v>
+        <v>281.9</v>
       </c>
       <c r="H72" t="n">
-        <v>64.8</v>
+        <v>62.5</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>1.76</v>
+        <v>-442.46</v>
       </c>
       <c r="K72" t="n">
-        <v>-237.49</v>
+        <v>20.97</v>
       </c>
       <c r="L72" t="n">
-        <v>237.49</v>
+        <v>442.95</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:26:46</t>
+          <t>09:23:58</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.86</v>
+        <v>4.12</v>
       </c>
       <c r="F73" t="n">
-        <v>8.5</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H73" t="n">
-        <v>61.9</v>
+        <v>49</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>205.49</v>
+        <v>204.59</v>
       </c>
       <c r="K73" t="n">
-        <v>106.24</v>
+        <v>160.1</v>
       </c>
       <c r="L73" t="n">
-        <v>231.33</v>
+        <v>259.79</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:36:43</t>
+          <t>09:36:04</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.97</v>
+        <v>4.73</v>
       </c>
       <c r="F74" t="n">
-        <v>9.6</v>
+        <v>10.58</v>
       </c>
       <c r="G74" t="n">
-        <v>318.2</v>
+        <v>285.7</v>
       </c>
       <c r="H74" t="n">
-        <v>50.3</v>
+        <v>7.7</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-21.67</v>
+        <v>-74.05</v>
       </c>
       <c r="K74" t="n">
-        <v>-60.78</v>
+        <v>44.29</v>
       </c>
       <c r="L74" t="n">
-        <v>64.53</v>
+        <v>86.29000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:38:47</t>
+          <t>09:37:56</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.82</v>
+        <v>4.29</v>
       </c>
       <c r="F75" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
       </c>
       <c r="G75" t="n">
-        <v>304.9</v>
+        <v>305.6</v>
       </c>
       <c r="H75" t="n">
-        <v>90.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>-127.2</v>
+        <v>-32.46</v>
       </c>
       <c r="K75" t="n">
-        <v>-34.31</v>
+        <v>84.53</v>
       </c>
       <c r="L75" t="n">
-        <v>131.74</v>
+        <v>90.55</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:40:52</t>
+          <t>09:40:18</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.1</v>
+        <v>3.74</v>
       </c>
       <c r="F76" t="n">
-        <v>10.92</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>305.3</v>
+        <v>301.3</v>
       </c>
       <c r="H76" t="n">
-        <v>87.5</v>
+        <v>64.8</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-34.49</v>
+        <v>13.85</v>
       </c>
       <c r="K76" t="n">
-        <v>96.97</v>
+        <v>-63.2</v>
       </c>
       <c r="L76" t="n">
-        <v>102.93</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:44:50</t>
+          <t>09:44:15</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.32</v>
+        <v>3.91</v>
       </c>
       <c r="F77" t="n">
-        <v>10.92</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>300.7</v>
+        <v>308</v>
       </c>
       <c r="H77" t="n">
-        <v>54.1</v>
+        <v>61.9</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>13.97</v>
+        <v>82.66</v>
       </c>
       <c r="K77" t="n">
-        <v>95.23999999999999</v>
+        <v>20.73</v>
       </c>
       <c r="L77" t="n">
-        <v>96.26000000000001</v>
+        <v>85.22</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:46:04</t>
+          <t>09:46:31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.24</v>
+        <v>4</v>
       </c>
       <c r="F78" t="n">
-        <v>8.76</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>303</v>
+        <v>318.2</v>
       </c>
       <c r="H78" t="n">
-        <v>92.5</v>
+        <v>50.3</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>97.34</v>
+        <v>-10.69</v>
       </c>
       <c r="K78" t="n">
-        <v>-32.73</v>
+        <v>-91.64</v>
       </c>
       <c r="L78" t="n">
-        <v>102.7</v>
+        <v>92.26000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:48:20</t>
+          <t>09:48:44</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.49</v>
+        <v>4.85</v>
       </c>
       <c r="F79" t="n">
         <v>10.92</v>
       </c>
       <c r="G79" t="n">
-        <v>308.5</v>
+        <v>304.9</v>
       </c>
       <c r="H79" t="n">
-        <v>69.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-55.86</v>
+        <v>-162.87</v>
       </c>
       <c r="K79" t="n">
-        <v>-98.02</v>
+        <v>-93.90000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>112.82</v>
+        <v>188</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:52:33</t>
+          <t>09:53:47</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.39</v>
+        <v>5.14</v>
       </c>
       <c r="F80" t="n">
-        <v>10.2</v>
+        <v>10.92</v>
       </c>
       <c r="G80" t="n">
-        <v>296.8</v>
+        <v>305.3</v>
       </c>
       <c r="H80" t="n">
-        <v>66.5</v>
+        <v>87.5</v>
       </c>
       <c r="I80" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-156.45</v>
+        <v>-25.89</v>
       </c>
       <c r="K80" t="n">
-        <v>-76.52</v>
+        <v>191.76</v>
       </c>
       <c r="L80" t="n">
-        <v>174.17</v>
+        <v>193.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:54:04</t>
+          <t>09:56:05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="F81" t="n">
-        <v>9.66</v>
+        <v>10.92</v>
       </c>
       <c r="G81" t="n">
-        <v>296</v>
+        <v>300.7</v>
       </c>
       <c r="H81" t="n">
-        <v>53.7</v>
+        <v>54.1</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>68.31999999999999</v>
+        <v>59.65</v>
       </c>
       <c r="K81" t="n">
-        <v>54.14</v>
+        <v>130.99</v>
       </c>
       <c r="L81" t="n">
-        <v>87.18000000000001</v>
+        <v>143.93</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:55:47</t>
+          <t>09:56:49</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.18</v>
+        <v>4.27</v>
       </c>
       <c r="F82" t="n">
-        <v>10.92</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>301.9</v>
+        <v>303</v>
       </c>
       <c r="H82" t="n">
-        <v>62.6</v>
+        <v>92.5</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>155.38</v>
+        <v>143.99</v>
       </c>
       <c r="K82" t="n">
-        <v>65.95</v>
+        <v>-58.69</v>
       </c>
       <c r="L82" t="n">
-        <v>168.8</v>
+        <v>155.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:59:09</t>
+          <t>10:01:47</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.68</v>
+        <v>4.53</v>
       </c>
       <c r="F83" t="n">
-        <v>10.44</v>
+        <v>10.92</v>
       </c>
       <c r="G83" t="n">
-        <v>289.7</v>
+        <v>308.5</v>
       </c>
       <c r="H83" t="n">
-        <v>28</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-186.83</v>
+        <v>-61.52</v>
       </c>
       <c r="K83" t="n">
-        <v>94.34999999999999</v>
+        <v>-257.55</v>
       </c>
       <c r="L83" t="n">
-        <v>209.3</v>
+        <v>264.8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:00:49</t>
+          <t>10:03:05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.67</v>
+        <v>4.42</v>
       </c>
       <c r="F84" t="n">
-        <v>10.35</v>
+        <v>10.32</v>
       </c>
       <c r="G84" t="n">
-        <v>307.6</v>
+        <v>296.8</v>
       </c>
       <c r="H84" t="n">
-        <v>65.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-155.6</v>
+        <v>-226.02</v>
       </c>
       <c r="K84" t="n">
-        <v>239.59</v>
+        <v>-193.91</v>
       </c>
       <c r="L84" t="n">
-        <v>285.68</v>
+        <v>297.8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:02:24</t>
+          <t>10:04:44</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.86</v>
+        <v>4.18</v>
       </c>
       <c r="F85" t="n">
-        <v>10.92</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G85" t="n">
-        <v>295.6</v>
+        <v>296</v>
       </c>
       <c r="H85" t="n">
-        <v>42.2</v>
+        <v>53.7</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-216.65</v>
+        <v>188.71</v>
       </c>
       <c r="K85" t="n">
-        <v>-141.84</v>
+        <v>62.15</v>
       </c>
       <c r="L85" t="n">
-        <v>258.96</v>
+        <v>198.68</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:06:16</t>
+          <t>10:08:12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.07</v>
+        <v>5.22</v>
       </c>
       <c r="F86" t="n">
-        <v>10.48</v>
+        <v>10.92</v>
       </c>
       <c r="G86" t="n">
-        <v>312.7</v>
+        <v>301.9</v>
       </c>
       <c r="H86" t="n">
-        <v>86.8</v>
+        <v>62.6</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J86" t="n">
-        <v>-133.87</v>
+        <v>330.66</v>
       </c>
       <c r="K86" t="n">
-        <v>273.35</v>
+        <v>54.83</v>
       </c>
       <c r="L86" t="n">
-        <v>304.37</v>
+        <v>335.17</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:08:23</t>
+          <t>10:09:57</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.09</v>
+        <v>4.71</v>
       </c>
       <c r="F87" t="n">
-        <v>10.47</v>
+        <v>10.56</v>
       </c>
       <c r="G87" t="n">
-        <v>301.7</v>
+        <v>289.7</v>
       </c>
       <c r="H87" t="n">
-        <v>73.40000000000001</v>
+        <v>28</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>290.31</v>
+        <v>-249.43</v>
       </c>
       <c r="K87" t="n">
-        <v>-33.46</v>
+        <v>140.04</v>
       </c>
       <c r="L87" t="n">
-        <v>292.23</v>
+        <v>286.05</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:10:01</t>
+          <t>10:11:40</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.61</v>
+        <v>4.7</v>
       </c>
       <c r="F88" t="n">
-        <v>10.78</v>
+        <v>10.48</v>
       </c>
       <c r="G88" t="n">
-        <v>309.9</v>
+        <v>307.6</v>
       </c>
       <c r="H88" t="n">
-        <v>40</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I88" t="n">
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-370.91</v>
+        <v>-176.09</v>
       </c>
       <c r="K88" t="n">
-        <v>171.99</v>
+        <v>356.26</v>
       </c>
       <c r="L88" t="n">
-        <v>408.85</v>
+        <v>397.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-04.xlsx
+++ b/output/2024-04-04.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>36.65</v>
+        <v>41.81</v>
       </c>
       <c r="K14" t="n">
-        <v>53.65</v>
+        <v>61.2</v>
       </c>
       <c r="L14" t="n">
-        <v>64.98</v>
+        <v>74.11</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>40.87</v>
+        <v>47.38</v>
       </c>
       <c r="K15" t="n">
-        <v>55.05</v>
+        <v>63.82</v>
       </c>
       <c r="L15" t="n">
-        <v>68.56999999999999</v>
+        <v>79.48999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>32.3</v>
+        <v>38.89</v>
       </c>
       <c r="K16" t="n">
-        <v>49.43</v>
+        <v>59.52</v>
       </c>
       <c r="L16" t="n">
-        <v>59.04</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>50.74</v>
+        <v>57.26</v>
       </c>
       <c r="K17" t="n">
-        <v>-89.73</v>
+        <v>-101.26</v>
       </c>
       <c r="L17" t="n">
-        <v>103.08</v>
+        <v>116.32</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>-67.23999999999999</v>
+        <v>-81.92</v>
       </c>
       <c r="K18" t="n">
-        <v>24.32</v>
+        <v>29.63</v>
       </c>
       <c r="L18" t="n">
-        <v>71.5</v>
+        <v>87.11</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-90.78</v>
+        <v>-102.93</v>
       </c>
       <c r="K19" t="n">
-        <v>42.79</v>
+        <v>48.51</v>
       </c>
       <c r="L19" t="n">
-        <v>100.36</v>
+        <v>113.79</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>89.67</v>
+        <v>114.75</v>
       </c>
       <c r="K20" t="n">
-        <v>-48.15</v>
+        <v>-61.62</v>
       </c>
       <c r="L20" t="n">
-        <v>101.78</v>
+        <v>130.24</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>50.44</v>
+        <v>58.46</v>
       </c>
       <c r="K21" t="n">
-        <v>144.72</v>
+        <v>167.73</v>
       </c>
       <c r="L21" t="n">
-        <v>153.26</v>
+        <v>177.63</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-170.34</v>
+        <v>-198.07</v>
       </c>
       <c r="K22" t="n">
-        <v>27.31</v>
+        <v>31.76</v>
       </c>
       <c r="L22" t="n">
-        <v>172.52</v>
+        <v>200.6</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-225.93</v>
+        <v>-266.33</v>
       </c>
       <c r="K23" t="n">
-        <v>-18.85</v>
+        <v>-22.22</v>
       </c>
       <c r="L23" t="n">
-        <v>226.71</v>
+        <v>267.26</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>131.53</v>
+        <v>166.19</v>
       </c>
       <c r="K24" t="n">
-        <v>91.41</v>
+        <v>115.5</v>
       </c>
       <c r="L24" t="n">
-        <v>160.18</v>
+        <v>202.38</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-136.7</v>
+        <v>-175.05</v>
       </c>
       <c r="K25" t="n">
-        <v>88.34999999999999</v>
+        <v>113.14</v>
       </c>
       <c r="L25" t="n">
-        <v>162.77</v>
+        <v>208.43</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-89.18000000000001</v>
+        <v>-115.13</v>
       </c>
       <c r="K26" t="n">
-        <v>-252.24</v>
+        <v>-325.63</v>
       </c>
       <c r="L26" t="n">
-        <v>267.54</v>
+        <v>345.38</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-202.03</v>
+        <v>-258.95</v>
       </c>
       <c r="K27" t="n">
-        <v>164.59</v>
+        <v>210.97</v>
       </c>
       <c r="L27" t="n">
-        <v>260.59</v>
+        <v>334.01</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>266.76</v>
+        <v>348.09</v>
       </c>
       <c r="K28" t="n">
-        <v>8.32</v>
+        <v>10.85</v>
       </c>
       <c r="L28" t="n">
-        <v>266.89</v>
+        <v>348.26</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-19.91</v>
+        <v>-21.76</v>
       </c>
       <c r="K29" t="n">
-        <v>-88.61</v>
+        <v>-96.88</v>
       </c>
       <c r="L29" t="n">
-        <v>90.81999999999999</v>
+        <v>99.29000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-88.01000000000001</v>
+        <v>-96.09</v>
       </c>
       <c r="K30" t="n">
-        <v>-31.12</v>
+        <v>-33.97</v>
       </c>
       <c r="L30" t="n">
-        <v>93.34999999999999</v>
+        <v>101.92</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-62.55</v>
+        <v>-75.51000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-24.16</v>
+        <v>-29.16</v>
       </c>
       <c r="L31" t="n">
-        <v>67.05</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>75.87</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-21.16</v>
+        <v>-25.74</v>
       </c>
       <c r="L32" t="n">
-        <v>78.76000000000001</v>
+        <v>95.78</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>67.72</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>28.77</v>
+        <v>36.66</v>
       </c>
       <c r="L33" t="n">
-        <v>73.58</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-64.87</v>
+        <v>-76.29000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-63.12</v>
+        <v>-74.23</v>
       </c>
       <c r="L34" t="n">
-        <v>90.51000000000001</v>
+        <v>106.45</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>66.84</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-10.96</v>
+        <v>-14.74</v>
       </c>
       <c r="L35" t="n">
-        <v>67.73</v>
+        <v>91.05</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-122.52</v>
+        <v>-142.3</v>
       </c>
       <c r="K36" t="n">
-        <v>95.51000000000001</v>
+        <v>110.93</v>
       </c>
       <c r="L36" t="n">
-        <v>155.35</v>
+        <v>180.43</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-10.08</v>
+        <v>-12.05</v>
       </c>
       <c r="K37" t="n">
-        <v>161.1</v>
+        <v>192.59</v>
       </c>
       <c r="L37" t="n">
-        <v>161.42</v>
+        <v>192.97</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-155.9</v>
+        <v>-201.91</v>
       </c>
       <c r="K38" t="n">
-        <v>36.59</v>
+        <v>47.39</v>
       </c>
       <c r="L38" t="n">
-        <v>160.13</v>
+        <v>207.4</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>178.21</v>
+        <v>226.24</v>
       </c>
       <c r="K39" t="n">
-        <v>-72.06999999999999</v>
+        <v>-91.5</v>
       </c>
       <c r="L39" t="n">
-        <v>192.23</v>
+        <v>244.04</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>25.81</v>
+        <v>35.42</v>
       </c>
       <c r="K40" t="n">
-        <v>187.73</v>
+        <v>257.66</v>
       </c>
       <c r="L40" t="n">
-        <v>189.49</v>
+        <v>260.08</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-22.81</v>
+        <v>-31.12</v>
       </c>
       <c r="K41" t="n">
-        <v>-263.22</v>
+        <v>-359.06</v>
       </c>
       <c r="L41" t="n">
-        <v>264.2</v>
+        <v>360.41</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-118.44</v>
+        <v>-155.01</v>
       </c>
       <c r="K42" t="n">
-        <v>-314.2</v>
+        <v>-411.19</v>
       </c>
       <c r="L42" t="n">
-        <v>335.78</v>
+        <v>439.44</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-74.09999999999999</v>
+        <v>-98.73</v>
       </c>
       <c r="K43" t="n">
-        <v>236.55</v>
+        <v>315.19</v>
       </c>
       <c r="L43" t="n">
-        <v>247.89</v>
+        <v>330.29</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-49.37</v>
+        <v>-62.78</v>
       </c>
       <c r="K44" t="n">
-        <v>12.01</v>
+        <v>15.28</v>
       </c>
       <c r="L44" t="n">
-        <v>50.81</v>
+        <v>64.61</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-75.87</v>
+        <v>-86.81</v>
       </c>
       <c r="K45" t="n">
-        <v>10.87</v>
+        <v>12.44</v>
       </c>
       <c r="L45" t="n">
-        <v>76.64</v>
+        <v>87.69</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>16.37</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>63.51</v>
+        <v>77.59</v>
       </c>
       <c r="L46" t="n">
-        <v>65.58</v>
+        <v>80.13</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>105.09</v>
+        <v>120.7</v>
       </c>
       <c r="K47" t="n">
-        <v>20.09</v>
+        <v>23.07</v>
       </c>
       <c r="L47" t="n">
-        <v>106.99</v>
+        <v>122.88</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-73.3</v>
+        <v>-84.29000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-52.46</v>
+        <v>-60.33</v>
       </c>
       <c r="L48" t="n">
-        <v>90.13</v>
+        <v>103.65</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>2.94</v>
+        <v>3.74</v>
       </c>
       <c r="K49" t="n">
-        <v>21.15</v>
+        <v>26.92</v>
       </c>
       <c r="L49" t="n">
-        <v>21.35</v>
+        <v>27.18</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-42.13</v>
+        <v>-58.03</v>
       </c>
       <c r="K50" t="n">
-        <v>87.89</v>
+        <v>121.07</v>
       </c>
       <c r="L50" t="n">
-        <v>97.45999999999999</v>
+        <v>134.26</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>37.52</v>
+        <v>49.25</v>
       </c>
       <c r="K51" t="n">
-        <v>-124.9</v>
+        <v>-163.98</v>
       </c>
       <c r="L51" t="n">
-        <v>130.42</v>
+        <v>171.21</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>-32.16</v>
+        <v>-36.34</v>
       </c>
       <c r="K52" t="n">
-        <v>212.93</v>
+        <v>240.56</v>
       </c>
       <c r="L52" t="n">
-        <v>215.34</v>
+        <v>243.29</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-37.53</v>
+        <v>-49.5</v>
       </c>
       <c r="K53" t="n">
-        <v>163.64</v>
+        <v>215.87</v>
       </c>
       <c r="L53" t="n">
-        <v>167.89</v>
+        <v>221.47</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>106.41</v>
+        <v>139.82</v>
       </c>
       <c r="K54" t="n">
-        <v>-126.13</v>
+        <v>-165.74</v>
       </c>
       <c r="L54" t="n">
-        <v>165.03</v>
+        <v>216.84</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>105.09</v>
+        <v>120.55</v>
       </c>
       <c r="K55" t="n">
-        <v>269.66</v>
+        <v>309.34</v>
       </c>
       <c r="L55" t="n">
-        <v>289.41</v>
+        <v>332</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-243.61</v>
+        <v>-312.74</v>
       </c>
       <c r="K56" t="n">
-        <v>71.48</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>253.88</v>
+        <v>325.93</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-338.65</v>
+        <v>-429.62</v>
       </c>
       <c r="K57" t="n">
-        <v>-150.2</v>
+        <v>-190.54</v>
       </c>
       <c r="L57" t="n">
-        <v>370.47</v>
+        <v>469.98</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>133.47</v>
+        <v>179.18</v>
       </c>
       <c r="K58" t="n">
-        <v>-201.9</v>
+        <v>-271.05</v>
       </c>
       <c r="L58" t="n">
-        <v>242.03</v>
+        <v>324.92</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-59.23</v>
+        <v>-68.98999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-37.1</v>
+        <v>-43.22</v>
       </c>
       <c r="L59" t="n">
-        <v>69.89</v>
+        <v>81.41</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>37.05</v>
+        <v>44.77</v>
       </c>
       <c r="K60" t="n">
-        <v>56.5</v>
+        <v>68.27</v>
       </c>
       <c r="L60" t="n">
-        <v>67.56</v>
+        <v>81.64</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.16</v>
+        <v>-1.43</v>
       </c>
       <c r="K61" t="n">
-        <v>-8.26</v>
+        <v>-10.17</v>
       </c>
       <c r="L61" t="n">
-        <v>8.34</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-84.8</v>
+        <v>-99.19</v>
       </c>
       <c r="K62" t="n">
-        <v>18.84</v>
+        <v>22.04</v>
       </c>
       <c r="L62" t="n">
-        <v>86.86</v>
+        <v>101.6</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>101.04</v>
+        <v>114.46</v>
       </c>
       <c r="K63" t="n">
-        <v>-58.71</v>
+        <v>-66.51000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>116.86</v>
+        <v>132.38</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-52.28</v>
+        <v>-59.09</v>
       </c>
       <c r="K64" t="n">
-        <v>-84.43000000000001</v>
+        <v>-95.42</v>
       </c>
       <c r="L64" t="n">
-        <v>99.3</v>
+        <v>112.23</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-141.61</v>
+        <v>-175.85</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.81</v>
+        <v>-5.97</v>
       </c>
       <c r="L65" t="n">
-        <v>141.7</v>
+        <v>175.95</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>127.81</v>
+        <v>160.2</v>
       </c>
       <c r="K66" t="n">
-        <v>76.89</v>
+        <v>96.39</v>
       </c>
       <c r="L66" t="n">
-        <v>149.15</v>
+        <v>186.96</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-25.01</v>
+        <v>-29.26</v>
       </c>
       <c r="K67" t="n">
-        <v>-155.92</v>
+        <v>-182.39</v>
       </c>
       <c r="L67" t="n">
-        <v>157.91</v>
+        <v>184.72</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-159.36</v>
+        <v>-198.75</v>
       </c>
       <c r="K68" t="n">
-        <v>224.3</v>
+        <v>279.74</v>
       </c>
       <c r="L68" t="n">
-        <v>275.15</v>
+        <v>343.15</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>45.16</v>
+        <v>59.42</v>
       </c>
       <c r="K69" t="n">
-        <v>147.88</v>
+        <v>194.6</v>
       </c>
       <c r="L69" t="n">
-        <v>154.62</v>
+        <v>203.47</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-94.89</v>
+        <v>-126.31</v>
       </c>
       <c r="K70" t="n">
-        <v>206.58</v>
+        <v>274.98</v>
       </c>
       <c r="L70" t="n">
-        <v>227.33</v>
+        <v>302.61</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-494.02</v>
+        <v>-620.97</v>
       </c>
       <c r="K71" t="n">
-        <v>-54.86</v>
+        <v>-68.95999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>497.06</v>
+        <v>624.79</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>208.58</v>
+        <v>299.83</v>
       </c>
       <c r="K72" t="n">
-        <v>127.96</v>
+        <v>183.94</v>
       </c>
       <c r="L72" t="n">
-        <v>244.71</v>
+        <v>351.76</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-191.39</v>
+        <v>-280.64</v>
       </c>
       <c r="K73" t="n">
-        <v>210.76</v>
+        <v>309.04</v>
       </c>
       <c r="L73" t="n">
-        <v>284.7</v>
+        <v>417.46</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>86.43000000000001</v>
+        <v>98.34</v>
       </c>
       <c r="K74" t="n">
-        <v>10.6</v>
+        <v>12.06</v>
       </c>
       <c r="L74" t="n">
-        <v>87.08</v>
+        <v>99.06999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>126.51</v>
+        <v>134.39</v>
       </c>
       <c r="K75" t="n">
-        <v>39.37</v>
+        <v>41.82</v>
       </c>
       <c r="L75" t="n">
-        <v>132.49</v>
+        <v>140.75</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>54.16</v>
+        <v>62.9</v>
       </c>
       <c r="K76" t="n">
-        <v>-66.11</v>
+        <v>-76.78</v>
       </c>
       <c r="L76" t="n">
-        <v>85.47</v>
+        <v>99.25</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>12.52</v>
+        <v>14.77</v>
       </c>
       <c r="K77" t="n">
-        <v>-94.18000000000001</v>
+        <v>-111.14</v>
       </c>
       <c r="L77" t="n">
-        <v>95.01000000000001</v>
+        <v>112.12</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-87.5</v>
+        <v>-103.59</v>
       </c>
       <c r="K78" t="n">
-        <v>-27.32</v>
+        <v>-32.34</v>
       </c>
       <c r="L78" t="n">
-        <v>91.66</v>
+        <v>108.52</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-96.66</v>
+        <v>-114.43</v>
       </c>
       <c r="K79" t="n">
-        <v>-17.89</v>
+        <v>-21.18</v>
       </c>
       <c r="L79" t="n">
-        <v>98.3</v>
+        <v>116.37</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-14.54</v>
+        <v>-19.4</v>
       </c>
       <c r="K80" t="n">
-        <v>-15.18</v>
+        <v>-20.25</v>
       </c>
       <c r="L80" t="n">
-        <v>21.02</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>63.23</v>
+        <v>77.12</v>
       </c>
       <c r="K81" t="n">
-        <v>129.05</v>
+        <v>157.4</v>
       </c>
       <c r="L81" t="n">
-        <v>143.71</v>
+        <v>175.28</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-144.3</v>
+        <v>-177.11</v>
       </c>
       <c r="K82" t="n">
-        <v>-46.87</v>
+        <v>-57.52</v>
       </c>
       <c r="L82" t="n">
-        <v>151.72</v>
+        <v>186.21</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-120.71</v>
+        <v>-149.91</v>
       </c>
       <c r="K83" t="n">
-        <v>-187.74</v>
+        <v>-233.16</v>
       </c>
       <c r="L83" t="n">
-        <v>223.19</v>
+        <v>277.19</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-209.34</v>
+        <v>-259.48</v>
       </c>
       <c r="K84" t="n">
-        <v>-154.46</v>
+        <v>-191.45</v>
       </c>
       <c r="L84" t="n">
-        <v>260.16</v>
+        <v>322.46</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-57.98</v>
+        <v>-75.11</v>
       </c>
       <c r="K85" t="n">
-        <v>224.19</v>
+        <v>290.4</v>
       </c>
       <c r="L85" t="n">
-        <v>231.57</v>
+        <v>299.96</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>296.9</v>
+        <v>383.12</v>
       </c>
       <c r="K86" t="n">
-        <v>-242.15</v>
+        <v>-312.47</v>
       </c>
       <c r="L86" t="n">
-        <v>383.13</v>
+        <v>494.39</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>277.05</v>
+        <v>400.6</v>
       </c>
       <c r="K87" t="n">
-        <v>-14.51</v>
+        <v>-20.98</v>
       </c>
       <c r="L87" t="n">
-        <v>277.43</v>
+        <v>401.15</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-219.37</v>
+        <v>-319.62</v>
       </c>
       <c r="K88" t="n">
-        <v>-129.11</v>
+        <v>-188.11</v>
       </c>
       <c r="L88" t="n">
-        <v>254.54</v>
+        <v>370.87</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-04.xlsx
+++ b/output/2024-04-04.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>41.81</v>
+        <v>42.04</v>
       </c>
       <c r="K14" t="n">
-        <v>61.2</v>
+        <v>61.54</v>
       </c>
       <c r="L14" t="n">
-        <v>74.11</v>
+        <v>74.53</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>47.38</v>
+        <v>54.85</v>
       </c>
       <c r="K15" t="n">
-        <v>63.82</v>
+        <v>73.87</v>
       </c>
       <c r="L15" t="n">
-        <v>79.48999999999999</v>
+        <v>92.01000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>38.89</v>
+        <v>48.26</v>
       </c>
       <c r="K16" t="n">
-        <v>59.52</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>71.09999999999999</v>
+        <v>88.22</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>57.26</v>
+        <v>62.84</v>
       </c>
       <c r="K17" t="n">
-        <v>-101.26</v>
+        <v>-111.13</v>
       </c>
       <c r="L17" t="n">
-        <v>116.32</v>
+        <v>127.66</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>-81.92</v>
+        <v>-84.64</v>
       </c>
       <c r="K18" t="n">
-        <v>29.63</v>
+        <v>30.62</v>
       </c>
       <c r="L18" t="n">
-        <v>87.11</v>
+        <v>90.01000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-102.93</v>
+        <v>-111.29</v>
       </c>
       <c r="K19" t="n">
-        <v>48.51</v>
+        <v>52.45</v>
       </c>
       <c r="L19" t="n">
-        <v>113.79</v>
+        <v>123.03</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-21.76</v>
+        <v>-23.81</v>
       </c>
       <c r="K29" t="n">
-        <v>-96.88</v>
+        <v>-105.97</v>
       </c>
       <c r="L29" t="n">
-        <v>99.29000000000001</v>
+        <v>108.61</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-96.09</v>
+        <v>-107.89</v>
       </c>
       <c r="K30" t="n">
-        <v>-33.97</v>
+        <v>-38.14</v>
       </c>
       <c r="L30" t="n">
-        <v>101.92</v>
+        <v>114.43</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-75.51000000000001</v>
+        <v>-90.3</v>
       </c>
       <c r="K31" t="n">
-        <v>-29.16</v>
+        <v>-34.88</v>
       </c>
       <c r="L31" t="n">
-        <v>80.94</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>92.26000000000001</v>
+        <v>103.26</v>
       </c>
       <c r="K32" t="n">
-        <v>-25.74</v>
+        <v>-28.81</v>
       </c>
       <c r="L32" t="n">
-        <v>95.78</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>86.29000000000001</v>
+        <v>107.25</v>
       </c>
       <c r="K33" t="n">
-        <v>36.66</v>
+        <v>45.56</v>
       </c>
       <c r="L33" t="n">
-        <v>93.75</v>
+        <v>116.53</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-76.29000000000001</v>
+        <v>-84.36</v>
       </c>
       <c r="K34" t="n">
-        <v>-74.23</v>
+        <v>-82.08</v>
       </c>
       <c r="L34" t="n">
-        <v>106.45</v>
+        <v>117.7</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-62.78</v>
+        <v>-76.64</v>
       </c>
       <c r="K44" t="n">
-        <v>15.28</v>
+        <v>18.65</v>
       </c>
       <c r="L44" t="n">
-        <v>64.61</v>
+        <v>78.87</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-86.81</v>
+        <v>-98.25</v>
       </c>
       <c r="K45" t="n">
-        <v>12.44</v>
+        <v>14.08</v>
       </c>
       <c r="L45" t="n">
-        <v>87.69</v>
+        <v>99.26000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>26.16</v>
       </c>
       <c r="K46" t="n">
-        <v>77.59</v>
+        <v>101.5</v>
       </c>
       <c r="L46" t="n">
-        <v>80.13</v>
+        <v>104.82</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>120.7</v>
+        <v>141.68</v>
       </c>
       <c r="K47" t="n">
-        <v>23.07</v>
+        <v>27.08</v>
       </c>
       <c r="L47" t="n">
-        <v>122.88</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-84.29000000000001</v>
+        <v>-91</v>
       </c>
       <c r="K48" t="n">
-        <v>-60.33</v>
+        <v>-65.13</v>
       </c>
       <c r="L48" t="n">
-        <v>103.65</v>
+        <v>111.91</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>3.74</v>
+        <v>4.42</v>
       </c>
       <c r="K49" t="n">
-        <v>26.92</v>
+        <v>31.8</v>
       </c>
       <c r="L49" t="n">
-        <v>27.18</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-68.98999999999999</v>
+        <v>-82.51000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-43.22</v>
+        <v>-51.69</v>
       </c>
       <c r="L59" t="n">
-        <v>81.41</v>
+        <v>97.37</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>44.77</v>
+        <v>56.47</v>
       </c>
       <c r="K60" t="n">
-        <v>68.27</v>
+        <v>86.11</v>
       </c>
       <c r="L60" t="n">
-        <v>81.64</v>
+        <v>102.97</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.43</v>
+        <v>-1.77</v>
       </c>
       <c r="K61" t="n">
-        <v>-10.17</v>
+        <v>-12.65</v>
       </c>
       <c r="L61" t="n">
-        <v>10.27</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-99.19</v>
+        <v>-115.53</v>
       </c>
       <c r="K62" t="n">
-        <v>22.04</v>
+        <v>25.67</v>
       </c>
       <c r="L62" t="n">
-        <v>101.6</v>
+        <v>118.35</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>114.46</v>
+        <v>138.58</v>
       </c>
       <c r="K63" t="n">
-        <v>-66.51000000000001</v>
+        <v>-80.52</v>
       </c>
       <c r="L63" t="n">
-        <v>132.38</v>
+        <v>160.28</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-59.09</v>
+        <v>-67.67</v>
       </c>
       <c r="K64" t="n">
-        <v>-95.42</v>
+        <v>-109.28</v>
       </c>
       <c r="L64" t="n">
-        <v>112.23</v>
+        <v>128.54</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>98.34</v>
+        <v>139.04</v>
       </c>
       <c r="K74" t="n">
-        <v>12.06</v>
+        <v>17.05</v>
       </c>
       <c r="L74" t="n">
-        <v>99.06999999999999</v>
+        <v>140.08</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>134.39</v>
+        <v>187.42</v>
       </c>
       <c r="K75" t="n">
-        <v>41.82</v>
+        <v>58.32</v>
       </c>
       <c r="L75" t="n">
-        <v>140.75</v>
+        <v>196.28</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>62.9</v>
+        <v>88.06</v>
       </c>
       <c r="K76" t="n">
-        <v>-76.78</v>
+        <v>-107.49</v>
       </c>
       <c r="L76" t="n">
-        <v>99.25</v>
+        <v>138.96</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>14.77</v>
+        <v>17.97</v>
       </c>
       <c r="K77" t="n">
-        <v>-111.14</v>
+        <v>-135.19</v>
       </c>
       <c r="L77" t="n">
-        <v>112.12</v>
+        <v>136.37</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-103.59</v>
+        <v>-114.72</v>
       </c>
       <c r="K78" t="n">
-        <v>-32.34</v>
+        <v>-35.82</v>
       </c>
       <c r="L78" t="n">
-        <v>108.52</v>
+        <v>120.18</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-114.43</v>
+        <v>-143.78</v>
       </c>
       <c r="K79" t="n">
-        <v>-21.18</v>
+        <v>-26.61</v>
       </c>
       <c r="L79" t="n">
-        <v>116.37</v>
+        <v>146.22</v>
       </c>
     </row>
     <row r="80">
